--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D30</f>
+        <f>'Mano de Obra'!D28</f>
         <v/>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17453,7 +17453,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D30</f>
+        <f>D5/D28</f>
         <v/>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D30</f>
+        <f>D6/D28</f>
         <v/>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D30</f>
+        <f>D7/D28</f>
         <v/>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D30</f>
+        <f>D8/D28</f>
         <v/>
       </c>
     </row>
@@ -17549,7 +17549,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D30</f>
+        <f>D9/D28</f>
         <v/>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D30</f>
+        <f>D10/D28</f>
         <v/>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D30</f>
+        <f>D11/D28</f>
         <v/>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D30</f>
+        <f>D12/D28</f>
         <v/>
       </c>
     </row>
@@ -17645,7 +17645,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D30</f>
+        <f>D13/D28</f>
         <v/>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D30</f>
+        <f>D14/D28</f>
         <v/>
       </c>
     </row>
@@ -17680,7 +17680,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2224</v>
+        <v>2256</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -17693,7 +17693,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D30</f>
+        <f>D15/D28</f>
         <v/>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D30</f>
+        <f>D16/D28</f>
         <v/>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D30</f>
+        <f>D17/D28</f>
         <v/>
       </c>
     </row>
@@ -17765,7 +17765,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D30</f>
+        <f>D18/D28</f>
         <v/>
       </c>
     </row>
@@ -17789,7 +17789,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D30</f>
+        <f>D19/D28</f>
         <v/>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D30</f>
+        <f>D20/D28</f>
         <v/>
       </c>
     </row>
@@ -17837,7 +17837,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D30</f>
+        <f>D21/D28</f>
         <v/>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D30</f>
+        <f>D22/D28</f>
         <v/>
       </c>
     </row>
@@ -17885,7 +17885,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D30</f>
+        <f>D23/D28</f>
         <v/>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D30</f>
+        <f>D24/D28</f>
         <v/>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D30</f>
+        <f>D25/D28</f>
         <v/>
       </c>
     </row>
@@ -17957,7 +17957,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D30</f>
+        <f>D26/D28</f>
         <v/>
       </c>
     </row>
@@ -17981,73 +17981,27 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D30</f>
+        <f>D27/D28</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>2100 - MURO VECINO</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>10550.72</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F28" s="6">
-        <f>D28/D30</f>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="B28" s="7">
+        <f>SUM(B5:B27)</f>
         <v/>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>2600 - OBRA CAMPO</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>19055.33</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F29" s="6">
-        <f>D29/D30</f>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8">
+        <f>SUM(D5:D27)</f>
         <v/>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="B30" s="7">
-        <f>SUM(B5:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17800,7 +17800,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>992</v>
+        <v>1016</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>23917.62</v>
+        <v>2.391762e+16</v>
       </c>
       <c r="D5" s="6">
         <f>C5/C24</f>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>63277.34</v>
+        <v>6.327734e+16</v>
       </c>
       <c r="D9" s="6">
         <f>C9/C24</f>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>116432.26</v>
+        <v>1.1643226e+16</v>
       </c>
       <c r="D12" s="6">
         <f>C12/C24</f>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>88834.71000000001</v>
+        <v>8883470999999999</v>
       </c>
       <c r="D17" s="6">
         <f>C17/C24</f>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D28</f>
+        <f>'Mano de Obra'!D30</f>
         <v/>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17453,7 +17453,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D28</f>
+        <f>D5/D30</f>
         <v/>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D28</f>
+        <f>D6/D30</f>
         <v/>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D28</f>
+        <f>D7/D30</f>
         <v/>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D28</f>
+        <f>D8/D30</f>
         <v/>
       </c>
     </row>
@@ -17549,7 +17549,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D28</f>
+        <f>D9/D30</f>
         <v/>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D28</f>
+        <f>D10/D30</f>
         <v/>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D28</f>
+        <f>D11/D30</f>
         <v/>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D28</f>
+        <f>D12/D30</f>
         <v/>
       </c>
     </row>
@@ -17645,7 +17645,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D28</f>
+        <f>D13/D30</f>
         <v/>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D28</f>
+        <f>D14/D30</f>
         <v/>
       </c>
     </row>
@@ -17693,7 +17693,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D28</f>
+        <f>D15/D30</f>
         <v/>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D28</f>
+        <f>D16/D30</f>
         <v/>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D28</f>
+        <f>D17/D30</f>
         <v/>
       </c>
     </row>
@@ -17765,7 +17765,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D28</f>
+        <f>D18/D30</f>
         <v/>
       </c>
     </row>
@@ -17789,7 +17789,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D28</f>
+        <f>D19/D30</f>
         <v/>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D28</f>
+        <f>D20/D30</f>
         <v/>
       </c>
     </row>
@@ -17837,7 +17837,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D28</f>
+        <f>D21/D30</f>
         <v/>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D28</f>
+        <f>D22/D30</f>
         <v/>
       </c>
     </row>
@@ -17885,7 +17885,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D28</f>
+        <f>D23/D30</f>
         <v/>
       </c>
     </row>
@@ -17909,7 +17909,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D28</f>
+        <f>D24/D30</f>
         <v/>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D28</f>
+        <f>D25/D30</f>
         <v/>
       </c>
     </row>
@@ -17957,7 +17957,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D28</f>
+        <f>D26/D30</f>
         <v/>
       </c>
     </row>
@@ -17981,27 +17981,75 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D28</f>
+        <f>D27/D30</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2100 - MURO VECINO</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>10550</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="4">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F28" s="6">
+        <f>D28/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2600 - OBRA CAMPO</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>19055</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="6">
+        <f>D29/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(B5:B27)</f>
+      <c r="B30" s="7">
+        <f>SUM(B5:B29)</f>
         <v/>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8">
-        <f>SUM(D5:D27)</f>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8">
+        <f>SUM(D5:D29)</f>
         <v/>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17992,14 +17992,13 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>10550</v>
+        <v>0</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D28" s="4">
-        <f>B28*C28</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>10550.72</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>2026</v>
@@ -18016,14 +18015,13 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>19055</v>
+        <v>0</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" s="4">
-        <f>B29*C29</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>19055.33</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>2026</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2.391762e+16</v>
+        <v>23917.62</v>
       </c>
       <c r="D5" s="6">
         <f>C5/C24</f>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.327734e+16</v>
+        <v>63277.34</v>
       </c>
       <c r="D9" s="6">
         <f>C9/C24</f>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.1643226e+16</v>
+        <v>116432.26</v>
       </c>
       <c r="D12" s="6">
         <f>C12/C24</f>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>8883470999999999</v>
+        <v>88834.70999999999</v>
       </c>
       <c r="D17" s="6">
         <f>C17/C24</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17680,7 +17680,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2256</v>
+        <v>2292</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -17800,7 +17800,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1016</v>
+        <v>1044</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -18363,7 +18363,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -52786,7 +52786,7 @@
     <row r="1034">
       <c r="A1034" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
         </is>
       </c>
       <c r="B1034" s="6" t="inlineStr">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17916,7 +17916,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -18363,7 +18363,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -52786,7 +52786,7 @@
     <row r="1034">
       <c r="A1034" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B1034" s="6" t="inlineStr">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -7893,7 +7893,7 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>950,00</t>
+          <t>950</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
@@ -7919,7 +7919,7 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>928,00</t>
+          <t>928</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -7945,7 +7945,7 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>927,00</t>
+          <t>927</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>926,00</t>
+          <t>926</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>925,00</t>
+          <t>925</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>924,00</t>
+          <t>924</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -8049,7 +8049,7 @@
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>922,00</t>
+          <t>922</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
@@ -8071,7 +8071,7 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>917,00</t>
+          <t>917</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>906,00</t>
+          <t>906</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>890,00</t>
+          <t>890</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>888,00</t>
+          <t>888</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
@@ -8175,7 +8175,7 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>887,00</t>
+          <t>887</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>886,00</t>
+          <t>886</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>885,00</t>
+          <t>885</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>878,00</t>
+          <t>878</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>873,00</t>
+          <t>873</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -8305,7 +8305,7 @@
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>872,00</t>
+          <t>872</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
@@ -8331,7 +8331,7 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>871,00</t>
+          <t>871</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>870,00</t>
+          <t>870</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
@@ -8383,7 +8383,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>866,00</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -8409,7 +8409,7 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>863,00</t>
+          <t>863</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
@@ -8435,7 +8435,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>857,00</t>
+          <t>857</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>842,00</t>
+          <t>842</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>826,00</t>
+          <t>826</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -8771,7 +8771,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>908,00</t>
+          <t>908</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>907,00</t>
+          <t>907</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>911,00</t>
+          <t>911</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>901,00</t>
+          <t>901</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>916,00</t>
+          <t>916</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>900,00</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>913,00</t>
+          <t>913</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>904,00</t>
+          <t>904</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>902,00</t>
+          <t>902</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>912,00</t>
+          <t>912</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>820,00</t>
+          <t>820</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>819,00</t>
+          <t>819</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>821,00</t>
+          <t>821</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>626,00</t>
+          <t>626</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>909,00</t>
+          <t>909</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>499,00</t>
+          <t>499</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>858,00</t>
+          <t>858</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>860,00</t>
+          <t>860</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>855,00</t>
+          <t>855</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>818,00</t>
+          <t>818</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>884,00</t>
+          <t>884</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>498,00</t>
+          <t>498</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>856,00</t>
+          <t>856</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>618,00</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>605,00</t>
+          <t>605</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>632,00</t>
+          <t>632</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>583,00</t>
+          <t>583</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>625,00</t>
+          <t>625</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>861,00</t>
+          <t>861</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>899,00</t>
+          <t>899</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>639,00</t>
+          <t>639</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>630,00</t>
+          <t>630</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>822,00</t>
+          <t>822</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>825,00</t>
+          <t>825</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>792,00</t>
+          <t>792</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>600,00</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>824,00</t>
+          <t>824</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>536,00</t>
+          <t>536</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>631,00</t>
+          <t>631</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>612,00</t>
+          <t>612</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>867,00</t>
+          <t>867</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>621,00</t>
+          <t>621</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>864,00</t>
+          <t>864</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>865,00</t>
+          <t>865</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>642,00</t>
+          <t>642</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>645,00</t>
+          <t>645</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
@@ -18370,7 +18370,7 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>613,00</t>
+          <t>613</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
@@ -18475,7 +18475,7 @@
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>801,00</t>
+          <t>801</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>898,00</t>
+          <t>898</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
@@ -18545,7 +18545,7 @@
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>897,00</t>
+          <t>897</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>869,00</t>
+          <t>869</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>896,00</t>
+          <t>896</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>800,00</t>
+          <t>800</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>799,00</t>
+          <t>799</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>798,00</t>
+          <t>798</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>797,00</t>
+          <t>797</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>796,00</t>
+          <t>796</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>795,00</t>
+          <t>795</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>894,00</t>
+          <t>894</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>601,00</t>
+          <t>601</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>839,00</t>
+          <t>839</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>859,00</t>
+          <t>859</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>538,00</t>
+          <t>538</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>622,00</t>
+          <t>622</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>883,00</t>
+          <t>883</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
@@ -21523,7 +21523,7 @@
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>623,00</t>
+          <t>623</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>823,00</t>
+          <t>823</t>
         </is>
       </c>
       <c r="C338" s="6" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>813,00</t>
+          <t>813</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>889,00</t>
+          <t>889</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>791,00</t>
+          <t>791</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>811,00</t>
+          <t>811</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
@@ -21943,7 +21943,7 @@
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>862,00</t>
+          <t>862</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>891,00</t>
+          <t>891</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>854,00</t>
+          <t>854</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
@@ -22919,7 +22919,7 @@
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>788,00</t>
+          <t>788</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>789,00</t>
+          <t>789</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>595,00</t>
+          <t>595</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>877,00</t>
+          <t>877</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>876,00</t>
+          <t>876</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>594,00</t>
+          <t>594</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>589,00</t>
+          <t>589</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
@@ -23374,7 +23374,7 @@
       </c>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>875,00</t>
+          <t>875</t>
         </is>
       </c>
       <c r="C390" s="6" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>914,00</t>
+          <t>914</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
@@ -23444,7 +23444,7 @@
       </c>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>918,00</t>
+          <t>918</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>610,00</t>
+          <t>610</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>598,00</t>
+          <t>598</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>619,00</t>
+          <t>619</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>879,00</t>
+          <t>879</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>615,00</t>
+          <t>615</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>603,00</t>
+          <t>603</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>840,00</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>597,00</t>
+          <t>597</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>841,00</t>
+          <t>841</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>614,00</t>
+          <t>614</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>814,00</t>
+          <t>814</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>812,00</t>
+          <t>812</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
@@ -24630,7 +24630,7 @@
       </c>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>851,00</t>
+          <t>851</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
@@ -24665,7 +24665,7 @@
       </c>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>874,00</t>
+          <t>874</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>853,00</t>
+          <t>853</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>852,00</t>
+          <t>852</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>880,00</t>
+          <t>880</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>893,00</t>
+          <t>893</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
@@ -24840,7 +24840,7 @@
       </c>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>881,00</t>
+          <t>881</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>892,00</t>
+          <t>892</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4083</v>
+        <v>4119</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1044</v>
+        <v>1068</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2292</v>
+        <v>2332</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1068</v>
+        <v>1084</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2328</v>
+        <v>2352</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1080</v>
+        <v>1104</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D30</f>
+        <f>'Mano de Obra'!D31</f>
         <v/>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D30</f>
+        <f>D5/D31</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D30</f>
+        <f>D6/D31</f>
         <v/>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D30</f>
+        <f>D7/D31</f>
         <v/>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D30</f>
+        <f>D8/D31</f>
         <v/>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D30</f>
+        <f>D9/D31</f>
         <v/>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D30</f>
+        <f>D10/D31</f>
         <v/>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D30</f>
+        <f>D11/D31</f>
         <v/>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D30</f>
+        <f>D12/D31</f>
         <v/>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D30</f>
+        <f>D13/D31</f>
         <v/>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D30</f>
+        <f>D14/D31</f>
         <v/>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D30</f>
+        <f>D15/D31</f>
         <v/>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D30</f>
+        <f>D16/D31</f>
         <v/>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D30</f>
+        <f>D17/D31</f>
         <v/>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D30</f>
+        <f>D18/D31</f>
         <v/>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D30</f>
+        <f>D19/D31</f>
         <v/>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D30</f>
+        <f>D20/D31</f>
         <v/>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D30</f>
+        <f>D21/D31</f>
         <v/>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D30</f>
+        <f>D22/D31</f>
         <v/>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D30</f>
+        <f>D23/D31</f>
         <v/>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D30</f>
+        <f>D24/D31</f>
         <v/>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D30</f>
+        <f>D25/D31</f>
         <v/>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D30</f>
+        <f>D26/D31</f>
         <v/>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D30</f>
+        <f>D27/D31</f>
         <v/>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
         <v>2026</v>
       </c>
       <c r="F28" s="6">
-        <f>D28/D30</f>
+        <f>D28/D31</f>
         <v/>
       </c>
     </row>
@@ -9501,27 +9501,51 @@
         <v>2026</v>
       </c>
       <c r="F29" s="6">
-        <f>D29/D30</f>
+        <f>D29/D31</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F30" s="6">
+        <f>D30/D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(B5:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
+      <c r="B31" s="7">
+        <f>SUM(B5:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8">
+        <f>SUM(D5:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2352</v>
+        <v>2376</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1104</v>
+        <v>1136</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20972.59</v>
+        <v>15047.28</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C24</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D31</f>
+        <f>'Mano de Obra'!D32</f>
         <v/>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D31</f>
+        <f>D5/D32</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D31</f>
+        <f>D6/D32</f>
         <v/>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D31</f>
+        <f>D7/D32</f>
         <v/>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D31</f>
+        <f>D8/D32</f>
         <v/>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D31</f>
+        <f>D9/D32</f>
         <v/>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D31</f>
+        <f>D10/D32</f>
         <v/>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D31</f>
+        <f>D11/D32</f>
         <v/>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D31</f>
+        <f>D12/D32</f>
         <v/>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D31</f>
+        <f>D13/D32</f>
         <v/>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D31</f>
+        <f>D14/D32</f>
         <v/>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D31</f>
+        <f>D15/D32</f>
         <v/>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D31</f>
+        <f>D16/D32</f>
         <v/>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D31</f>
+        <f>D17/D32</f>
         <v/>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D31</f>
+        <f>D18/D32</f>
         <v/>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D31</f>
+        <f>D19/D32</f>
         <v/>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D31</f>
+        <f>D20/D32</f>
         <v/>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D31</f>
+        <f>D21/D32</f>
         <v/>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D31</f>
+        <f>D22/D32</f>
         <v/>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D31</f>
+        <f>D23/D32</f>
         <v/>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D31</f>
+        <f>D24/D32</f>
         <v/>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D31</f>
+        <f>D25/D32</f>
         <v/>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D31</f>
+        <f>D26/D32</f>
         <v/>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D31</f>
+        <f>D27/D32</f>
         <v/>
       </c>
     </row>
@@ -9472,13 +9472,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10550.72</v>
+        <v>8976</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>2026</v>
       </c>
       <c r="F28" s="6">
-        <f>D28/D31</f>
+        <f>D28/D32</f>
         <v/>
       </c>
     </row>
@@ -9495,13 +9495,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>19055.33</v>
+        <v>16201</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>2026</v>
       </c>
       <c r="F29" s="6">
-        <f>D29/D31</f>
+        <f>D29/D32</f>
         <v/>
       </c>
     </row>
@@ -9525,27 +9525,51 @@
         <v>2026</v>
       </c>
       <c r="F30" s="6">
-        <f>D30/D31</f>
+        <f>D30/D32</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F31" s="6">
+        <f>D31/D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(B5:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8">
-        <f>SUM(D5:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
+      <c r="B32" s="7">
+        <f>SUM(B5:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8">
+        <f>SUM(D5:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2400</v>
+        <v>2424</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'Gastos Generales'!E262</f>
+        <f>'Gastos Generales'!E264</f>
         <v/>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F262"/>
+  <dimension ref="A1:F264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1890,7 +1890,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GASTOS GENERALES (258 facturas)</t>
+          <t>GASTOS GENERALES (260 facturas)</t>
         </is>
       </c>
     </row>
@@ -1929,277 +1929,269 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1.922,00</t>
+          <t>1.925,00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>HOLDED AGOSTO</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
-        </is>
-      </c>
+          <t>VIA T - JULIO</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="4" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1.918,00</t>
+          <t>1.924,00</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL AGOSTO</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>PLENOIL SL.</t>
-        </is>
-      </c>
+          <t>VIA T - AGOSTO</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="4" t="n">
-        <v>846.6900000000001</v>
+        <v>15</v>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.911,00</t>
+          <t>1.922,00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE SEPTIEMBRE</t>
+          <t>HOLDED AGOSTO</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>350</v>
+        <v>59</v>
       </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1.910,00</t>
+          <t>1.918,00</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE AGOSTO</t>
+          <t>PLENOIL AGOSTO</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>350</v>
+        <v>846.6900000000001</v>
       </c>
       <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.908,00</t>
+          <t>1.911,00</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>NATURGY AGOSTO</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
+          <t>ALQUILER NAVE SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="n">
-        <v>53.13</v>
+        <v>350</v>
       </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1.899,00</t>
+          <t>1.910,00</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - AGOSTO</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr"/>
+          <t>ALQUILER NAVE AGOSTO</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n">
-        <v>54.51</v>
+        <v>350</v>
       </c>
       <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.898,00</t>
+          <t>1.908,00</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3  - SEPTIEMBRE</t>
+          <t>NATURGY AGOSTO</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="4" t="n">
-        <v>54.36</v>
+        <v>53.13</v>
       </c>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1.897,00</t>
+          <t>1.899,00</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL JULIO</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>PLENOIL SL.</t>
-        </is>
-      </c>
+          <t>CONECTA 3 - AGOSTO</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="4" t="n">
-        <v>1699.09</v>
+        <v>54.51</v>
       </c>
       <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.882,00</t>
+          <t>1.898,00</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL JULIO</t>
+          <t>CONECTA 3  - SEPTIEMBRE</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="4" t="n">
-        <v>260</v>
+        <v>54.36</v>
       </c>
       <c r="F12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1.875,00</t>
+          <t>1.897,00</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PLENOIL JULIO</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>CONCORDY SA</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>74.39</v>
+        <v>1699.09</v>
       </c>
       <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.874,00</t>
+          <t>1.882,00</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTOS MEDICOS</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL JULIO</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="4" t="n">
-        <v>175.8</v>
+        <v>260</v>
       </c>
       <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1.873,00</t>
+          <t>1.875,00</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2209,206 +2201,206 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>CONCORDY SA</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n">
-        <v>360.15</v>
+        <v>74.39</v>
       </c>
       <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.860,00</t>
+          <t>1.874,00</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>RECONOCIMIENTOS MEDICOS</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>260</v>
+        <v>175.8</v>
       </c>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1.850,00</t>
+          <t>1.873,00</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>CUERDA</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>FERRELDA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="4" t="n">
-        <v>64.7</v>
+        <v>360.15</v>
       </c>
       <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.846,00</t>
+          <t>1.860,00</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>LAVADO COHES</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>FARES JAVIER HERNANDEZ OSORIO</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1.845,00</t>
+          <t>1.850,00</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>LAVADO OPEL COMBO</t>
+          <t>CUERDA</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>FARES JAVIER HERNANDEZ OSORIO</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>35</v>
+        <v>64.7</v>
       </c>
       <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.842,00</t>
+          <t>1.846,00</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>SACO ASPIRADORA</t>
+          <t>LAVADO COHES</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>HILTI ESPAÑOLA SA</t>
+          <t>FARES JAVIER HERNANDEZ OSORIO</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>74.76000000000001</v>
+        <v>59</v>
       </c>
       <c r="F20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1.827,00</t>
+          <t>1.845,00</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>LAVADO OPEL COMBO</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>FARES JAVIER HERNANDEZ OSORIO</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>16.53</v>
+        <v>35</v>
       </c>
       <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.826,00</t>
+          <t>1.842,00</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE JULIO</t>
+          <t>SACO ASPIRADORA</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>HILTI ESPAÑOLA SA</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>350</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1.825,00</t>
+          <t>1.827,00</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2418,410 +2410,410 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>22.97</v>
+        <v>16.53</v>
       </c>
       <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1.822,00</t>
+          <t>1.826,00</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>DISCO DE CORTE</t>
+          <t>ALQUILER NAVE JULIO</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>187.5</v>
+        <v>350</v>
       </c>
       <c r="F24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1.815,00</t>
+          <t>1.825,00</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>SPRAY PINTURA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>19.31</v>
+        <v>22.97</v>
       </c>
       <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1.814,00</t>
+          <t>1.822,00</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTO MÉDICO</t>
+          <t>DISCO DE CORTE</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>175.8</v>
+        <v>187.5</v>
       </c>
       <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1.811,00</t>
+          <t>1.815,00</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>ASESORÍA LABORAL JUNIO</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
+          <t>SPRAY PINTURA</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>PINTURAS IDELLA SL.</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="n">
-        <v>260</v>
+        <v>19.31</v>
       </c>
       <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1.808,00</t>
+          <t>1.814,00</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>TAPA POROS HIERRO GALVANIZADO</t>
+          <t>RECONOCIMIENTO MÉDICO</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-17</v>
+        <v>175.8</v>
       </c>
       <c r="F28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1.807,00</t>
+          <t>1.811,00</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>FONTANERIA</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
-        </is>
-      </c>
+          <t>ASESORÍA LABORAL JUNIO</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="4" t="n">
-        <v>-29.68</v>
+        <v>260</v>
       </c>
       <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1.806,00</t>
+          <t>1.808,00</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>MAQUINARIA HONDA</t>
+          <t>TAPA POROS HIERRO GALVANIZADO</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>POLI PRIMI SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1983.47</v>
+        <v>-17</v>
       </c>
       <c r="F30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>1.805,00</t>
+          <t>1.807,00</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>HOLDED JUNIO</t>
+          <t>FONTANERIA</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>59</v>
+        <v>-29.68</v>
       </c>
       <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>1.799,00</t>
+          <t>1.806,00</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL JUNIO</t>
+          <t>MAQUINARIA HONDA</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>POLI PRIMI SL</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1745.38</v>
+        <v>1983.47</v>
       </c>
       <c r="F32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1.797,00</t>
+          <t>1.805,00</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>VARIOS COMPRA</t>
+          <t>HOLDED JUNIO</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>134.86</v>
+        <v>59</v>
       </c>
       <c r="F33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1.794,00</t>
+          <t>1.799,00</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>NATURGY JUNIO</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
+          <t>PLENOIL JUNIO</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>PLENOIL SL.</t>
+        </is>
+      </c>
       <c r="E34" s="4" t="n">
-        <v>30.35</v>
+        <v>1745.38</v>
       </c>
       <c r="F34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>1.786,00</t>
+          <t>1.797,00</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>SACO PARA POLVO</t>
+          <t>VARIOS COMPRA</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>HILTI ESPAÑOLA SA</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>100.28</v>
+        <v>134.86</v>
       </c>
       <c r="F35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1.785,00</t>
+          <t>1.794,00</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>JR VIDAL RICO SL</t>
-        </is>
-      </c>
+          <t>NATURGY JUNIO</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="4" t="n">
-        <v>65.69</v>
+        <v>30.35</v>
       </c>
       <c r="F36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1.776,00</t>
+          <t>1.786,00</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>SACO PARA POLVO</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>HILTI ESPAÑOLA SA</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>11.83</v>
+        <v>100.28</v>
       </c>
       <c r="F37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1.775,00</t>
+          <t>1.785,00</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>ARANDELAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>JR VIDAL RICO SL</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>43.75</v>
+        <v>65.69</v>
       </c>
       <c r="F38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>1.774,00</t>
+          <t>1.776,00</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>FONTANERIA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2830,24 +2822,24 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>29.68</v>
+        <v>11.83</v>
       </c>
       <c r="F39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1.768,00</t>
+          <t>1.775,00</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>CONTROLADOR PH</t>
+          <t>ARANDELAS</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2856,166 +2848,166 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>34.83</v>
+        <v>43.75</v>
       </c>
       <c r="F40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>1.767,00</t>
+          <t>1.774,00</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OFICINA</t>
+          <t>FONTANERIA</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>LOPA PAPER SL.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>29.68</v>
       </c>
       <c r="F41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>1.766,00</t>
+          <t>1.768,00</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>VIA T</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr"/>
+          <t>CONTROLADOR PH</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+        </is>
+      </c>
       <c r="E42" s="4" t="n">
-        <v>2.69</v>
+        <v>34.83</v>
       </c>
       <c r="F42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1.756,00</t>
+          <t>1.767,00</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL OFICINA</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>EXPLOTACION ESTACION DE SERVICIO SA</t>
+          <t>LOPA PAPER SL.</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>72.16</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>1.755,00</t>
+          <t>1.766,00</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>DM BRICO SL</t>
-        </is>
-      </c>
+          <t>VIA T</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="4" t="n">
-        <v>218.18</v>
+        <v>2.69</v>
       </c>
       <c r="F44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>1.754,00</t>
+          <t>1.756,00</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>FOCOS LUZ</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>EXPLOTACION ESTACION DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>66.06999999999999</v>
+        <v>72.16</v>
       </c>
       <c r="F45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1.753,00</t>
+          <t>1.755,00</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>PH REDUCTOR</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>DM BRICO SL</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>19.48</v>
+        <v>218.18</v>
       </c>
       <c r="F46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>1.752,00</t>
+          <t>1.754,00</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3025,111 +3017,111 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>RUEDAS</t>
+          <t>FOCOS LUZ</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>20.38</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="F47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1.751,00</t>
+          <t>1.753,00</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL / BERMUDAS</t>
+          <t>PH REDUCTOR</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>FORMATO DIGITAL ACTIVIDADES PUBLICITARIAS SOCIEDAD LIMITADA.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>142.6</v>
+        <v>19.48</v>
       </c>
       <c r="F48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1.750,00</t>
+          <t>1.752,00</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>COLCHA</t>
+          <t>RUEDAS</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>50.4</v>
+        <v>20.38</v>
       </c>
       <c r="F49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1.749,00</t>
+          <t>1.751,00</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>COMPRA AMAZON</t>
+          <t>ROPA LABORAL / BERMUDAS</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
+          <t>FORMATO DIGITAL ACTIVIDADES PUBLICITARIAS SOCIEDAD LIMITADA.</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>28.92</v>
+        <v>142.6</v>
       </c>
       <c r="F50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>1.748,00</t>
+          <t>1.750,00</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>FUNDA JARDIN</t>
+          <t>COLCHA</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3138,50 +3130,50 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>53.71</v>
+        <v>50.4</v>
       </c>
       <c r="F51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>1.747,00</t>
+          <t>1.749,00</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>PAGO TJ AMAZON</t>
+          <t>COMPRA AMAZON</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>40.25</v>
+        <v>28.92</v>
       </c>
       <c r="F52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>1.746,00</t>
+          <t>1.748,00</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>PAGO TJ AMAZON</t>
+          <t>FUNDA JARDIN</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -3190,50 +3182,50 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>24.29</v>
+        <v>53.71</v>
       </c>
       <c r="F53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>1.744,00</t>
+          <t>1.747,00</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>HORAS JARDINERIA</t>
+          <t>PAGO TJ AMAZON</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>MARCOS GALIANO POVEDA</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>178</v>
+        <v>40.25</v>
       </c>
       <c r="F54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>1.730,00</t>
+          <t>1.746,00</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>ARRANCADOR COCHE</t>
+          <t>PAGO TJ AMAZON</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -3242,267 +3234,267 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>57.84</v>
+        <v>24.29</v>
       </c>
       <c r="F55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>1.728,00</t>
+          <t>1.744,00</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>HORAS JARDINERIA</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>MARCOS GALIANO POVEDA</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>27.26</v>
+        <v>178</v>
       </c>
       <c r="F56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>1.726,00</t>
+          <t>1.730,00</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>CALZADO LABORAL</t>
+          <t>ARRANCADOR COCHE</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>79.67</v>
+        <v>57.84</v>
       </c>
       <c r="F57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>1.722,00</t>
+          <t>1.728,00</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>HOLDED MAYO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>59</v>
+        <v>27.26</v>
       </c>
       <c r="F58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>1.721,00</t>
+          <t>1.726,00</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>ASESORÍA MAYO</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr"/>
+          <t>CALZADO LABORAL</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>BRICOLAJE BRICOMAN SLU</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="n">
-        <v>260</v>
+        <v>79.67</v>
       </c>
       <c r="F59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>1.720,00</t>
+          <t>1.722,00</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>HOLDED MAYO</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>15.19</v>
+        <v>59</v>
       </c>
       <c r="F60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>1.716,00</t>
+          <t>1.721,00</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>NATURGY MAYO</t>
+          <t>ASESORÍA MAYO</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr"/>
       <c r="E61" s="4" t="n">
-        <v>25.3</v>
+        <v>260</v>
       </c>
       <c r="F61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>1.708,00</t>
+          <t>1.720,00</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>MAQUINA MULTIHERRAMIENTA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>DETECTALIA EUROPE SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3304.96</v>
+        <v>15.19</v>
       </c>
       <c r="F62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>1.706,00</t>
+          <t>1.716,00</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL JUNIO</t>
+          <t>NATURGY MAYO</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr"/>
       <c r="E63" s="4" t="n">
-        <v>360.15</v>
+        <v>25.3</v>
       </c>
       <c r="F63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>1.699,00</t>
+          <t>1.708,00</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MAQUINA MULTIHERRAMIENTA</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
+          <t>DETECTALIA EUROPE SL</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>8.26</v>
+        <v>3304.96</v>
       </c>
       <c r="F64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>1.698,00</t>
+          <t>1.706,00</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>TAPON LATON</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>ROSALIA MARTINEZ RUIZ</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL JUNIO</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr"/>
       <c r="E65" s="4" t="n">
-        <v>1.69</v>
+        <v>360.15</v>
       </c>
       <c r="F65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>1.693,00</t>
+          <t>1.699,00</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3512,49 +3504,49 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>82.22</v>
+        <v>8.26</v>
       </c>
       <c r="F66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>1.692,00</t>
+          <t>1.698,00</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
+          <t>TAPON LATON</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>CHINAWIN IBERICA SL</t>
+          <t>ROSALIA MARTINEZ RUIZ</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>46.28</v>
+        <v>1.69</v>
       </c>
       <c r="F67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>1.685,00</t>
+          <t>1.693,00</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -3564,526 +3556,526 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>55.23</v>
+        <v>82.22</v>
       </c>
       <c r="F68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>1.681,00</t>
+          <t>1.692,00</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE JUNIO</t>
+          <t>ROPA LABORAL</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>350</v>
+        <v>46.28</v>
       </c>
       <c r="F69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>1.674,00</t>
+          <t>1.685,00</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - MAYO</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+        </is>
+      </c>
       <c r="E70" s="4" t="n">
-        <v>34.53</v>
+        <v>55.23</v>
       </c>
       <c r="F70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>1.673,00</t>
+          <t>1.681,00</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>TAPA POROS HIERRO GALVANIZADO</t>
+          <t>ALQUILER NAVE JUNIO</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>17</v>
+        <v>350</v>
       </c>
       <c r="F71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>1.667,00</t>
+          <t>1.674,00</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>ARANDELAS</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
-        </is>
-      </c>
+          <t>CONECTA 3 - MAYO</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr"/>
       <c r="E72" s="4" t="n">
-        <v>10.8</v>
+        <v>34.53</v>
       </c>
       <c r="F72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>1.654,00</t>
+          <t>1.673,00</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>TAPA POROS HIERRO GALVANIZADO</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>140.21</v>
+        <v>17</v>
       </c>
       <c r="F73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>1.648,00</t>
+          <t>1.667,00</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL MAYO</t>
+          <t>ARANDELAS</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1764.79</v>
+        <v>10.8</v>
       </c>
       <c r="F74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>1.646,00</t>
+          <t>1.654,00</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO LABORAL ABRIL</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr"/>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>PINTURAS IDELLA SL.</t>
+        </is>
+      </c>
       <c r="E75" s="4" t="n">
-        <v>260</v>
+        <v>140.21</v>
       </c>
       <c r="F75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>1.645,00</t>
+          <t>1.648,00</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>MALLA GALLINERO</t>
+          <t>PLENOIL MAYO</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>92.98999999999999</v>
+        <v>1764.79</v>
       </c>
       <c r="F76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1.644,00</t>
+          <t>1.646,00</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>CLORO PISCINA</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO LABORAL ABRIL</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr"/>
       <c r="E77" s="4" t="n">
-        <v>18.79</v>
+        <v>260</v>
       </c>
       <c r="F77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>1.643,00</t>
+          <t>1.645,00</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 623973</t>
+          <t>MALLA GALLINERO</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>313.22</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>1.641,00</t>
+          <t>1.644,00</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>CLORO PISCINA</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>43.87</v>
+        <v>18.79</v>
       </c>
       <c r="F79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>1.640,00</t>
+          <t>1.643,00</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PRESUPUESTO 623973</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>161.32</v>
+        <v>313.22</v>
       </c>
       <c r="F80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>1.639,00</t>
+          <t>1.641,00</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>LA AVENIDA CERAMICAS SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1096.03</v>
+        <v>43.87</v>
       </c>
       <c r="F81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>1.636,00</t>
+          <t>1.640,00</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>86.34999999999999</v>
+        <v>161.32</v>
       </c>
       <c r="F82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>1.634,00</t>
+          <t>1.639,00</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACION</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>EVOTEK FUTURE SL.</t>
+          <t>LA AVENIDA CERAMICAS SL.</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>78.51000000000001</v>
+        <v>1096.03</v>
       </c>
       <c r="F83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>1.631,00</t>
+          <t>1.636,00</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>IVA NO DEDUCIBLE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>ACTION RETAIL SPAIN SL.</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0.86</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="F84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>1.630,00</t>
+          <t>1.634,00</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 622168</t>
+          <t>SERVICIO REPARACION</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>EVOTEK FUTURE SL.</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>3981.68</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="F85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1.629,00</t>
+          <t>1.631,00</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
+          <t>IVA NO DEDUCIBLE</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>ACTION RETAIL SPAIN SL.</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="n">
-        <v>360.15</v>
+        <v>0.86</v>
       </c>
       <c r="F86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>1.628,00</t>
+          <t>1.630,00</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>VENTOSA VIBRADORA</t>
+          <t>PRESUPUESTO 622168</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>DIAMOND-SERVICE PRO TOOLS SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>163.64</v>
+        <v>3981.68</v>
       </c>
       <c r="F87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>1.627,00</t>
+          <t>1.629,00</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>INFLADORA</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
       <c r="E88" s="4" t="n">
-        <v>19.99</v>
+        <v>360.15</v>
       </c>
       <c r="F88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>1.626,00</t>
+          <t>1.628,00</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4093,33 +4085,33 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>ALMODILLA PULIDO DIAMANTE</t>
+          <t>VENTOSA VIBRADORA</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>EASTAR SUPER HARD TOOLS SOCIEDAD LIMITADA.</t>
+          <t>DIAMOND-SERVICE PRO TOOLS SL.</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>40.04</v>
+        <v>163.64</v>
       </c>
       <c r="F89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1.625,00</t>
+          <t>1.627,00</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>GRIFO</t>
+          <t>INFLADORA</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -4128,72 +4120,76 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>117.35</v>
+        <v>19.99</v>
       </c>
       <c r="F90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>1.624,00</t>
+          <t>1.626,00</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>citronela</t>
+          <t>ALMODILLA PULIDO DIAMANTE</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
+          <t>EASTAR SUPER HARD TOOLS SOCIEDAD LIMITADA.</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>6.12</v>
+        <v>40.04</v>
       </c>
       <c r="F91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>1.623,00</t>
+          <t>1.625,00</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>ETIQUETS</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
+          <t>GRIFO</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
+        </is>
+      </c>
       <c r="E92" s="4" t="n">
-        <v>8.26</v>
+        <v>117.35</v>
       </c>
       <c r="F92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>1.622,00</t>
+          <t>1.624,00</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>CANTU acondicionador</t>
+          <t>citronela</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -4202,275 +4198,271 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>4.84</v>
+        <v>6.12</v>
       </c>
       <c r="F93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>1.621,00</t>
+          <t>1.623,00</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>DISPENSADOR AGUA</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
-        </is>
-      </c>
+          <t>ETIQUETS</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr"/>
       <c r="E94" s="4" t="n">
-        <v>8.23</v>
+        <v>8.26</v>
       </c>
       <c r="F94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>1.620,00</t>
+          <t>1.622,00</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>BOMBILLAS</t>
+          <t>CANTU acondicionador</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>AIGOTECH ONSYNK SL</t>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>33.75</v>
+        <v>4.84</v>
       </c>
       <c r="F95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>1.619,00</t>
+          <t>1.621,00</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE MADERA</t>
+          <t>DISPENSADOR AGUA</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>17.97</v>
+        <v>8.23</v>
       </c>
       <c r="F96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>1.618,00</t>
+          <t>1.620,00</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE-FISCAL</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr"/>
+          <t>BOMBILLAS</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>AIGOTECH ONSYNK SL</t>
+        </is>
+      </c>
       <c r="E97" s="4" t="n">
-        <v>360.15</v>
+        <v>33.75</v>
       </c>
       <c r="F97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>1.617,00</t>
+          <t>1.619,00</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>CHALECO</t>
+          <t>SOPORTE MADERA</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>CHINAWIN IBERICA SL</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>70.25</v>
+        <v>17.97</v>
       </c>
       <c r="F98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>1.616,00</t>
+          <t>1.618,00</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>TUBO GOTEO</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>COMERFONSA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE-FISCAL</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr"/>
       <c r="E99" s="4" t="n">
-        <v>70.27</v>
+        <v>360.15</v>
       </c>
       <c r="F99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>1.615,00</t>
+          <t>1.617,00</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>CEMENTO/RESINA</t>
+          <t>CHALECO</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>18.53</v>
+        <v>70.25</v>
       </c>
       <c r="F100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>1.614,00</t>
+          <t>1.616,00</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>TUBO GOTEO</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>47.5</v>
+        <v>70.27</v>
       </c>
       <c r="F101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>1.613,00</t>
+          <t>1.615,00</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>CEMENTO/RESINA</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>17.96</v>
+        <v>18.53</v>
       </c>
       <c r="F102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>1.612,00</t>
+          <t>1.614,00</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>MANGUERA</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>COMERFONSA SL</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>18.99</v>
+        <v>47.5</v>
       </c>
       <c r="F103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>1.611,00</t>
+          <t>1.613,00</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -4484,604 +4476,604 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>69.44</v>
+        <v>17.96</v>
       </c>
       <c r="F104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>1.610,00</t>
+          <t>1.612,00</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>QUITACEMENTO</t>
+          <t>MANGUERA</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>37.96</v>
+        <v>18.99</v>
       </c>
       <c r="F105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>1.602,00</t>
+          <t>1.611,00</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>58.13</v>
+        <v>69.44</v>
       </c>
       <c r="F106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>1.601,00</t>
+          <t>1.610,00</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>QUITACEMENTO</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>22.27</v>
+        <v>37.96</v>
       </c>
       <c r="F107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>1.593,00</t>
+          <t>1.602,00</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>ACTION RETAIL SPAIN SL.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>4.09</v>
+        <v>58.13</v>
       </c>
       <c r="F108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>1.592,00</t>
+          <t>1.601,00</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE MAYO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>350</v>
+        <v>22.27</v>
       </c>
       <c r="F109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>1.591,00</t>
+          <t>1.593,00</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>AGUA 2026/02</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
+          <t>ACTION RETAIL SPAIN SL.</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>30.65</v>
+        <v>4.09</v>
       </c>
       <c r="F110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>1.587,00</t>
+          <t>1.592,00</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>CAMBIO NOMBRE RENAULT MEGANE SCENIC</t>
+          <t>ALQUILER NAVE MAYO</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>ACCIONGEST ASEGEST SLP.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>190.16</v>
+        <v>350</v>
       </c>
       <c r="F111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>1.583,00</t>
+          <t>1.591,00</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>AGUA 2026/02</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>68.20999999999999</v>
+        <v>30.65</v>
       </c>
       <c r="F112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>1.582,00</t>
+          <t>1.587,00</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>CAMBIO NOMBRE RENAULT MEGANE SCENIC</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>ACCIONGEST ASEGEST SLP.</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>49.92</v>
+        <v>190.16</v>
       </c>
       <c r="F113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>1.579,00</t>
+          <t>1.583,00</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>16.36</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>1.578,00</t>
+          <t>1.582,00</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>GLEM S.L.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>17.2</v>
+        <v>49.92</v>
       </c>
       <c r="F115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>1.576,00</t>
+          <t>1.579,00</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>FIANZA AHOYADORA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>247.93</v>
+        <v>16.36</v>
       </c>
       <c r="F116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>1.574,00</t>
+          <t>1.578,00</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>DISTRIBUCION QING YONG SL</t>
+          <t>GLEM S.L.</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="F117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>1.573,00</t>
+          <t>1.576,00</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL PRUEBA</t>
+          <t>FIANZA AHOYADORA</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>CHINAWIN IBERICA SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>59.5</v>
+        <v>247.93</v>
       </c>
       <c r="F118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>1.570,00</t>
+          <t>1.574,00</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>HOLDED MARZO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>59</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>1.569,00</t>
+          <t>1.573,00</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>HOLDED ABRIL</t>
+          <t>ROPA LABORAL PRUEBA</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="F120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>1.568,00</t>
+          <t>1.570,00</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL ABRIL</t>
+          <t>HOLDED MARZO</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>23.93</v>
+        <v>59</v>
       </c>
       <c r="F121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>1.567,00</t>
+          <t>1.569,00</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - MAYO</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr"/>
+          <t>HOLDED ABRIL</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>HOLDED TECHNOLOGIES SL.</t>
+        </is>
+      </c>
       <c r="E122" s="4" t="n">
-        <v>34.68</v>
+        <v>59</v>
       </c>
       <c r="F122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>1.566,00</t>
+          <t>1.568,00</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
+          <t>JAZZTEL ABRIL</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Mª CARMEN PRIETO AVELLAN</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>65</v>
+        <v>23.93</v>
       </c>
       <c r="F123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>1.565,00</t>
+          <t>1.567,00</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>NATURGY ABRIL</t>
+          <t>CONECTA 3 - MAYO</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr"/>
       <c r="E124" s="4" t="n">
-        <v>23.6</v>
+        <v>34.68</v>
       </c>
       <c r="F124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>1.564,00</t>
+          <t>1.566,00</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>BEBIDA OBRA</t>
+          <t>ROPA LABORAL</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>Mª CARMEN PRIETO AVELLAN</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>61.8</v>
+        <v>65</v>
       </c>
       <c r="F125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>1.544,00</t>
+          <t>1.565,00</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>EUROBAMAS SL</t>
-        </is>
-      </c>
+          <t>NATURGY ABRIL</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="4" t="n">
-        <v>57.85</v>
+        <v>23.6</v>
       </c>
       <c r="F126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>1.543,00</t>
+          <t>1.564,00</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>BEBIDA OBRA</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>33.73</v>
+        <v>61.8</v>
       </c>
       <c r="F127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>1.542,00</t>
+          <t>1.544,00</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
@@ -5091,101 +5083,101 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>89.83</v>
+        <v>57.85</v>
       </c>
       <c r="F128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>1.540,00</t>
+          <t>1.543,00</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>RADIAL ANGULAR</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>WURTH ESPAÑA SA</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>511.2</v>
+        <v>33.73</v>
       </c>
       <c r="F129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>1.535,00</t>
+          <t>1.542,00</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>76.16</v>
+        <v>89.83</v>
       </c>
       <c r="F130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>1.523,00</t>
+          <t>1.540,00</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>COMPRA IKEA</t>
+          <t>RADIAL ANGULAR</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>IKEA IBERICA SAU</t>
+          <t>WURTH ESPAÑA SA</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.03</v>
+        <v>511.2</v>
       </c>
       <c r="F131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>1.517,00</t>
+          <t>1.535,00</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
@@ -5195,175 +5187,179 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL ABRIL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>1729.15</v>
+        <v>76.16</v>
       </c>
       <c r="F132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>1.516,00</t>
+          <t>1.523,00</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE ABRIL</t>
+          <t>COMPRA IKEA</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>IKEA IBERICA SAU</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>350</v>
+        <v>52.03</v>
       </c>
       <c r="F133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>1.515,00</t>
+          <t>1.517,00</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
+          <t>PLENOIL ABRIL</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Mª CARMEN PRIETO AVELLAN</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>833.5</v>
+        <v>1729.15</v>
       </c>
       <c r="F134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>1.514,00</t>
+          <t>1.516,00</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>COMPRAVENTA PARTICIPACIONES SOCIALES</t>
+          <t>ALQUILER NAVE ABRIL</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>ALEJANDRO PEREZ MARTINEZ</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>381.09</v>
+        <v>350</v>
       </c>
       <c r="F135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>1.513,00</t>
+          <t>1.515,00</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>REGISTRO MERCANTIL COMPRA EMPRESA</t>
+          <t>ROPA LABORAL</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>REGISTRO MERCANTIL DE ALICANTE, S.C.</t>
+          <t>Mª CARMEN PRIETO AVELLAN</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>97.81</v>
+        <v>833.5</v>
       </c>
       <c r="F136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>1.512,00</t>
+          <t>1.514,00</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>PUBLICACION BORME</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr"/>
+          <t>COMPRAVENTA PARTICIPACIONES SOCIALES</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>ALEJANDRO PEREZ MARTINEZ</t>
+        </is>
+      </c>
       <c r="E137" s="4" t="n">
-        <v>28.72</v>
+        <v>381.09</v>
       </c>
       <c r="F137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>1.511,00</t>
+          <t>1.513,00</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>COMPRA AMAZON</t>
+          <t>REGISTRO MERCANTIL COMPRA EMPRESA</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>REGISTRO MERCANTIL DE ALICANTE, S.C.</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>80.08</v>
+        <v>97.81</v>
       </c>
       <c r="F138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>1.507,00</t>
+          <t>1.512,00</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -5373,54 +5369,50 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>EUROBAMAS SL</t>
-        </is>
-      </c>
+          <t>PUBLICACION BORME</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr"/>
       <c r="E139" s="4" t="n">
-        <v>60.33</v>
+        <v>28.72</v>
       </c>
       <c r="F139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>1.506,00</t>
+          <t>1.511,00</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>COMPRA AMAZON</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>45.83</v>
+        <v>80.08</v>
       </c>
       <c r="F140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>1.503,00</t>
+          <t>1.507,00</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -5430,23 +5422,23 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>NOVELDIESEL SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>87.26000000000001</v>
+        <v>60.33</v>
       </c>
       <c r="F141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>1.502,00</t>
+          <t>1.506,00</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -5456,275 +5448,279 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>45.83</v>
       </c>
       <c r="F142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>1.501,00</t>
+          <t>1.503,00</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>DIGI MARZO-ABRIL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>NOVELDIESEL SL</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>6.45</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="F143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>1.498,00</t>
+          <t>1.502,00</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>FONTANERO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO REYES PACHECO</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>195</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>1.497,00</t>
+          <t>1.501,00</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>HONORARIOS</t>
+          <t>DIGI MARZO-ABRIL</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>INMOCEYLAN SL.</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>4000</v>
+        <v>6.45</v>
       </c>
       <c r="F145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>1.496,00</t>
+          <t>1.498,00</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>NATURGY MARZO</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
+          <t>FONTANERO</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>JOSE ANTONIO REYES PACHECO</t>
+        </is>
+      </c>
       <c r="E146" s="4" t="n">
-        <v>51.16</v>
+        <v>195</v>
       </c>
       <c r="F146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>1.495,00</t>
+          <t>1.497,00</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>HONORARIOS</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>INMOCEYLAN SL.</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>26.36</v>
+        <v>4000</v>
       </c>
       <c r="F147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>1.493,00</t>
+          <t>1.496,00</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>COMPRA VENTILADORES</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>INDEPSALE TECHNOLOGY LIMITED</t>
-        </is>
-      </c>
+          <t>NATURGY MARZO</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="4" t="n">
-        <v>564.22</v>
+        <v>51.16</v>
       </c>
       <c r="F148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>1.280,00</t>
+          <t>1.495,00</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>DISCO DIAMANTE MINI</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>WURTH ESPAÑA SA</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>170.4</v>
+        <v>26.36</v>
       </c>
       <c r="F149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>1.274,00</t>
+          <t>1.493,00</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL MARZ</t>
+          <t>COMPRA VENTILADORES</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>INDEPSALE TECHNOLOGY LIMITED</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>31.66</v>
+        <v>564.22</v>
       </c>
       <c r="F150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>1.271,00</t>
+          <t>1.280,00</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>DISCO DIAMANTE MINI</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>WURTH ESPAÑA SA</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>69.08</v>
+        <v>170.4</v>
       </c>
       <c r="F151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>1.270,00</t>
+          <t>1.274,00</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 MARZO</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
+          <t>JAZZTEL MARZ</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>ORANGE ESPAGNE SAU.</t>
+        </is>
+      </c>
       <c r="E152" s="4" t="n">
-        <v>44.66</v>
+        <v>31.66</v>
       </c>
       <c r="F152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>1.264,00</t>
+          <t>1.271,00</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -5734,96 +5730,92 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>72.34</v>
+        <v>69.08</v>
       </c>
       <c r="F153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>1.257,00</t>
+          <t>1.270,00</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
-        </is>
-      </c>
+          <t>CONECTA 3 MARZO</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="4" t="n">
-        <v>75.8</v>
+        <v>44.66</v>
       </c>
       <c r="F154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>1.255,00</t>
+          <t>1.264,00</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL MARZO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1557.38</v>
+        <v>72.34</v>
       </c>
       <c r="F155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>1.254,00</t>
+          <t>1.257,00</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>480</v>
+        <v>75.8</v>
       </c>
       <c r="F156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>1.245,00</t>
+          <t>1.255,00</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -5833,310 +5825,310 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO LABORAL MARZO</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr"/>
+          <t>PLENOIL MARZO</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>PLENOIL SL.</t>
+        </is>
+      </c>
       <c r="E157" s="4" t="n">
-        <v>260</v>
+        <v>1557.38</v>
       </c>
       <c r="F157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>1.237,00</t>
+          <t>1.254,00</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>DISTRIBUCION QING YONG SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>16.86</v>
+        <v>480</v>
       </c>
       <c r="F158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>1.236,00</t>
+          <t>1.245,00</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>MAGUERA Y ADAPTADORES</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>COMERFONSA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO LABORAL MARZO</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr"/>
       <c r="E159" s="4" t="n">
-        <v>74.18000000000001</v>
+        <v>260</v>
       </c>
       <c r="F159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>1.235,00</t>
+          <t>1.237,00</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>56.86</v>
+        <v>16.86</v>
       </c>
       <c r="F160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>1.233,00</t>
+          <t>1.236,00</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MAGUERA Y ADAPTADORES</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>MOEVE RETAIL OPERATIONS S.A.U.</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>17.65</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="F161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>1.232,00</t>
+          <t>1.235,00</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>MARCO  + TAPADERA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>SALTOKI ELCHE SL.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>-70.06999999999999</v>
+        <v>56.86</v>
       </c>
       <c r="F162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>1.230,00</t>
+          <t>1.233,00</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>MARCO  + TAPADERA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>SALTOKI ELCHE SL.</t>
+          <t>MOEVE RETAIL OPERATIONS S.A.U.</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>17.65</v>
       </c>
       <c r="F163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>1.228,00</t>
+          <t>1.232,00</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MARCO  + TAPADERA</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>SALTOKI ELCHE SL.</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>76.92</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="F164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>1.227,00</t>
+          <t>1.230,00</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>PALA PLUS MARTILLO</t>
+          <t>MARCO  + TAPADERA</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>SALTOKI ELCHE SL.</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>14.04</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>1.226,00</t>
+          <t>1.228,00</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>PARKING CANALEJAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>PARKING 3000 SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>6.28</v>
+        <v>76.92</v>
       </c>
       <c r="F166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>1.225,00</t>
+          <t>1.227,00</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PALA PLUS MARTILLO</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>17.5</v>
+        <v>14.04</v>
       </c>
       <c r="F167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>1.222,00</t>
+          <t>1.226,00</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PARKING CANALEJAS</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>PARKING 3000 SL</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>60</v>
+        <v>6.28</v>
       </c>
       <c r="F168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>1.219,00</t>
+          <t>1.225,00</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -6146,127 +6138,127 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="F169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>1.218,00</t>
+          <t>1.222,00</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>FINA LIFANTE FLORES</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>11.24</v>
+        <v>60</v>
       </c>
       <c r="F170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>1.199,00</t>
+          <t>1.219,00</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>DISTRIBUCION QING YONG SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>11.49</v>
+        <v>60</v>
       </c>
       <c r="F171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>1.198,00</t>
+          <t>1.218,00</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>FINA LIFANTE FLORES</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>61.98</v>
+        <v>11.24</v>
       </c>
       <c r="F172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>1.197,00</t>
+          <t>1.199,00</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>24.79</v>
+        <v>11.49</v>
       </c>
       <c r="F173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>1.196,00</t>
+          <t>1.198,00</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -6280,66 +6272,66 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>118.53</v>
+        <v>61.98</v>
       </c>
       <c r="F174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>1.195,00</t>
+          <t>1.197,00</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>PARKING CANALEJAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>PARKING 3000 SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>12.6</v>
+        <v>24.79</v>
       </c>
       <c r="F175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>1.194,00</t>
+          <t>1.196,00</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>PARKING CANALEJAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>PARKING 3000 SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>12.69</v>
+        <v>118.53</v>
       </c>
       <c r="F176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>1.193,00</t>
+          <t>1.195,00</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -6358,14 +6350,14 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>11.94</v>
+        <v>12.6</v>
       </c>
       <c r="F177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>1.192,00</t>
+          <t>1.194,00</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
@@ -6384,14 +6376,14 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>12.4</v>
+        <v>12.69</v>
       </c>
       <c r="F178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>1.191,00</t>
+          <t>1.193,00</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -6410,14 +6402,14 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>8.6</v>
+        <v>11.94</v>
       </c>
       <c r="F179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>1.190,00</t>
+          <t>1.192,00</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
@@ -6436,241 +6428,245 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>12.19</v>
+        <v>12.4</v>
       </c>
       <c r="F180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>1.189,00</t>
+          <t>1.191,00</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PARKING CANALEJAS</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>PARKING 3000 SL</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="F181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>1.187,00</t>
+          <t>1.190,00</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>RESPOSTAJE</t>
+          <t>PARKING CANALEJAS</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
+          <t>PARKING 3000 SL</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>12.4</v>
+        <v>12.19</v>
       </c>
       <c r="F182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>1.184,00</t>
+          <t>1.189,00</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>REPOSATAJE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>74.38</v>
+        <v>55</v>
       </c>
       <c r="F183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>1.181,00</t>
+          <t>1.187,00</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>RESPOSTAJE</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>60.17</v>
+        <v>12.4</v>
       </c>
       <c r="F184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>1.171,00</t>
+          <t>1.184,00</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr"/>
+          <t>REPOSATAJE</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>EUROBAMAS SL</t>
+        </is>
+      </c>
       <c r="E185" s="4" t="n">
-        <v>360.15</v>
+        <v>74.38</v>
       </c>
       <c r="F185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>1.170,00</t>
+          <t>1.181,00</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>EUROBAMAS SL</t>
+        </is>
+      </c>
       <c r="E186" s="4" t="n">
-        <v>360.15</v>
+        <v>60.17</v>
       </c>
       <c r="F186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>1.166,00</t>
+          <t>1.171,00</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>MANGUERA RIEGO</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t>COMERFONSA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr"/>
       <c r="E187" s="4" t="n">
-        <v>142.11</v>
+        <v>360.15</v>
       </c>
       <c r="F187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>1.156,00</t>
+          <t>1.170,00</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr"/>
       <c r="E188" s="4" t="n">
-        <v>2.02</v>
+        <v>360.15</v>
       </c>
       <c r="F188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>1.147,00</t>
+          <t>1.166,00</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL FEBRERO</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr"/>
+          <t>MANGUERA RIEGO</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>COMERFONSA SL</t>
+        </is>
+      </c>
       <c r="E189" s="4" t="n">
-        <v>260</v>
+        <v>142.11</v>
       </c>
       <c r="F189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>1.146,00</t>
+          <t>1.156,00</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -6680,471 +6676,467 @@
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>21.82</v>
+        <v>2.02</v>
       </c>
       <c r="F190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>1.145,00</t>
+          <t>1.147,00</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>PUERTA RELLENABLE GALVANIZADA</t>
-        </is>
-      </c>
-      <c r="D191" s="6" t="inlineStr">
-        <is>
-          <t>TOSANTO SL</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL FEBRERO</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr"/>
       <c r="E191" s="4" t="n">
-        <v>105.08</v>
+        <v>260</v>
       </c>
       <c r="F191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>1.144,00</t>
+          <t>1.146,00</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>PUERTA RELLENABLE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>TOSANTO SL</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>179.87</v>
+        <v>21.82</v>
       </c>
       <c r="F192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>1.143,00</t>
+          <t>1.145,00</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>NATURGY FEBRERO</t>
-        </is>
-      </c>
-      <c r="D193" s="6" t="inlineStr"/>
+          <t>PUERTA RELLENABLE GALVANIZADA</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>TOSANTO SL</t>
+        </is>
+      </c>
       <c r="E193" s="4" t="n">
-        <v>40.54</v>
+        <v>105.08</v>
       </c>
       <c r="F193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>1.142,00</t>
+          <t>1.144,00</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PUERTA RELLENABLE</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>VECTALIA OIL SL.</t>
+          <t>TOSANTO SL</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>26.37</v>
+        <v>179.87</v>
       </c>
       <c r="F194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>1.139,00</t>
+          <t>1.143,00</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>08/03/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
-        <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
-        </is>
-      </c>
+          <t>NATURGY FEBRERO</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr"/>
       <c r="E195" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>40.54</v>
       </c>
       <c r="F195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>1.138,00</t>
+          <t>1.142,00</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>CABALLETES TRABAJAO TELESCOPICOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>TOSANTO SL</t>
+          <t>VECTALIA OIL SL.</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>328.1</v>
+        <v>26.37</v>
       </c>
       <c r="F196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>1.133,00</t>
+          <t>1.139,00</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>08/03/2026</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>CAPAZOS</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>28.51</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>1.128,00</t>
+          <t>1.138,00</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>VIA T ENERO</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr"/>
+          <t>CABALLETES TRABAJAO TELESCOPICOS</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>TOSANTO SL</t>
+        </is>
+      </c>
       <c r="E198" s="4" t="n">
-        <v>10.81</v>
+        <v>328.1</v>
       </c>
       <c r="F198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>1.127,00</t>
+          <t>1.133,00</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>VIA T FEBRERO</t>
-        </is>
-      </c>
-      <c r="D199" s="6" t="inlineStr"/>
+          <t>CAPAZOS</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>BRICOLAJE BRICOMAN SLU</t>
+        </is>
+      </c>
       <c r="E199" s="4" t="n">
-        <v>32.52</v>
+        <v>28.51</v>
       </c>
       <c r="F199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>1.126,00</t>
+          <t>1.128,00</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>21/02/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>HOLDED FEBRERO</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
-        </is>
-      </c>
+          <t>VIA T ENERO</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr"/>
       <c r="E200" s="4" t="n">
-        <v>59</v>
+        <v>10.81</v>
       </c>
       <c r="F200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>1.125,00</t>
+          <t>1.127,00</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>VIA T MARZO</t>
+          <t>VIA T FEBRERO</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr"/>
       <c r="E201" s="4" t="n">
-        <v>9.42</v>
+        <v>32.52</v>
       </c>
       <c r="F201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>1.124,00</t>
+          <t>1.126,00</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>21/02/2026</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE MARZO</t>
+          <t>HOLDED FEBRERO</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>350</v>
+        <v>59</v>
       </c>
       <c r="F202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>1.123,00</t>
+          <t>1.125,00</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>GASOLINA FEBRERO</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="inlineStr">
-        <is>
-          <t>PLENOIL SL.</t>
-        </is>
-      </c>
+          <t>VIA T MARZO</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr"/>
       <c r="E203" s="4" t="n">
-        <v>1017.62</v>
+        <v>9.42</v>
       </c>
       <c r="F203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>1.122,00</t>
+          <t>1.124,00</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL FEBRERO</t>
+          <t>ALQUILER NAVE MARZO</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>41.28</v>
+        <v>350</v>
       </c>
       <c r="F204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>1.120,00</t>
+          <t>1.123,00</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>IGUALA ENERO</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr"/>
+          <t>GASOLINA FEBRERO</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>PLENOIL SL.</t>
+        </is>
+      </c>
       <c r="E205" s="4" t="n">
-        <v>360.15</v>
+        <v>1017.62</v>
       </c>
       <c r="F205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>1.107,00</t>
+          <t>1.122,00</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>JAZZTEL FEBRERO</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>33.06</v>
+        <v>41.28</v>
       </c>
       <c r="F206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>1.106,00</t>
+          <t>1.120,00</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D207" s="6" t="inlineStr">
-        <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
-        </is>
-      </c>
+          <t>IGUALA ENERO</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr"/>
       <c r="E207" s="4" t="n">
-        <v>16.53</v>
+        <v>360.15</v>
       </c>
       <c r="F207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>1.104,00</t>
+          <t>1.107,00</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>ROSALIA MARTINEZ RUIZ</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>13.84</v>
+        <v>33.06</v>
       </c>
       <c r="F208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>1.101,00</t>
+          <t>1.106,00</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -7154,231 +7146,231 @@
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>19.79</v>
+        <v>16.53</v>
       </c>
       <c r="F209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>1.094,00</t>
+          <t>1.104,00</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>PROLONGADOR 50M IP55</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ROSALIA MARTINEZ RUIZ</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>1203.5</v>
+        <v>13.84</v>
       </c>
       <c r="F210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>1.093,00</t>
+          <t>1.101,00</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>GENERADOR MOTOR HONDA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1430</v>
+        <v>19.79</v>
       </c>
       <c r="F211" s="6" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>1.092,00</t>
+          <t>1.094,00</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PROLONGADOR 50M IP55</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>15.48</v>
+        <v>1203.5</v>
       </c>
       <c r="F212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>1.091,00</t>
+          <t>1.093,00</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>NATURGY ENERO</t>
+          <t>GENERADOR MOTOR HONDA</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>48.52</v>
+        <v>1430</v>
       </c>
       <c r="F213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>1.090,00</t>
+          <t>1.092,00</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL ENERO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>41.28</v>
+        <v>15.48</v>
       </c>
       <c r="F214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>1.089,00</t>
+          <t>1.091,00</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>GUANTES TRABAJO</t>
+          <t>NATURGY ENERO</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>120</v>
+        <v>48.52</v>
       </c>
       <c r="F215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>1.088,00</t>
+          <t>1.090,00</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>JAZZTEL ENERO</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>61.99</v>
+        <v>41.28</v>
       </c>
       <c r="F216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>1.087,00</t>
+          <t>1.089,00</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>ON BOARGING BILLD IN</t>
+          <t>GUANTES TRABAJO</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>SIDE QUEST APES, S.L.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="F217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>1.086,00</t>
+          <t>1.088,00</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
@@ -7388,642 +7380,642 @@
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>19.26</v>
+        <v>61.99</v>
       </c>
       <c r="F218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>1.085,00</t>
+          <t>1.087,00</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>CHAQUETAS LABORAL</t>
+          <t>ON BOARGING BILLD IN</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>INDICATIVO SL</t>
+          <t>SIDE QUEST APES, S.L.</t>
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>430</v>
+        <v>1200</v>
       </c>
       <c r="F219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>1.084,00</t>
+          <t>1.086,00</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE FEBRERO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>350</v>
+        <v>19.26</v>
       </c>
       <c r="F220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>1.083,00</t>
+          <t>1.085,00</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>CHAQUETAS LABORAL</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>INDICATIVO SL</t>
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>74.38</v>
+        <v>430</v>
       </c>
       <c r="F221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>1.082,00</t>
+          <t>1.084,00</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ALQUILER NAVE FEBRERO</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>37.19</v>
+        <v>350</v>
       </c>
       <c r="F222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>1.081,00</t>
+          <t>1.083,00</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>ROLLO HILO DE ALAMBRE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>300</v>
+        <v>74.38</v>
       </c>
       <c r="F223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>1.080,00</t>
+          <t>1.082,00</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>GUANTE SOLDADOR / MASCARILLA / SOPLETE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS INDUSTRIALES FARELL SA</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>160.74</v>
+        <v>37.19</v>
       </c>
       <c r="F224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>1.078,00</t>
+          <t>1.081,00</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ROLLO HILO DE ALAMBRE</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>13.18</v>
+        <v>300</v>
       </c>
       <c r="F225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>1.077,00</t>
+          <t>1.080,00</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>GUANTE SOLDADOR / MASCARILLA / SOPLETE</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>REATA ESTACIONES SL.</t>
+          <t>SUMINISTROS INDUSTRIALES FARELL SA</t>
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>29.38</v>
+        <v>160.74</v>
       </c>
       <c r="F226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>1.076,00</t>
+          <t>1.078,00</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>ALARGADERA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>51.24</v>
+        <v>13.18</v>
       </c>
       <c r="F227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>1.075,00</t>
+          <t>1.077,00</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>PROLONGADOR 50M IP55</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>REATA ESTACIONES SL.</t>
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>234</v>
+        <v>29.38</v>
       </c>
       <c r="F228" s="6" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>1.074,00</t>
+          <t>1.076,00</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>ALARGADERA</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>JYSK DBL IBERIA SLU</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>44.86</v>
+        <v>51.24</v>
       </c>
       <c r="F229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>1.073,00</t>
+          <t>1.075,00</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PROLONGADOR 50M IP55</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>CONCORDY SA</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>56.07</v>
+        <v>234</v>
       </c>
       <c r="F230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>1.072,00</t>
+          <t>1.074,00</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>PEGATINAS VALLAS</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>INDICATIVO SL</t>
+          <t>JYSK DBL IBERIA SLU</t>
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>200</v>
+        <v>44.86</v>
       </c>
       <c r="F231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>1.071,00</t>
+          <t>1.073,00</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>DIGI ENERO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>CONCORDY SA</t>
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>9.09</v>
+        <v>56.07</v>
       </c>
       <c r="F232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>1.070,00</t>
+          <t>1.072,00</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>NATURGY DICIEMBRE</t>
+          <t>PEGATINAS VALLAS</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>INDICATIVO SL</t>
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>32.89</v>
+        <v>200</v>
       </c>
       <c r="F233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>1.069,00</t>
+          <t>1.071,00</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>MAQUINA STHILL</t>
+          <t>DIGI ENERO</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>MARHUENDA IMPORTACIONES SL</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>1716.53</v>
+        <v>9.09</v>
       </c>
       <c r="F234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>1.068,00</t>
+          <t>1.070,00</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>CALZADO LABORAL</t>
+          <t>NATURGY DICIEMBRE</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>119.09</v>
+        <v>32.89</v>
       </c>
       <c r="F235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>1.067,00</t>
+          <t>1.069,00</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MAQUINA STHILL</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>MARHUENDA IMPORTACIONES SL</t>
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>16.94</v>
+        <v>1716.53</v>
       </c>
       <c r="F236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>1.064,00</t>
+          <t>1.068,00</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL DICIEMBRE</t>
+          <t>CALZADO LABORAL</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>73.02</v>
+        <v>119.09</v>
       </c>
       <c r="F237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1.067,00</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>NATURGY AGOSTO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>19.68</v>
+        <v>16.94</v>
       </c>
       <c r="F238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1.064,00</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL ENERO</t>
+          <t>JAZZTEL DICIEMBRE</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1109.93</v>
+        <v>73.02</v>
       </c>
       <c r="F239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>950</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>AGUA ENERO</t>
+          <t>NATURGY AGOSTO</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>31.33</v>
+        <v>19.68</v>
       </c>
       <c r="F240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>928</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>SELLO FACTURAS</t>
+          <t>PLENOIL ENERO</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>ENDLESS SYSTEMS SLU</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>26.45</v>
+        <v>1109.93</v>
       </c>
       <c r="F241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>927</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>ROLLO ALAMBRE</t>
+          <t>AGUA ENERO</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>1000</v>
+        <v>31.33</v>
       </c>
       <c r="F242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>926</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -8033,227 +8025,227 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>SELLO FACTURAS</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ENDLESS SYSTEMS SLU</t>
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>389.7</v>
+        <v>26.45</v>
       </c>
       <c r="F243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>925</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL ENERO</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr"/>
+          <t>ROLLO ALAMBRE</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+        </is>
+      </c>
       <c r="E244" s="4" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="F244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>924</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE ENERO</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>350</v>
+        <v>389.7</v>
       </c>
       <c r="F245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>922</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D246" s="6" t="inlineStr">
-        <is>
-          <t>JR VIDAL RICO SL</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL ENERO</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr"/>
       <c r="E246" s="4" t="n">
-        <v>59.66</v>
+        <v>260</v>
       </c>
       <c r="F246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>917</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ALQUILER NAVE ENERO</t>
         </is>
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>E.E. CAÑIZARES, CB</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>74.38</v>
+        <v>350</v>
       </c>
       <c r="F247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>906</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>GUANTES</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>JR VIDAL RICO SL</t>
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>7.25</v>
+        <v>59.66</v>
       </c>
       <c r="F248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>890</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>E.E. CAÑIZARES, CB</t>
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>321.37</v>
+        <v>74.38</v>
       </c>
       <c r="F249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>888</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>GUANTES</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>24.9</v>
+        <v>7.25</v>
       </c>
       <c r="F250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>887</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>63.79</v>
+        <v>321.37</v>
       </c>
       <c r="F251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>886</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
@@ -8263,101 +8255,101 @@
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>MASCARILLAS / CALDERETA / NIVEL ASER</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>976.7</v>
+        <v>24.9</v>
       </c>
       <c r="F252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>885</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>15/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>BARNIZ</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>7.34</v>
+        <v>63.79</v>
       </c>
       <c r="F253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>878</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>DIGI FEBRERO</t>
+          <t>MASCARILLAS / CALDERETA / NIVEL ASER</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>9.09</v>
+        <v>976.7</v>
       </c>
       <c r="F254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>873</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>15/02/2026</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>CAPAZO / BORRIQUETA / TAPA CONTADOR</t>
+          <t>BARNIZ</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>143.47</v>
+        <v>7.34</v>
       </c>
       <c r="F255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>872</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
@@ -8367,75 +8359,75 @@
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>ESPATULA</t>
+          <t>DIGI FEBRERO</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>54.51</v>
+        <v>9.09</v>
       </c>
       <c r="F256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>871</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL VARIO</t>
+          <t>CAPAZO / BORRIQUETA / TAPA CONTADOR</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>44.67</v>
+        <v>143.47</v>
       </c>
       <c r="F257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>870</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
-          <t>TALADRO ATORNILLADOR</t>
+          <t>ESPATULA</t>
         </is>
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>57.85</v>
+        <v>54.51</v>
       </c>
       <c r="F258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -8445,85 +8437,137 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL VARIO</t>
         </is>
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>107.46</v>
+        <v>44.67</v>
       </c>
       <c r="F259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>863</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
-          <t>DISCO DE CORTE</t>
+          <t>TALADRO ATORNILLADOR</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA-VISTA ALEGRE SL</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>8.26</v>
+        <v>57.85</v>
       </c>
       <c r="F260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D261" s="6" t="inlineStr">
+        <is>
+          <t>E.S. PINOSO S.L.</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="F261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>DISCO DE CORTE</t>
+        </is>
+      </c>
+      <c r="D262" s="6" t="inlineStr">
+        <is>
+          <t>FERRETERIA-VISTA ALEGRE SL</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="F262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
           <t>826</t>
         </is>
       </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="C261" s="6" t="inlineStr">
+      <c r="C263" s="6" t="inlineStr">
         <is>
           <t>HOLDED ENERO</t>
         </is>
       </c>
-      <c r="D261" s="6" t="inlineStr">
+      <c r="D263" s="6" t="inlineStr">
         <is>
           <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
-      <c r="E261" s="4" t="n">
+      <c r="E263" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="F261" s="6" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="7" t="n"/>
-      <c r="B262" s="7" t="n"/>
-      <c r="C262" s="7" t="inlineStr">
+      <c r="F263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="7" t="n"/>
+      <c r="B264" s="7" t="n"/>
+      <c r="C264" s="7" t="inlineStr">
         <is>
           <t>TOTAL GASTOS GENERALES</t>
         </is>
       </c>
-      <c r="D262" s="7" t="n"/>
-      <c r="E262" s="8">
-        <f>SUM(E4:E261)</f>
-        <v/>
-      </c>
-      <c r="F262" s="7" t="n"/>
+      <c r="D264" s="7" t="n"/>
+      <c r="E264" s="8">
+        <f>SUM(E4:E263)</f>
+        <v/>
+      </c>
+      <c r="F264" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -25748,7 +25792,7 @@
       </c>
       <c r="F456" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G456" s="4" t="n">
@@ -26864,7 +26908,7 @@
       </c>
       <c r="F488" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G488" s="4" t="n">
@@ -26899,7 +26943,7 @@
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G489" s="4" t="n">
@@ -26934,7 +26978,7 @@
       </c>
       <c r="F490" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G490" s="4" t="n">
@@ -26969,7 +27013,7 @@
       </c>
       <c r="F491" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G491" s="4" t="n">
@@ -27004,7 +27048,7 @@
       </c>
       <c r="F492" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G492" s="4" t="n">
@@ -27039,7 +27083,7 @@
       </c>
       <c r="F493" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G493" s="4" t="n">
@@ -27074,7 +27118,7 @@
       </c>
       <c r="F494" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G494" s="4" t="n">
@@ -27109,7 +27153,7 @@
       </c>
       <c r="F495" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G495" s="4" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'Certificaciones'!C24</f>
+        <f>'Certificaciones'!C26</f>
         <v/>
       </c>
     </row>
@@ -1387,41 +1387,117 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6">
+        <f>'Certificaciones'!B24</f>
+        <v/>
+      </c>
+      <c r="B32" s="4">
+        <f>'Certificaciones'!C24</f>
+        <v/>
+      </c>
+      <c r="C32" s="6">
+        <f>'Certificaciones'!D24</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>C32*$B$7</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A32,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A32,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>D32+E32+F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="4">
+        <f>B32-G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="6">
+        <f>IF(B32=0,0,G32/B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6">
+        <f>'Certificaciones'!B25</f>
+        <v/>
+      </c>
+      <c r="B33" s="4">
+        <f>'Certificaciones'!C25</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>'Certificaciones'!D25</f>
+        <v/>
+      </c>
+      <c r="D33" s="4">
+        <f>C33*$B$7</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A33,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F33" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A33,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G33" s="4">
+        <f>D33+E33+F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="4">
+        <f>B33-G33</f>
+        <v/>
+      </c>
+      <c r="I33" s="6">
+        <f>IF(B33=0,0,G33/B33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B32" s="8">
-        <f>SUM(B12:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="7">
-        <f>SUM(C12:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D12:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="8">
-        <f>SUM(E12:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>SUM(F12:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="8">
-        <f>SUM(G12:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="8">
-        <f>SUM(H12:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="7">
-        <f>IF(B32=0,0,G32/B32)</f>
+      <c r="B34" s="8">
+        <f>SUM(B12:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="7">
+        <f>SUM(C12:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="8">
+        <f>SUM(D12:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="8">
+        <f>SUM(E12:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="8">
+        <f>SUM(F12:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="8">
+        <f>SUM(G12:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="8">
+        <f>SUM(H12:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="7">
+        <f>IF(B34=0,0,G34/B34)</f>
         <v/>
       </c>
     </row>
@@ -1440,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1497,7 +1573,7 @@
         <v>8875.66</v>
       </c>
       <c r="D4" s="6">
-        <f>C4/C24</f>
+        <f>C4/C26</f>
         <v/>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
@@ -1515,7 +1591,7 @@
         <v>23917.62</v>
       </c>
       <c r="D5" s="6">
-        <f>C5/C24</f>
+        <f>C5/C26</f>
         <v/>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
@@ -1533,7 +1609,7 @@
         <v>46635.25</v>
       </c>
       <c r="D6" s="6">
-        <f>C6/C24</f>
+        <f>C6/C26</f>
         <v/>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
@@ -1551,7 +1627,7 @@
         <v>105543.77</v>
       </c>
       <c r="D7" s="6">
-        <f>C7/C24</f>
+        <f>C7/C26</f>
         <v/>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -1569,7 +1645,7 @@
         <v>173193.43</v>
       </c>
       <c r="D8" s="6">
-        <f>C8/C24</f>
+        <f>C8/C26</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -1587,7 +1663,7 @@
         <v>63277.34</v>
       </c>
       <c r="D9" s="6">
-        <f>C9/C24</f>
+        <f>C9/C26</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -1605,7 +1681,7 @@
         <v>3288</v>
       </c>
       <c r="D10" s="6">
-        <f>C10/C24</f>
+        <f>C10/C26</f>
         <v/>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -1623,7 +1699,7 @@
         <v>16241.92</v>
       </c>
       <c r="D11" s="6">
-        <f>C11/C24</f>
+        <f>C11/C26</f>
         <v/>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -1641,7 +1717,7 @@
         <v>116432.26</v>
       </c>
       <c r="D12" s="6">
-        <f>C12/C24</f>
+        <f>C12/C26</f>
         <v/>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -1659,7 +1735,7 @@
         <v>45611.44</v>
       </c>
       <c r="D13" s="6">
-        <f>C13/C24</f>
+        <f>C13/C26</f>
         <v/>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
@@ -1677,7 +1753,7 @@
         <v>278129.21</v>
       </c>
       <c r="D14" s="6">
-        <f>C14/C24</f>
+        <f>C14/C26</f>
         <v/>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
@@ -1695,7 +1771,7 @@
         <v>1407.99</v>
       </c>
       <c r="D15" s="6">
-        <f>C15/C24</f>
+        <f>C15/C26</f>
         <v/>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -1713,7 +1789,7 @@
         <v>4320</v>
       </c>
       <c r="D16" s="6">
-        <f>C16/C24</f>
+        <f>C16/C26</f>
         <v/>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
@@ -1731,7 +1807,7 @@
         <v>88834.70999999999</v>
       </c>
       <c r="D17" s="6">
-        <f>C17/C24</f>
+        <f>C17/C26</f>
         <v/>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -1746,10 +1822,10 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>21606.67</v>
+        <v>52020.39999999999</v>
       </c>
       <c r="D18" s="6">
-        <f>C18/C24</f>
+        <f>C18/C26</f>
         <v/>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -1764,10 +1840,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13330.32</v>
+        <v>51343.23</v>
       </c>
       <c r="D19" s="6">
-        <f>C19/C24</f>
+        <f>C19/C26</f>
         <v/>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -1785,7 +1861,7 @@
         <v>7600</v>
       </c>
       <c r="D20" s="6">
-        <f>C20/C24</f>
+        <f>C20/C26</f>
         <v/>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -1803,7 +1879,7 @@
         <v>15047.28</v>
       </c>
       <c r="D21" s="6">
-        <f>C21/C24</f>
+        <f>C21/C26</f>
         <v/>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -1821,7 +1897,7 @@
         <v>14095.61</v>
       </c>
       <c r="D22" s="6">
-        <f>C22/C24</f>
+        <f>C22/C26</f>
         <v/>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -1839,27 +1915,63 @@
         <v>41569.41</v>
       </c>
       <c r="D23" s="6">
-        <f>C23/C24</f>
+        <f>C23/C26</f>
         <v/>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1377.3</v>
+      </c>
+      <c r="D24" s="6">
+        <f>C24/C26</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D25" s="6">
+        <f>C25/C26</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>TOTAL CERTIFICACIONES</t>
         </is>
       </c>
-      <c r="C24" s="8">
-        <f>SUM(C4:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="7">
-        <f>SUM(D4:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="7" t="n"/>
+      <c r="C26" s="8">
+        <f>SUM(C4:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="7">
+        <f>SUM(D4:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -27192,7 +27304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -27598,21 +27710,57 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6">
+        <f>'Certificaciones'!B24</f>
+        <v/>
+      </c>
+      <c r="B26" s="4">
+        <f>'Certificaciones'!C24</f>
+        <v/>
+      </c>
+      <c r="C26" s="6">
+        <f>'Certificaciones'!D24</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>C26*'Resumen'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <f>'Certificaciones'!B25</f>
+        <v/>
+      </c>
+      <c r="B27" s="4">
+        <f>'Certificaciones'!C25</f>
+        <v/>
+      </c>
+      <c r="C27" s="6">
+        <f>'Certificaciones'!D25</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>C27*'Resumen'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="8">
-        <f>SUM(B6:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="7">
-        <f>SUM(C6:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D6:D25)</f>
+      <c r="B28" s="8">
+        <f>SUM(B6:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="7">
+        <f>SUM(C6:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="8">
+        <f>SUM(D6:D27)</f>
         <v/>
       </c>
     </row>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'Certificaciones'!C26</f>
+        <f>'Certificaciones'!C27</f>
         <v/>
       </c>
     </row>
@@ -1463,41 +1463,79 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="6">
+        <f>'Certificaciones'!B26</f>
+        <v/>
+      </c>
+      <c r="B34" s="4">
+        <f>'Certificaciones'!C26</f>
+        <v/>
+      </c>
+      <c r="C34" s="6">
+        <f>'Certificaciones'!D26</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>C34*$B$7</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A34,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A34,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>D34+E34+F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="4">
+        <f>B34-G34</f>
+        <v/>
+      </c>
+      <c r="I34" s="6">
+        <f>IF(B34=0,0,G34/B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B34" s="8">
-        <f>SUM(B12:B33)</f>
-        <v/>
-      </c>
-      <c r="C34" s="7">
-        <f>SUM(C12:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="8">
-        <f>SUM(D12:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="8">
-        <f>SUM(E12:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="8">
-        <f>SUM(F12:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="8">
-        <f>SUM(G12:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="8">
-        <f>SUM(H12:H33)</f>
-        <v/>
-      </c>
-      <c r="I34" s="7">
-        <f>IF(B34=0,0,G34/B34)</f>
+      <c r="B35" s="8">
+        <f>SUM(B12:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="7">
+        <f>SUM(C12:C34)</f>
+        <v/>
+      </c>
+      <c r="D35" s="8">
+        <f>SUM(D12:D34)</f>
+        <v/>
+      </c>
+      <c r="E35" s="8">
+        <f>SUM(E12:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="8">
+        <f>SUM(F12:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="8">
+        <f>SUM(G12:G34)</f>
+        <v/>
+      </c>
+      <c r="H35" s="8">
+        <f>SUM(H12:H34)</f>
+        <v/>
+      </c>
+      <c r="I35" s="7">
+        <f>IF(B35=0,0,G35/B35)</f>
         <v/>
       </c>
     </row>
@@ -1516,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1573,7 +1611,7 @@
         <v>8875.66</v>
       </c>
       <c r="D4" s="6">
-        <f>C4/C26</f>
+        <f>C4/C27</f>
         <v/>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
@@ -1591,7 +1629,7 @@
         <v>23917.62</v>
       </c>
       <c r="D5" s="6">
-        <f>C5/C26</f>
+        <f>C5/C27</f>
         <v/>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
@@ -1609,7 +1647,7 @@
         <v>46635.25</v>
       </c>
       <c r="D6" s="6">
-        <f>C6/C26</f>
+        <f>C6/C27</f>
         <v/>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
@@ -1627,7 +1665,7 @@
         <v>105543.77</v>
       </c>
       <c r="D7" s="6">
-        <f>C7/C26</f>
+        <f>C7/C27</f>
         <v/>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -1645,7 +1683,7 @@
         <v>173193.43</v>
       </c>
       <c r="D8" s="6">
-        <f>C8/C26</f>
+        <f>C8/C27</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -1663,7 +1701,7 @@
         <v>63277.34</v>
       </c>
       <c r="D9" s="6">
-        <f>C9/C26</f>
+        <f>C9/C27</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -1681,7 +1719,7 @@
         <v>3288</v>
       </c>
       <c r="D10" s="6">
-        <f>C10/C26</f>
+        <f>C10/C27</f>
         <v/>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -1699,7 +1737,7 @@
         <v>16241.92</v>
       </c>
       <c r="D11" s="6">
-        <f>C11/C26</f>
+        <f>C11/C27</f>
         <v/>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -1717,7 +1755,7 @@
         <v>116432.26</v>
       </c>
       <c r="D12" s="6">
-        <f>C12/C26</f>
+        <f>C12/C27</f>
         <v/>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -1735,7 +1773,7 @@
         <v>45611.44</v>
       </c>
       <c r="D13" s="6">
-        <f>C13/C26</f>
+        <f>C13/C27</f>
         <v/>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
@@ -1750,10 +1788,10 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>278129.21</v>
+        <v>305555.25</v>
       </c>
       <c r="D14" s="6">
-        <f>C14/C26</f>
+        <f>C14/C27</f>
         <v/>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
@@ -1771,7 +1809,7 @@
         <v>1407.99</v>
       </c>
       <c r="D15" s="6">
-        <f>C15/C26</f>
+        <f>C15/C27</f>
         <v/>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -1789,7 +1827,7 @@
         <v>4320</v>
       </c>
       <c r="D16" s="6">
-        <f>C16/C26</f>
+        <f>C16/C27</f>
         <v/>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
@@ -1807,7 +1845,7 @@
         <v>88834.70999999999</v>
       </c>
       <c r="D17" s="6">
-        <f>C17/C26</f>
+        <f>C17/C27</f>
         <v/>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -1825,7 +1863,7 @@
         <v>52020.39999999999</v>
       </c>
       <c r="D18" s="6">
-        <f>C18/C26</f>
+        <f>C18/C27</f>
         <v/>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -1843,7 +1881,7 @@
         <v>51343.23</v>
       </c>
       <c r="D19" s="6">
-        <f>C19/C26</f>
+        <f>C19/C27</f>
         <v/>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -1861,7 +1899,7 @@
         <v>7600</v>
       </c>
       <c r="D20" s="6">
-        <f>C20/C26</f>
+        <f>C20/C27</f>
         <v/>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -1879,7 +1917,7 @@
         <v>15047.28</v>
       </c>
       <c r="D21" s="6">
-        <f>C21/C26</f>
+        <f>C21/C27</f>
         <v/>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -1897,7 +1935,7 @@
         <v>14095.61</v>
       </c>
       <c r="D22" s="6">
-        <f>C22/C26</f>
+        <f>C22/C27</f>
         <v/>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -1912,10 +1950,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>41569.41</v>
+        <v>58496.02</v>
       </c>
       <c r="D23" s="6">
-        <f>C23/C26</f>
+        <f>C23/C27</f>
         <v/>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -1926,14 +1964,14 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>26022 - OBRA COLEGIO MONOVAR</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1377.3</v>
+        <v>34338.63</v>
       </c>
       <c r="D24" s="6">
-        <f>C24/C26</f>
+        <f>C24/C27</f>
         <v/>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -1944,34 +1982,52 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1377.3</v>
+      </c>
+      <c r="D25" s="6">
+        <f>C25/C27</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C26" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="D25" s="6">
-        <f>C25/C26</f>
-        <v/>
-      </c>
-      <c r="E25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="D26" s="6">
+        <f>C26/C27</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>TOTAL CERTIFICACIONES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C4:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="7">
-        <f>SUM(D4:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="7" t="n"/>
+      <c r="C27" s="8">
+        <f>SUM(C4:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="7">
+        <f>SUM(D4:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -27304,7 +27360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -27746,21 +27802,39 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6">
+        <f>'Certificaciones'!B26</f>
+        <v/>
+      </c>
+      <c r="B28" s="4">
+        <f>'Certificaciones'!C26</f>
+        <v/>
+      </c>
+      <c r="C28" s="6">
+        <f>'Certificaciones'!D26</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f>C28*'Resumen'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="8">
-        <f>SUM(B6:B27)</f>
-        <v/>
-      </c>
-      <c r="C28" s="7">
-        <f>SUM(C6:C27)</f>
-        <v/>
-      </c>
-      <c r="D28" s="8">
-        <f>SUM(D6:D27)</f>
+      <c r="B29" s="8">
+        <f>SUM(B6:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="7">
+        <f>SUM(C6:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>SUM(D6:D28)</f>
         <v/>
       </c>
     </row>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>58496.02</v>
+        <v>61269.98</v>
       </c>
       <c r="D23" s="6">
         <f>C23/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2424</v>
+        <v>2448</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1188</v>
+        <v>1212</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prorrateo" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facturas por Obra'!$A$3:$G$518</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facturas por Obra'!$A$3:$G$521</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>6536.6</v>
+        <v>6572.3</v>
       </c>
       <c r="C15" s="6" t="n"/>
     </row>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2285.36</v>
+        <v>2341.82</v>
       </c>
       <c r="C22" s="6" t="n"/>
     </row>
@@ -10205,22 +10205,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>67.55</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="C26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>57.21</v>
+        <v>67.55</v>
       </c>
       <c r="C27" s="6" t="n"/>
     </row>
@@ -10251,7 +10251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G519"/>
+  <dimension ref="A1:G522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -10266,7 +10266,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FACTURAS POR OBRA - Todas las facturas directas (515 facturas)</t>
+          <t>FACTURAS POR OBRA - Todas las facturas directas (518 facturas)</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G338" s="4" t="n">
@@ -26455,22 +26455,22 @@
       </c>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>1.951,00</t>
+          <t>1.967,00</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>MALLA BALIZAJE</t>
+          <t>CAPAZOS/GARRAFA</t>
         </is>
       </c>
       <c r="E467" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>FERRETERIA PARRA SL</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
@@ -26479,33 +26479,33 @@
         </is>
       </c>
       <c r="G467" s="4" t="n">
-        <v>15.36</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26007 - OBRA HELENA Y JACOBO</t>
         </is>
       </c>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>1.917,00</t>
+          <t>1.951,00</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>BOLSA/PALETINA/TACO/RESINA</t>
+          <t>MALLA BALIZAJE</t>
         </is>
       </c>
       <c r="E468" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F468" s="6" t="inlineStr">
@@ -26514,73 +26514,77 @@
         </is>
       </c>
       <c r="G468" s="4" t="n">
-        <v>57.21</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="6" t="inlineStr">
         <is>
-          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>1.906,00</t>
+          <t>1.917,00</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>PREINSTALACION AIRE ACONDICIONADO SPLIT PARED</t>
+          <t>BOLSA/PALETINA/TACO/RESINA</t>
         </is>
       </c>
       <c r="E469" s="6" t="inlineStr">
         <is>
-          <t>GOCLIMA FRIO Y CALOR SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G469" s="4" t="n">
-        <v>1140</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="6" t="inlineStr">
         <is>
-          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>1.821,00</t>
+          <t>1.966,00</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>ELECTRICIDAD</t>
-        </is>
-      </c>
-      <c r="E470" s="6" t="inlineStr"/>
+          <t>ANGULO/BROCA/SPRAY</t>
+        </is>
+      </c>
+      <c r="E470" s="6" t="inlineStr">
+        <is>
+          <t>FERRETERIA FLORIDA SL</t>
+        </is>
+      </c>
       <c r="F470" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G470" s="4" t="n">
-        <v>956.5</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="471">
@@ -26591,22 +26595,22 @@
       </c>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>1.872,00</t>
+          <t>1.906,00</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 641758</t>
+          <t>PREINSTALACION AIRE ACONDICIONADO SPLIT PARED</t>
         </is>
       </c>
       <c r="E471" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>GOCLIMA FRIO Y CALOR SL</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
@@ -26615,7 +26619,7 @@
         </is>
       </c>
       <c r="G471" s="4" t="n">
-        <v>947.6</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="472">
@@ -26626,31 +26630,27 @@
       </c>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>1.820,00</t>
+          <t>1.821,00</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>FONTANERÍA</t>
-        </is>
-      </c>
-      <c r="E472" s="6" t="inlineStr">
-        <is>
-          <t>FONTAFIX EAR</t>
-        </is>
-      </c>
+          <t>ELECTRICIDAD</t>
+        </is>
+      </c>
+      <c r="E472" s="6" t="inlineStr"/>
       <c r="F472" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G472" s="4" t="n">
-        <v>877.25</v>
+        <v>956.5</v>
       </c>
     </row>
     <row r="473">
@@ -26661,31 +26661,31 @@
       </c>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>1.961,00</t>
+          <t>1.872,00</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>MORTERO/PEGA SELLA/MORTERO/PLASTICO NEGRO/CEMENTO/TUBO/ESPATULA</t>
+          <t>PRESUPUESTO 641758</t>
         </is>
       </c>
       <c r="E473" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G473" s="4" t="n">
-        <v>858.59</v>
+        <v>947.6</v>
       </c>
     </row>
     <row r="474">
@@ -26696,31 +26696,31 @@
       </c>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>1.939,00</t>
+          <t>1.820,00</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>PLATO DUCHA/PASTA/PISTOLA/CEMENTO</t>
+          <t>FONTANERÍA</t>
         </is>
       </c>
       <c r="E474" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>FONTAFIX EAR</t>
         </is>
       </c>
       <c r="F474" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G474" s="4" t="n">
-        <v>554.98</v>
+        <v>877.25</v>
       </c>
     </row>
     <row r="475">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>1.916,00</t>
+          <t>1.961,00</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
@@ -26741,21 +26741,21 @@
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES</t>
+          <t>MORTERO/PEGA SELLA/MORTERO/PLASTICO NEGRO/CEMENTO/TUBO/ESPATULA</t>
         </is>
       </c>
       <c r="E475" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES REUNIDOS SL</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G475" s="4" t="n">
-        <v>290</v>
+        <v>858.59</v>
       </c>
     </row>
     <row r="476">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>1.938,00</t>
+          <t>1.939,00</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
@@ -26776,12 +26776,12 @@
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PLATO DUCHA/PASTA/PISTOLA/CEMENTO</t>
         </is>
       </c>
       <c r="E476" s="6" t="inlineStr">
         <is>
-          <t>SANZ BUILDING 2000 SL</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F476" s="6" t="inlineStr">
@@ -26790,7 +26790,7 @@
         </is>
       </c>
       <c r="G476" s="4" t="n">
-        <v>211.3</v>
+        <v>554.98</v>
       </c>
     </row>
     <row r="477">
@@ -26801,31 +26801,31 @@
       </c>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>1.905,00</t>
+          <t>1.916,00</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>CEMENTO/PASTA AGARRE/ARENA/YESO/MORTERO HIDROFUGO</t>
+          <t>CONTENEDORES</t>
         </is>
       </c>
       <c r="E477" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>CONTENEDORES REUNIDOS SL</t>
         </is>
       </c>
       <c r="F477" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G477" s="4" t="n">
-        <v>188.96</v>
+        <v>290</v>
       </c>
     </row>
     <row r="478">
@@ -26836,31 +26836,31 @@
       </c>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>1.900,00</t>
+          <t>1.938,00</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>PASTA JUNTA/TRAMPILLA/CINTA YESO/CEPILLO</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E478" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>SANZ BUILDING 2000 SL</t>
         </is>
       </c>
       <c r="F478" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G478" s="4" t="n">
-        <v>157.36</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="479">
@@ -26871,22 +26871,22 @@
       </c>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>1.953,00</t>
+          <t>1.905,00</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>CINTA/CANAL/MONTANTE/PASTA</t>
+          <t>CEMENTO/PASTA AGARRE/ARENA/YESO/MORTERO HIDROFUGO</t>
         </is>
       </c>
       <c r="E479" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F479" s="6" t="inlineStr">
@@ -26895,7 +26895,7 @@
         </is>
       </c>
       <c r="G479" s="4" t="n">
-        <v>86.81</v>
+        <v>188.96</v>
       </c>
     </row>
     <row r="480">
@@ -26906,17 +26906,17 @@
       </c>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>1.945,00</t>
+          <t>1.900,00</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>MORTERO/ARENA/TRAMPILLA/GECOL</t>
+          <t>PASTA JUNTA/TRAMPILLA/CINTA YESO/CEPILLO</t>
         </is>
       </c>
       <c r="E480" s="6" t="inlineStr">
@@ -26930,7 +26930,7 @@
         </is>
       </c>
       <c r="G480" s="4" t="n">
-        <v>66.20999999999999</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="481">
@@ -26941,22 +26941,22 @@
       </c>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>1.921,00</t>
+          <t>1.953,00</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>DISCO CORTE/GUANTE/ZAPATO/PALETINA</t>
+          <t>CINTA/CANAL/MONTANTE/PASTA</t>
         </is>
       </c>
       <c r="E481" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F481" s="6" t="inlineStr">
@@ -26965,7 +26965,7 @@
         </is>
       </c>
       <c r="G481" s="4" t="n">
-        <v>45.03</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="482">
@@ -26976,22 +26976,22 @@
       </c>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>1.952,00</t>
+          <t>1.945,00</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>MASCARILLA/MASILLA/RODILLO/CUBETA</t>
+          <t>MORTERO/ARENA/TRAMPILLA/GECOL</t>
         </is>
       </c>
       <c r="E482" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F482" s="6" t="inlineStr">
@@ -27000,7 +27000,7 @@
         </is>
       </c>
       <c r="G482" s="4" t="n">
-        <v>43.25</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="483">
@@ -27011,17 +27011,17 @@
       </c>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>1.909,00</t>
+          <t>1.921,00</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>PEINE/PLIEGO LIJA/VARILLA</t>
+          <t>DISCO CORTE/GUANTE/ZAPATO/PALETINA</t>
         </is>
       </c>
       <c r="E483" s="6" t="inlineStr">
@@ -27035,7 +27035,7 @@
         </is>
       </c>
       <c r="G483" s="4" t="n">
-        <v>38.6</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="484">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>1.954,00</t>
+          <t>1.952,00</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>MORTERO JUNTA AXTON</t>
+          <t>MASCARILLA/MASILLA/RODILLO/CUBETA</t>
         </is>
       </c>
       <c r="E484" s="6" t="inlineStr">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="G484" s="4" t="n">
-        <v>24.77</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="485">
@@ -27081,17 +27081,17 @@
       </c>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>1.946,00</t>
+          <t>1.909,00</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>BERMUDA/CALDERETA</t>
+          <t>PEINE/PLIEGO LIJA/VARILLA</t>
         </is>
       </c>
       <c r="E485" s="6" t="inlineStr">
@@ -27105,7 +27105,7 @@
         </is>
       </c>
       <c r="G485" s="4" t="n">
-        <v>21.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="486">
@@ -27116,22 +27116,22 @@
       </c>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>1.904,00</t>
+          <t>1.968,00</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>IMPRIMACION PUENTE UNION</t>
+          <t>RHYNOGRIP</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F486" s="6" t="inlineStr">
@@ -27140,7 +27140,7 @@
         </is>
       </c>
       <c r="G486" s="4" t="n">
-        <v>21.03</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="487">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>1.903,00</t>
+          <t>1.954,00</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>ESPONJA/HIDROTUBO/TAPON/CODO/ADEHESIVO</t>
+          <t>MORTERO JUNTA AXTON</t>
         </is>
       </c>
       <c r="E487" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F487" s="6" t="inlineStr">
@@ -27175,138 +27175,138 @@
         </is>
       </c>
       <c r="G487" s="4" t="n">
-        <v>7.16</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="6" t="inlineStr">
         <is>
-          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
+          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>1.841,00</t>
+          <t>1.946,00</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>SUSCRIPCION NALANDA - GESTION DOCUMENTACION</t>
+          <t>BERMUDA/CALDERETA</t>
         </is>
       </c>
       <c r="E488" s="6" t="inlineStr">
         <is>
-          <t>NALANDA GLOBAL SA.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F488" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G488" s="4" t="n">
-        <v>420</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>1.829,00</t>
+          <t>1.904,00</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>HIERRO CIMENTACION Y MUROS</t>
+          <t>IMPRIMACION PUENTE UNION</t>
         </is>
       </c>
       <c r="E489" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G489" s="4" t="n">
-        <v>2433.16</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>1.895,00</t>
+          <t>1.903,00</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON</t>
+          <t>ESPONJA/HIDROTUBO/TAPON/CODO/ADEHESIVO</t>
         </is>
       </c>
       <c r="E490" s="6" t="inlineStr">
         <is>
-          <t>HORMIGONES DEL VINALOPO SA</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F490" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G490" s="4" t="n">
-        <v>2401.76</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
         </is>
       </c>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>1.907,00</t>
+          <t>1.841,00</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>FERRALLA/HIERRO</t>
+          <t>SUSCRIPCION NALANDA - GESTION DOCUMENTACION</t>
         </is>
       </c>
       <c r="E491" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>NALANDA GLOBAL SA.</t>
         </is>
       </c>
       <c r="F491" s="6" t="inlineStr">
@@ -27315,7 +27315,7 @@
         </is>
       </c>
       <c r="G491" s="4" t="n">
-        <v>1680.28</v>
+        <v>420</v>
       </c>
     </row>
     <row r="492">
@@ -27326,22 +27326,22 @@
       </c>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>1.843,00</t>
+          <t>1.829,00</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>HORMIGÓN CIMENTACION</t>
+          <t>HIERRO CIMENTACION Y MUROS</t>
         </is>
       </c>
       <c r="E492" s="6" t="inlineStr">
         <is>
-          <t>SEBASTIAN NAVARRO SL</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F492" s="6" t="inlineStr">
@@ -27350,7 +27350,7 @@
         </is>
       </c>
       <c r="G492" s="4" t="n">
-        <v>1560</v>
+        <v>2433.16</v>
       </c>
     </row>
     <row r="493">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>1.877,00</t>
+          <t>1.895,00</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
@@ -27371,12 +27371,12 @@
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>HORMIGON</t>
         </is>
       </c>
       <c r="E493" s="6" t="inlineStr">
         <is>
-          <t>GRUAS ILICITANAS SL.</t>
+          <t>HORMIGONES DEL VINALOPO SA</t>
         </is>
       </c>
       <c r="F493" s="6" t="inlineStr">
@@ -27385,7 +27385,7 @@
         </is>
       </c>
       <c r="G493" s="4" t="n">
-        <v>1550.25</v>
+        <v>2401.76</v>
       </c>
     </row>
     <row r="494">
@@ -27396,22 +27396,22 @@
       </c>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>1.893,00</t>
+          <t>1.907,00</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>FERRALLA/HIERRO</t>
         </is>
       </c>
       <c r="E494" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F494" s="6" t="inlineStr">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G494" s="4" t="n">
-        <v>1365</v>
+        <v>1680.28</v>
       </c>
     </row>
     <row r="495">
@@ -27431,22 +27431,22 @@
       </c>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>1.865,00</t>
+          <t>1.843,00</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 641631</t>
+          <t>HORMIGÓN CIMENTACION</t>
         </is>
       </c>
       <c r="E495" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>SEBASTIAN NAVARRO SL</t>
         </is>
       </c>
       <c r="F495" s="6" t="inlineStr">
@@ -27455,7 +27455,7 @@
         </is>
       </c>
       <c r="G495" s="4" t="n">
-        <v>998.6900000000001</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="496">
@@ -27466,31 +27466,31 @@
       </c>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>1.947,00</t>
+          <t>1.877,00</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON HA-25/F/20/XC1</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E496" s="6" t="inlineStr">
         <is>
-          <t>HORMIGONES DEL VINALOPO SA</t>
+          <t>GRUAS ILICITANAS SL.</t>
         </is>
       </c>
       <c r="F496" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G496" s="4" t="n">
-        <v>532.5</v>
+        <v>1550.25</v>
       </c>
     </row>
     <row r="497">
@@ -27501,22 +27501,22 @@
       </c>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>1.810,00</t>
+          <t>1.893,00</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON LIMPIEZA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E497" s="6" t="inlineStr">
         <is>
-          <t>SEBASTIAN NAVARRO SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F497" s="6" t="inlineStr">
@@ -27525,7 +27525,7 @@
         </is>
       </c>
       <c r="G497" s="4" t="n">
-        <v>510</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="498">
@@ -27536,22 +27536,22 @@
       </c>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>1.919,00</t>
+          <t>1.865,00</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>CAMION GRUA</t>
+          <t>PRESUPUESTO 641631</t>
         </is>
       </c>
       <c r="E498" s="6" t="inlineStr">
         <is>
-          <t>GRUAS ILICITANAS SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F498" s="6" t="inlineStr">
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="G498" s="4" t="n">
-        <v>500</v>
+        <v>998.6900000000001</v>
       </c>
     </row>
     <row r="499">
@@ -27571,31 +27571,31 @@
       </c>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>1.852,00</t>
+          <t>1.947,00</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>ELECTRICIDAD CUADRO</t>
+          <t>HORMIGON HA-25/F/20/XC1</t>
         </is>
       </c>
       <c r="E499" s="6" t="inlineStr">
         <is>
-          <t>GABRIEL MOYA INSTALACIONES ELECTRICAS SL.</t>
+          <t>HORMIGONES DEL VINALOPO SA</t>
         </is>
       </c>
       <c r="F499" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G499" s="4" t="n">
-        <v>426</v>
+        <v>532.5</v>
       </c>
     </row>
     <row r="500">
@@ -27606,22 +27606,22 @@
       </c>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>1.912,00</t>
+          <t>1.810,00</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>HORMIGON LIMPIEZA</t>
         </is>
       </c>
       <c r="E500" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>SEBASTIAN NAVARRO SL</t>
         </is>
       </c>
       <c r="F500" s="6" t="inlineStr">
@@ -27630,7 +27630,7 @@
         </is>
       </c>
       <c r="G500" s="4" t="n">
-        <v>325</v>
+        <v>510</v>
       </c>
     </row>
     <row r="501">
@@ -27641,22 +27641,22 @@
       </c>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>1.858,00</t>
+          <t>1.919,00</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>CAMION GRUA</t>
         </is>
       </c>
       <c r="E501" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>GRUAS ILICITANAS SL.</t>
         </is>
       </c>
       <c r="F501" s="6" t="inlineStr">
@@ -27665,7 +27665,7 @@
         </is>
       </c>
       <c r="G501" s="4" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
     </row>
     <row r="502">
@@ -27676,22 +27676,22 @@
       </c>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>1.884,00</t>
+          <t>1.852,00</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>TOMA DE MUESTRAS DE HORMIGON FRESCO</t>
+          <t>ELECTRICIDAD CUADRO</t>
         </is>
       </c>
       <c r="E502" s="6" t="inlineStr">
         <is>
-          <t>LABORATORIO DE INGENIERIA Y MEDIO AMBIENTE SA.</t>
+          <t>GABRIEL MOYA INSTALACIONES ELECTRICAS SL.</t>
         </is>
       </c>
       <c r="F502" s="6" t="inlineStr">
@@ -27700,7 +27700,7 @@
         </is>
       </c>
       <c r="G502" s="4" t="n">
-        <v>100</v>
+        <v>426</v>
       </c>
     </row>
     <row r="503">
@@ -27711,22 +27711,22 @@
       </c>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>1.790,00</t>
+          <t>1.912,00</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>FILM PE GALGA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E503" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F503" s="6" t="inlineStr">
@@ -27735,33 +27735,33 @@
         </is>
       </c>
       <c r="G503" s="4" t="n">
-        <v>92.56</v>
+        <v>325</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>1.891,00</t>
+          <t>1.858,00</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E504" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F504" s="6" t="inlineStr">
@@ -27770,33 +27770,33 @@
         </is>
       </c>
       <c r="G504" s="4" t="n">
-        <v>1350.83</v>
+        <v>325</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>1.828,00</t>
+          <t>1.884,00</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER MAQUINARIA (+20%)</t>
+          <t>TOMA DE MUESTRAS DE HORMIGON FRESCO</t>
         </is>
       </c>
       <c r="E505" s="6" t="inlineStr">
         <is>
-          <t>GOMARIZ SISTEMAS DE ELEVACION SL</t>
+          <t>LABORATORIO DE INGENIERIA Y MEDIO AMBIENTE SA.</t>
         </is>
       </c>
       <c r="F505" s="6" t="inlineStr">
@@ -27805,33 +27805,33 @@
         </is>
       </c>
       <c r="G505" s="4" t="n">
-        <v>498.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>1.914,00</t>
+          <t>1.790,00</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>FILM PE GALGA</t>
         </is>
       </c>
       <c r="E506" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F506" s="6" t="inlineStr">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="G506" s="4" t="n">
-        <v>455</v>
+        <v>92.56</v>
       </c>
     </row>
     <row r="507">
@@ -27851,22 +27851,22 @@
       </c>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>1.920,00</t>
+          <t>1.891,00</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>PALA EXCAVADORA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="E507" s="6" t="inlineStr">
         <is>
-          <t>PAULINO TOMAS JUAN</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F507" s="6" t="inlineStr">
@@ -27875,7 +27875,7 @@
         </is>
       </c>
       <c r="G507" s="4" t="n">
-        <v>180</v>
+        <v>1350.83</v>
       </c>
     </row>
     <row r="508">
@@ -27886,22 +27886,22 @@
       </c>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>1.923,00</t>
+          <t>1.828,00</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>RODILLO/PALETINA/MONOCAPA/CEMENTO COLA/LLANA</t>
+          <t>ALQUILER MAQUINARIA (+20%)</t>
         </is>
       </c>
       <c r="E508" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>GOMARIZ SISTEMAS DE ELEVACION SL</t>
         </is>
       </c>
       <c r="F508" s="6" t="inlineStr">
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="G508" s="4" t="n">
-        <v>178.56</v>
+        <v>498.65</v>
       </c>
     </row>
     <row r="509">
@@ -27921,22 +27921,22 @@
       </c>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>1.839,00</t>
+          <t>1.914,00</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E509" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F509" s="6" t="inlineStr">
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="G509" s="4" t="n">
-        <v>104.13</v>
+        <v>455</v>
       </c>
     </row>
     <row r="510">
@@ -27956,136 +27956,136 @@
       </c>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>1.942,00</t>
+          <t>1.920,00</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>IMPRESION PLANOS A3</t>
+          <t>PALA EXCAVADORA</t>
         </is>
       </c>
       <c r="E510" s="6" t="inlineStr">
         <is>
-          <t>PLACIDO BOTELLA PEREZ</t>
+          <t>PAULINO TOMAS JUAN</t>
         </is>
       </c>
       <c r="F510" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G510" s="4" t="n">
-        <v>30.46</v>
+        <v>180</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>1.782,00</t>
+          <t>1.923,00</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>RODILLO/PALETINA/MONOCAPA/CEMENTO COLA/LLANA</t>
         </is>
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="F511" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G511" s="4" t="n">
-        <v>2312.04</v>
+        <v>178.56</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>1.800,00</t>
+          <t>1.839,00</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON CIMENTACION</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E512" s="6" t="inlineStr">
         <is>
-          <t>CANTERAS Y RECICLADOS SL.</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F512" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G512" s="4" t="n">
-        <v>1196.25</v>
+        <v>104.13</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>1.804,00</t>
+          <t>1.942,00</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>IMPRESION PLANOS A3</t>
         </is>
       </c>
       <c r="E513" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>PLACIDO BOTELLA PEREZ</t>
         </is>
       </c>
       <c r="F513" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G513" s="4" t="n">
-        <v>975</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="514">
@@ -28096,22 +28096,22 @@
       </c>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>1.764,00</t>
+          <t>1.782,00</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>HIERRO CIMENTACIÓN</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E514" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F514" s="6" t="inlineStr">
@@ -28120,7 +28120,7 @@
         </is>
       </c>
       <c r="G514" s="4" t="n">
-        <v>441.36</v>
+        <v>2312.04</v>
       </c>
     </row>
     <row r="515">
@@ -28131,22 +28131,22 @@
       </c>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>1.812,00</t>
+          <t>1.800,00</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>PALA PAULINO</t>
+          <t>HORMIGON CIMENTACION</t>
         </is>
       </c>
       <c r="E515" s="6" t="inlineStr">
         <is>
-          <t>PAULINO TOMAS JUAN</t>
+          <t>CANTERAS Y RECICLADOS SL.</t>
         </is>
       </c>
       <c r="F515" s="6" t="inlineStr">
@@ -28155,7 +28155,7 @@
         </is>
       </c>
       <c r="G515" s="4" t="n">
-        <v>180</v>
+        <v>1196.25</v>
       </c>
     </row>
     <row r="516">
@@ -28166,22 +28166,22 @@
       </c>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>1.823,00</t>
+          <t>1.804,00</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>GRUA-CAMION</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E516" s="6" t="inlineStr">
         <is>
-          <t>JOSE LUIS PEREZ JAREÑO</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F516" s="6" t="inlineStr">
@@ -28190,7 +28190,7 @@
         </is>
       </c>
       <c r="G516" s="4" t="n">
-        <v>75</v>
+        <v>975</v>
       </c>
     </row>
     <row r="517">
@@ -28201,22 +28201,22 @@
       </c>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>1.840,00</t>
+          <t>1.764,00</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>HIERRO CIMENTACIÓN</t>
         </is>
       </c>
       <c r="E517" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F517" s="6" t="inlineStr">
@@ -28225,7 +28225,7 @@
         </is>
       </c>
       <c r="G517" s="4" t="n">
-        <v>41.9</v>
+        <v>441.36</v>
       </c>
     </row>
     <row r="518">
@@ -28236,51 +28236,156 @@
       </c>
       <c r="B518" s="6" t="inlineStr">
         <is>
+          <t>1.812,00</t>
+        </is>
+      </c>
+      <c r="C518" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="D518" s="6" t="inlineStr">
+        <is>
+          <t>PALA PAULINO</t>
+        </is>
+      </c>
+      <c r="E518" s="6" t="inlineStr">
+        <is>
+          <t>PAULINO TOMAS JUAN</t>
+        </is>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G518" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="6" t="inlineStr">
+        <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B519" s="6" t="inlineStr">
+        <is>
+          <t>1.823,00</t>
+        </is>
+      </c>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="D519" s="6" t="inlineStr">
+        <is>
+          <t>GRUA-CAMION</t>
+        </is>
+      </c>
+      <c r="E519" s="6" t="inlineStr">
+        <is>
+          <t>JOSE LUIS PEREZ JAREÑO</t>
+        </is>
+      </c>
+      <c r="F519" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G519" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="6" t="inlineStr">
+        <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B520" s="6" t="inlineStr">
+        <is>
+          <t>1.840,00</t>
+        </is>
+      </c>
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="D520" s="6" t="inlineStr">
+        <is>
+          <t>MATERIAL OBRA</t>
+        </is>
+      </c>
+      <c r="E520" s="6" t="inlineStr">
+        <is>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+        </is>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G520" s="4" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="6" t="inlineStr">
+        <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B521" s="6" t="inlineStr">
+        <is>
           <t>1.759,00</t>
         </is>
       </c>
-      <c r="C518" s="6" t="inlineStr">
+      <c r="C521" s="6" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="D518" s="6" t="inlineStr">
+      <c r="D521" s="6" t="inlineStr">
         <is>
           <t>ARENA Y BARDO</t>
         </is>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E521" s="6" t="inlineStr">
         <is>
           <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
-      <c r="F518" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <t>INVÁLIDO</t>
         </is>
       </c>
-      <c r="G518" s="4" t="n">
+      <c r="G521" s="4" t="n">
         <v>30.25</v>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" s="7" t="inlineStr">
+    <row r="522">
+      <c r="A522" s="7" t="inlineStr">
         <is>
           <t>TOTAL FACTURAS POR OBRA</t>
         </is>
       </c>
-      <c r="B519" s="7" t="n"/>
-      <c r="C519" s="7" t="n"/>
-      <c r="D519" s="7" t="n"/>
-      <c r="E519" s="7" t="n"/>
-      <c r="F519" s="7" t="n"/>
-      <c r="G519" s="8">
-        <f>SUM(G4:G518)</f>
+      <c r="B522" s="7" t="n"/>
+      <c r="C522" s="7" t="n"/>
+      <c r="D522" s="7" t="n"/>
+      <c r="E522" s="7" t="n"/>
+      <c r="F522" s="7" t="n"/>
+      <c r="G522" s="8">
+        <f>SUM(G4:G521)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G518"/>
+  <autoFilter ref="A3:G521"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2448</v>
+        <v>2476</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1212</v>
+        <v>1240</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>173193.43</v>
+        <v>171613.88</v>
       </c>
       <c r="D8" s="6">
         <f>C8/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>14095.61</v>
+        <v>16100.81</v>
       </c>
       <c r="D22" s="6">
         <f>C22/C27</f>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2476</v>
+        <v>2512</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>666</v>
+        <v>690</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2512</v>
+        <v>2536</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>690</v>
+        <v>718</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>20</v>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1260</v>
+        <v>1284</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>20</v>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>20</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prorrateo" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facturas por Obra'!$A$3:$G$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facturas por Obra'!$A$3:$G$533</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10148,44 +10148,44 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2100 - OBRA MURO VECINO CAMPO</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>15376.72</v>
+        <v>15398.13</v>
       </c>
       <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>2100 - OBRA MURO VECINO CAMPO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>14800.2</v>
+        <v>15376.72</v>
       </c>
       <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>26003 - BARINAS</t>
+          <t>26007 - OBRA HELENA Y JACOBO</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>13889.35</v>
+        <v>14994.26</v>
       </c>
       <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>26007 - OBRA HELENA Y JACOBO</t>
+          <t>26003 - BARINAS</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>10413.22</v>
+        <v>13889.35</v>
       </c>
       <c r="C12" s="6" t="n"/>
     </row>
@@ -10247,55 +10247,55 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>4230.33</v>
+        <v>4468.63</v>
       </c>
       <c r="C18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>26002 - GARAJE MURCIA</t>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>3350.48</v>
+        <v>4230.33</v>
       </c>
       <c r="C19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>24001 - OBRA C/IBIZA, ASPE (CASA CABO)</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>3248.2</v>
+        <v>3350.48</v>
       </c>
       <c r="C20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2400 - ARREGLOS OBRAS ARAQUE Y MAQUEDA</t>
+          <t>24001 - OBRA C/IBIZA, ASPE (CASA CABO)</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>3129</v>
+        <v>3248.2</v>
       </c>
       <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>2400 - ARREGLOS OBRAS ARAQUE Y MAQUEDA</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2797.63</v>
+        <v>3129</v>
       </c>
       <c r="C22" s="6" t="n"/>
     </row>
@@ -10324,33 +10324,33 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>26006 - OBRA PADRE TRINI</t>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>298.32</v>
+        <v>332.1</v>
       </c>
       <c r="C25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26006 - OBRA PADRE TRINI</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>199.96</v>
+        <v>298.32</v>
       </c>
       <c r="C26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>26022 - OBRA COLEGIO MONOVAR</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>102.1</v>
+        <v>199.96</v>
       </c>
       <c r="C27" s="6" t="n"/>
     </row>
@@ -10392,7 +10392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G528"/>
+  <dimension ref="A1:G534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -10407,7 +10407,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FACTURAS POR OBRA - Todas las facturas directas (524 facturas)</t>
+          <t>FACTURAS POR OBRA - Todas las facturas directas (530 facturas)</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G109" s="4" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G127" s="4" t="n">
@@ -26581,7 +26581,7 @@
       </c>
       <c r="F466" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G466" s="4" t="n">
@@ -26596,31 +26596,31 @@
       </c>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>1.901,00</t>
+          <t>1.971,00</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>REBAJE SOLAR</t>
+          <t>ACERO FERRALLADO</t>
         </is>
       </c>
       <c r="E467" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES Y EXCAVACIONES ASPE SL.</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G467" s="4" t="n">
-        <v>2270</v>
+        <v>3691.04</v>
       </c>
     </row>
     <row r="468">
@@ -26631,31 +26631,31 @@
       </c>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>1.929,00</t>
+          <t>1.901,00</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>COBRE/BRIDA/PICA DE TIERRA</t>
+          <t>REBAJE SOLAR</t>
         </is>
       </c>
       <c r="E468" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>CONTENEDORES Y EXCAVACIONES ASPE SL.</t>
         </is>
       </c>
       <c r="F468" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G468" s="4" t="n">
-        <v>101.4</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="469">
@@ -26666,22 +26666,22 @@
       </c>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>1.967,00</t>
+          <t>1.969,00</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>CAPAZOS/GARRAFA</t>
+          <t>BOMBA HORMIGON</t>
         </is>
       </c>
       <c r="E469" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA PARRA SL</t>
+          <t>LORENZO ROMERO MORALEDA</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
@@ -26690,7 +26690,7 @@
         </is>
       </c>
       <c r="G469" s="4" t="n">
-        <v>56.46</v>
+        <v>890</v>
       </c>
     </row>
     <row r="470">
@@ -26701,17 +26701,17 @@
       </c>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>1.951,00</t>
+          <t>1.929,00</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>MALLA BALIZAJE</t>
+          <t>COBRE/BRIDA/PICA DE TIERRA</t>
         </is>
       </c>
       <c r="E470" s="6" t="inlineStr">
@@ -26721,81 +26721,81 @@
       </c>
       <c r="F470" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G470" s="4" t="n">
-        <v>15.36</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26007 - OBRA HELENA Y JACOBO</t>
         </is>
       </c>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>1.934,00</t>
+          <t>1.967,00</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>DETECTOR/PROYECTOR/CAPUCHON/CINTA/CLAVIJA</t>
+          <t>CAPAZOS/GARRAFA</t>
         </is>
       </c>
       <c r="E471" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>FERRETERIA PARRA SL</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G471" s="4" t="n">
-        <v>117.7</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="6" t="inlineStr">
         <is>
-          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+          <t>26007 - OBRA HELENA Y JACOBO</t>
         </is>
       </c>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>1.917,00</t>
+          <t>1.951,00</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>BOLSA/PALETINA/TACO/RESINA</t>
+          <t>MALLA BALIZAJE</t>
         </is>
       </c>
       <c r="E472" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F472" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G472" s="4" t="n">
-        <v>57.21</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="473">
@@ -26806,22 +26806,22 @@
       </c>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>1.966,00</t>
+          <t>1.934,00</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>ANGULO/BROCA/SPRAY</t>
+          <t>DETECTOR/PROYECTOR/CAPUCHON/CINTA/CLAVIJA</t>
         </is>
       </c>
       <c r="E473" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA FLORIDA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
@@ -26830,73 +26830,77 @@
         </is>
       </c>
       <c r="G473" s="4" t="n">
-        <v>25.05</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="6" t="inlineStr">
         <is>
-          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>1.906,00</t>
+          <t>1.917,00</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>PREINSTALACION AIRE ACONDICIONADO SPLIT PARED</t>
+          <t>BOLSA/PALETINA/TACO/RESINA</t>
         </is>
       </c>
       <c r="E474" s="6" t="inlineStr">
         <is>
-          <t>GOCLIMA FRIO Y CALOR SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="F474" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G474" s="4" t="n">
-        <v>1140</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="6" t="inlineStr">
         <is>
-          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
+          <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
         </is>
       </c>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>1.821,00</t>
+          <t>1.966,00</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>ELECTRICIDAD</t>
-        </is>
-      </c>
-      <c r="E475" s="6" t="inlineStr"/>
+          <t>ANGULO/BROCA/SPRAY</t>
+        </is>
+      </c>
+      <c r="E475" s="6" t="inlineStr">
+        <is>
+          <t>FERRETERIA FLORIDA SL</t>
+        </is>
+      </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G475" s="4" t="n">
-        <v>956.5</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="476">
@@ -26907,22 +26911,22 @@
       </c>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>1.872,00</t>
+          <t>1.906,00</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 641758</t>
+          <t>PREINSTALACION AIRE ACONDICIONADO SPLIT PARED</t>
         </is>
       </c>
       <c r="E476" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>GOCLIMA FRIO Y CALOR SL</t>
         </is>
       </c>
       <c r="F476" s="6" t="inlineStr">
@@ -26931,7 +26935,7 @@
         </is>
       </c>
       <c r="G476" s="4" t="n">
-        <v>947.6</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="477">
@@ -26942,31 +26946,27 @@
       </c>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>1.820,00</t>
+          <t>1.821,00</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>FONTANERÍA</t>
-        </is>
-      </c>
-      <c r="E477" s="6" t="inlineStr">
-        <is>
-          <t>FONTAFIX EAR</t>
-        </is>
-      </c>
+          <t>ELECTRICIDAD</t>
+        </is>
+      </c>
+      <c r="E477" s="6" t="inlineStr"/>
       <c r="F477" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G477" s="4" t="n">
-        <v>877.25</v>
+        <v>956.5</v>
       </c>
     </row>
     <row r="478">
@@ -26977,31 +26977,31 @@
       </c>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>1.961,00</t>
+          <t>1.872,00</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>MORTERO/PEGA SELLA/MORTERO/PLASTICO NEGRO/CEMENTO/TUBO/ESPATULA</t>
+          <t>PRESUPUESTO 641758</t>
         </is>
       </c>
       <c r="E478" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F478" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G478" s="4" t="n">
-        <v>858.59</v>
+        <v>947.6</v>
       </c>
     </row>
     <row r="479">
@@ -27012,31 +27012,31 @@
       </c>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>1.939,00</t>
+          <t>1.820,00</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>PLATO DUCHA/PASTA/PISTOLA/CEMENTO</t>
+          <t>FONTANERÍA</t>
         </is>
       </c>
       <c r="E479" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>FONTAFIX EAR</t>
         </is>
       </c>
       <c r="F479" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G479" s="4" t="n">
-        <v>554.98</v>
+        <v>877.25</v>
       </c>
     </row>
     <row r="480">
@@ -27047,7 +27047,7 @@
       </c>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>1.916,00</t>
+          <t>1.961,00</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
@@ -27057,21 +27057,21 @@
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES</t>
+          <t>MORTERO/PEGA SELLA/MORTERO/PLASTICO NEGRO/CEMENTO/TUBO/ESPATULA</t>
         </is>
       </c>
       <c r="E480" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES REUNIDOS SL</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F480" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G480" s="4" t="n">
-        <v>290</v>
+        <v>858.59</v>
       </c>
     </row>
     <row r="481">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>1.938,00</t>
+          <t>1.939,00</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
@@ -27092,21 +27092,21 @@
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PLATO DUCHA/PASTA/PISTOLA/CEMENTO</t>
         </is>
       </c>
       <c r="E481" s="6" t="inlineStr">
         <is>
-          <t>SANZ BUILDING 2000 SL</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F481" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G481" s="4" t="n">
-        <v>211.3</v>
+        <v>554.98</v>
       </c>
     </row>
     <row r="482">
@@ -27117,31 +27117,31 @@
       </c>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>1.905,00</t>
+          <t>1.916,00</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>CEMENTO/PASTA AGARRE/ARENA/YESO/MORTERO HIDROFUGO</t>
+          <t>CONTENEDORES</t>
         </is>
       </c>
       <c r="E482" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>CONTENEDORES REUNIDOS SL</t>
         </is>
       </c>
       <c r="F482" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G482" s="4" t="n">
-        <v>188.96</v>
+        <v>290</v>
       </c>
     </row>
     <row r="483">
@@ -27152,31 +27152,31 @@
       </c>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>1.900,00</t>
+          <t>1.938,00</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>PASTA JUNTA/TRAMPILLA/CINTA YESO/CEPILLO</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E483" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>SANZ BUILDING 2000 SL</t>
         </is>
       </c>
       <c r="F483" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G483" s="4" t="n">
-        <v>157.36</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="484">
@@ -27187,22 +27187,22 @@
       </c>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>1.953,00</t>
+          <t>1.905,00</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>CINTA/CANAL/MONTANTE/PASTA</t>
+          <t>CEMENTO/PASTA AGARRE/ARENA/YESO/MORTERO HIDROFUGO</t>
         </is>
       </c>
       <c r="E484" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F484" s="6" t="inlineStr">
@@ -27211,7 +27211,7 @@
         </is>
       </c>
       <c r="G484" s="4" t="n">
-        <v>86.81</v>
+        <v>188.96</v>
       </c>
     </row>
     <row r="485">
@@ -27222,17 +27222,17 @@
       </c>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>1.945,00</t>
+          <t>1.900,00</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>MORTERO/ARENA/TRAMPILLA/GECOL</t>
+          <t>PASTA JUNTA/TRAMPILLA/CINTA YESO/CEPILLO</t>
         </is>
       </c>
       <c r="E485" s="6" t="inlineStr">
@@ -27246,7 +27246,7 @@
         </is>
       </c>
       <c r="G485" s="4" t="n">
-        <v>66.20999999999999</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="486">
@@ -27257,22 +27257,22 @@
       </c>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>1.921,00</t>
+          <t>1.953,00</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>DISCO CORTE/GUANTE/ZAPATO/PALETINA</t>
+          <t>CINTA/CANAL/MONTANTE/PASTA</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F486" s="6" t="inlineStr">
@@ -27281,7 +27281,7 @@
         </is>
       </c>
       <c r="G486" s="4" t="n">
-        <v>45.03</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="487">
@@ -27292,22 +27292,22 @@
       </c>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>1.952,00</t>
+          <t>1.945,00</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>MASCARILLA/MASILLA/RODILLO/CUBETA</t>
+          <t>MORTERO/ARENA/TRAMPILLA/GECOL</t>
         </is>
       </c>
       <c r="E487" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F487" s="6" t="inlineStr">
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="G487" s="4" t="n">
-        <v>43.25</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="488">
@@ -27327,17 +27327,17 @@
       </c>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>1.909,00</t>
+          <t>1.921,00</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>PEINE/PLIEGO LIJA/VARILLA</t>
+          <t>DISCO CORTE/GUANTE/ZAPATO/PALETINA</t>
         </is>
       </c>
       <c r="E488" s="6" t="inlineStr">
@@ -27351,7 +27351,7 @@
         </is>
       </c>
       <c r="G488" s="4" t="n">
-        <v>38.6</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="489">
@@ -27362,22 +27362,22 @@
       </c>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>1.968,00</t>
+          <t>1.952,00</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>RHYNOGRIP</t>
+          <t>MASCARILLA/MASILLA/RODILLO/CUBETA</t>
         </is>
       </c>
       <c r="E489" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F489" s="6" t="inlineStr">
@@ -27386,7 +27386,7 @@
         </is>
       </c>
       <c r="G489" s="4" t="n">
-        <v>35.7</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="490">
@@ -27397,22 +27397,22 @@
       </c>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>1.954,00</t>
+          <t>1.909,00</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>MORTERO JUNTA AXTON</t>
+          <t>PEINE/PLIEGO LIJA/VARILLA</t>
         </is>
       </c>
       <c r="E490" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F490" s="6" t="inlineStr">
@@ -27421,7 +27421,7 @@
         </is>
       </c>
       <c r="G490" s="4" t="n">
-        <v>24.77</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="491">
@@ -27432,7 +27432,7 @@
       </c>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>1.946,00</t>
+          <t>1.968,00</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
@@ -27442,21 +27442,21 @@
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>BERMUDA/CALDERETA</t>
+          <t>RHYNOGRIP</t>
         </is>
       </c>
       <c r="E491" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F491" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G491" s="4" t="n">
-        <v>21.2</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="492">
@@ -27467,22 +27467,22 @@
       </c>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>1.904,00</t>
+          <t>1.954,00</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>IMPRIMACION PUENTE UNION</t>
+          <t>MORTERO JUNTA AXTON</t>
         </is>
       </c>
       <c r="E492" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F492" s="6" t="inlineStr">
@@ -27491,7 +27491,7 @@
         </is>
       </c>
       <c r="G492" s="4" t="n">
-        <v>21.03</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="493">
@@ -27502,17 +27502,17 @@
       </c>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>1.903,00</t>
+          <t>1.946,00</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>ESPONJA/HIDROTUBO/TAPON/CODO/ADEHESIVO</t>
+          <t>BERMUDA/CALDERETA</t>
         </is>
       </c>
       <c r="E493" s="6" t="inlineStr">
@@ -27526,103 +27526,103 @@
         </is>
       </c>
       <c r="G493" s="4" t="n">
-        <v>7.16</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="6" t="inlineStr">
         <is>
-          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
+          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>1.841,00</t>
+          <t>1.904,00</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>SUSCRIPCION NALANDA - GESTION DOCUMENTACION</t>
+          <t>IMPRIMACION PUENTE UNION</t>
         </is>
       </c>
       <c r="E494" s="6" t="inlineStr">
         <is>
-          <t>NALANDA GLOBAL SA.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F494" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G494" s="4" t="n">
-        <v>420</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>26009 - OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>1.829,00</t>
+          <t>1.903,00</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>HIERRO CIMENTACION Y MUROS</t>
+          <t>ESPONJA/HIDROTUBO/TAPON/CODO/ADEHESIVO</t>
         </is>
       </c>
       <c r="E495" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F495" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G495" s="4" t="n">
-        <v>2433.16</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="6" t="inlineStr">
         <is>
-          <t>26011 - CASTILLO DE ELDA</t>
+          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
         </is>
       </c>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>1.895,00</t>
+          <t>1.841,00</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON</t>
+          <t>SUSCRIPCION NALANDA - GESTION DOCUMENTACION</t>
         </is>
       </c>
       <c r="E496" s="6" t="inlineStr">
         <is>
-          <t>HORMIGONES DEL VINALOPO SA</t>
+          <t>NALANDA GLOBAL SA.</t>
         </is>
       </c>
       <c r="F496" s="6" t="inlineStr">
@@ -27631,7 +27631,7 @@
         </is>
       </c>
       <c r="G496" s="4" t="n">
-        <v>2401.76</v>
+        <v>420</v>
       </c>
     </row>
     <row r="497">
@@ -27642,17 +27642,17 @@
       </c>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>1.907,00</t>
+          <t>1.829,00</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>FERRALLA/HIERRO</t>
+          <t>HIERRO CIMENTACION Y MUROS</t>
         </is>
       </c>
       <c r="E497" s="6" t="inlineStr">
@@ -27666,7 +27666,7 @@
         </is>
       </c>
       <c r="G497" s="4" t="n">
-        <v>1680.28</v>
+        <v>2433.16</v>
       </c>
     </row>
     <row r="498">
@@ -27677,22 +27677,22 @@
       </c>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>1.843,00</t>
+          <t>1.895,00</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>HORMIGÓN CIMENTACION</t>
+          <t>HORMIGON</t>
         </is>
       </c>
       <c r="E498" s="6" t="inlineStr">
         <is>
-          <t>SEBASTIAN NAVARRO SL</t>
+          <t>HORMIGONES DEL VINALOPO SA</t>
         </is>
       </c>
       <c r="F498" s="6" t="inlineStr">
@@ -27701,7 +27701,7 @@
         </is>
       </c>
       <c r="G498" s="4" t="n">
-        <v>1560</v>
+        <v>2401.76</v>
       </c>
     </row>
     <row r="499">
@@ -27712,22 +27712,22 @@
       </c>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>1.877,00</t>
+          <t>1.907,00</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>FERRALLA/HIERRO</t>
         </is>
       </c>
       <c r="E499" s="6" t="inlineStr">
         <is>
-          <t>GRUAS ILICITANAS SL.</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F499" s="6" t="inlineStr">
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="G499" s="4" t="n">
-        <v>1550.25</v>
+        <v>1680.28</v>
       </c>
     </row>
     <row r="500">
@@ -27747,22 +27747,22 @@
       </c>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>1.893,00</t>
+          <t>1.843,00</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>HORMIGÓN CIMENTACION</t>
         </is>
       </c>
       <c r="E500" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>SEBASTIAN NAVARRO SL</t>
         </is>
       </c>
       <c r="F500" s="6" t="inlineStr">
@@ -27771,7 +27771,7 @@
         </is>
       </c>
       <c r="G500" s="4" t="n">
-        <v>1365</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="501">
@@ -27782,22 +27782,22 @@
       </c>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>1.865,00</t>
+          <t>1.877,00</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 641631</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E501" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>GRUAS ILICITANAS SL.</t>
         </is>
       </c>
       <c r="F501" s="6" t="inlineStr">
@@ -27806,7 +27806,7 @@
         </is>
       </c>
       <c r="G501" s="4" t="n">
-        <v>998.6900000000001</v>
+        <v>1550.25</v>
       </c>
     </row>
     <row r="502">
@@ -27817,31 +27817,31 @@
       </c>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>1.947,00</t>
+          <t>1.893,00</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON HA-25/F/20/XC1</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E502" s="6" t="inlineStr">
         <is>
-          <t>HORMIGONES DEL VINALOPO SA</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F502" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G502" s="4" t="n">
-        <v>532.5</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="503">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>1.810,00</t>
+          <t>1.865,00</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON LIMPIEZA</t>
+          <t>PRESUPUESTO 641631</t>
         </is>
       </c>
       <c r="E503" s="6" t="inlineStr">
         <is>
-          <t>SEBASTIAN NAVARRO SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F503" s="6" t="inlineStr">
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="G503" s="4" t="n">
-        <v>510</v>
+        <v>998.6900000000001</v>
       </c>
     </row>
     <row r="504">
@@ -27887,31 +27887,31 @@
       </c>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>1.919,00</t>
+          <t>1.972,00</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>CAMION GRUA</t>
+          <t>ACERO LOSA</t>
         </is>
       </c>
       <c r="E504" s="6" t="inlineStr">
         <is>
-          <t>GRUAS ILICITANAS SL.</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F504" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G504" s="4" t="n">
-        <v>500</v>
+        <v>594</v>
       </c>
     </row>
     <row r="505">
@@ -27922,31 +27922,31 @@
       </c>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>1.852,00</t>
+          <t>1.947,00</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>ELECTRICIDAD CUADRO</t>
+          <t>HORMIGON HA-25/F/20/XC1</t>
         </is>
       </c>
       <c r="E505" s="6" t="inlineStr">
         <is>
-          <t>GABRIEL MOYA INSTALACIONES ELECTRICAS SL.</t>
+          <t>HORMIGONES DEL VINALOPO SA</t>
         </is>
       </c>
       <c r="F505" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G505" s="4" t="n">
-        <v>426</v>
+        <v>532.5</v>
       </c>
     </row>
     <row r="506">
@@ -27957,22 +27957,22 @@
       </c>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>1.912,00</t>
+          <t>1.810,00</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>HORMIGON LIMPIEZA</t>
         </is>
       </c>
       <c r="E506" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>SEBASTIAN NAVARRO SL</t>
         </is>
       </c>
       <c r="F506" s="6" t="inlineStr">
@@ -27981,7 +27981,7 @@
         </is>
       </c>
       <c r="G506" s="4" t="n">
-        <v>325</v>
+        <v>510</v>
       </c>
     </row>
     <row r="507">
@@ -27992,22 +27992,22 @@
       </c>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>1.858,00</t>
+          <t>1.919,00</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>CAMION GRUA</t>
         </is>
       </c>
       <c r="E507" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>GRUAS ILICITANAS SL.</t>
         </is>
       </c>
       <c r="F507" s="6" t="inlineStr">
@@ -28016,7 +28016,7 @@
         </is>
       </c>
       <c r="G507" s="4" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
     </row>
     <row r="508">
@@ -28027,22 +28027,22 @@
       </c>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>1.884,00</t>
+          <t>1.852,00</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>TOMA DE MUESTRAS DE HORMIGON FRESCO</t>
+          <t>ELECTRICIDAD CUADRO</t>
         </is>
       </c>
       <c r="E508" s="6" t="inlineStr">
         <is>
-          <t>LABORATORIO DE INGENIERIA Y MEDIO AMBIENTE SA.</t>
+          <t>GABRIEL MOYA INSTALACIONES ELECTRICAS SL.</t>
         </is>
       </c>
       <c r="F508" s="6" t="inlineStr">
@@ -28051,7 +28051,7 @@
         </is>
       </c>
       <c r="G508" s="4" t="n">
-        <v>100</v>
+        <v>426</v>
       </c>
     </row>
     <row r="509">
@@ -28062,22 +28062,22 @@
       </c>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>1.790,00</t>
+          <t>1.912,00</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>FILM PE GALGA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E509" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F509" s="6" t="inlineStr">
@@ -28086,33 +28086,33 @@
         </is>
       </c>
       <c r="G509" s="4" t="n">
-        <v>92.56</v>
+        <v>325</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>1.891,00</t>
+          <t>1.858,00</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E510" s="6" t="inlineStr">
         <is>
-          <t>CONSYDECOR SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F510" s="6" t="inlineStr">
@@ -28121,33 +28121,33 @@
         </is>
       </c>
       <c r="G510" s="4" t="n">
-        <v>1350.83</v>
+        <v>325</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>1.828,00</t>
+          <t>1.884,00</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER MAQUINARIA (+20%)</t>
+          <t>TOMA DE MUESTRAS DE HORMIGON FRESCO</t>
         </is>
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>GOMARIZ SISTEMAS DE ELEVACION SL</t>
+          <t>LABORATORIO DE INGENIERIA Y MEDIO AMBIENTE SA.</t>
         </is>
       </c>
       <c r="F511" s="6" t="inlineStr">
@@ -28156,33 +28156,33 @@
         </is>
       </c>
       <c r="G511" s="4" t="n">
-        <v>498.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>1.914,00</t>
+          <t>1.790,00</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>FILM PE GALGA</t>
         </is>
       </c>
       <c r="E512" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F512" s="6" t="inlineStr">
@@ -28191,42 +28191,42 @@
         </is>
       </c>
       <c r="G512" s="4" t="n">
-        <v>455</v>
+        <v>92.56</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
         <is>
-          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
+          <t>26011 - CASTILLO DE ELDA</t>
         </is>
       </c>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>1.920,00</t>
+          <t>1.970,00</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>PALA EXCAVADORA</t>
+          <t>ARENA MEZCLA</t>
         </is>
       </c>
       <c r="E513" s="6" t="inlineStr">
         <is>
-          <t>PAULINO TOMAS JUAN</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F513" s="6" t="inlineStr">
         <is>
-          <t>IMPUTADO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G513" s="4" t="n">
-        <v>180</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="514">
@@ -28237,22 +28237,22 @@
       </c>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>1.923,00</t>
+          <t>1.974,00</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>RODILLO/PALETINA/MONOCAPA/CEMENTO COLA/LLANA</t>
+          <t>HORMIGON HA-25/B/20</t>
         </is>
       </c>
       <c r="E514" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>CANTERAS Y RECICLADOS SL.</t>
         </is>
       </c>
       <c r="F514" s="6" t="inlineStr">
@@ -28261,7 +28261,7 @@
         </is>
       </c>
       <c r="G514" s="4" t="n">
-        <v>178.56</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="515">
@@ -28272,22 +28272,22 @@
       </c>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>1.839,00</t>
+          <t>1.891,00</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="E515" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>CONSYDECOR SL</t>
         </is>
       </c>
       <c r="F515" s="6" t="inlineStr">
@@ -28296,7 +28296,7 @@
         </is>
       </c>
       <c r="G515" s="4" t="n">
-        <v>104.13</v>
+        <v>1350.83</v>
       </c>
     </row>
     <row r="516">
@@ -28307,206 +28307,206 @@
       </c>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>1.942,00</t>
+          <t>1.828,00</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>IMPRESION PLANOS A3</t>
+          <t>ALQUILER MAQUINARIA (+20%)</t>
         </is>
       </c>
       <c r="E516" s="6" t="inlineStr">
         <is>
-          <t>PLACIDO BOTELLA PEREZ</t>
+          <t>GOMARIZ SISTEMAS DE ELEVACION SL</t>
         </is>
       </c>
       <c r="F516" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G516" s="4" t="n">
-        <v>30.46</v>
+        <v>498.65</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>1.782,00</t>
+          <t>1.914,00</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E517" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F517" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G517" s="4" t="n">
-        <v>2312.04</v>
+        <v>455</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>1.800,00</t>
+          <t>1.920,00</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="D518" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON CIMENTACION</t>
+          <t>PALA EXCAVADORA</t>
         </is>
       </c>
       <c r="E518" s="6" t="inlineStr">
         <is>
-          <t>CANTERAS Y RECICLADOS SL.</t>
+          <t>PAULINO TOMAS JUAN</t>
         </is>
       </c>
       <c r="F518" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G518" s="4" t="n">
-        <v>1196.25</v>
+        <v>180</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>1.804,00</t>
+          <t>1.923,00</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>RODILLO/PALETINA/MONOCAPA/CEMENTO COLA/LLANA</t>
         </is>
       </c>
       <c r="E519" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="F519" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G519" s="4" t="n">
-        <v>975</v>
+        <v>178.56</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>1.764,00</t>
+          <t>1.839,00</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>HIERRO CIMENTACIÓN</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E520" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F520" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G520" s="4" t="n">
-        <v>441.36</v>
+        <v>104.13</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="6" t="inlineStr">
         <is>
-          <t>26020 - OBRA CARLA, PINOSO</t>
+          <t>26017 - OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>1.812,00</t>
+          <t>1.942,00</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>PALA PAULINO</t>
+          <t>IMPRESION PLANOS A3</t>
         </is>
       </c>
       <c r="E521" s="6" t="inlineStr">
         <is>
-          <t>PAULINO TOMAS JUAN</t>
+          <t>PLACIDO BOTELLA PEREZ</t>
         </is>
       </c>
       <c r="F521" s="6" t="inlineStr">
         <is>
-          <t>INVÁLIDO</t>
+          <t>SIN IMPUTAR</t>
         </is>
       </c>
       <c r="G521" s="4" t="n">
-        <v>180</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="522">
@@ -28517,22 +28517,22 @@
       </c>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>1.823,00</t>
+          <t>1.782,00</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>GRUA-CAMION</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E522" s="6" t="inlineStr">
         <is>
-          <t>JOSE LUIS PEREZ JAREÑO</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F522" s="6" t="inlineStr">
@@ -28541,7 +28541,7 @@
         </is>
       </c>
       <c r="G522" s="4" t="n">
-        <v>75</v>
+        <v>2312.04</v>
       </c>
     </row>
     <row r="523">
@@ -28552,22 +28552,22 @@
       </c>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>1.840,00</t>
+          <t>1.800,00</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D523" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>HORMIGON CIMENTACION</t>
         </is>
       </c>
       <c r="E523" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>CANTERAS Y RECICLADOS SL.</t>
         </is>
       </c>
       <c r="F523" s="6" t="inlineStr">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="G523" s="4" t="n">
-        <v>41.9</v>
+        <v>1196.25</v>
       </c>
     </row>
     <row r="524">
@@ -28587,22 +28587,22 @@
       </c>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>1.759,00</t>
+          <t>1.804,00</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D524" s="6" t="inlineStr">
         <is>
-          <t>ARENA Y BARDO</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E524" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F524" s="6" t="inlineStr">
@@ -28611,132 +28611,342 @@
         </is>
       </c>
       <c r="G524" s="4" t="n">
-        <v>30.25</v>
+        <v>975</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
         <is>
-          <t>26022 - OBRA COLEGIO MONOVAR</t>
+          <t>26020 - OBRA CARLA, PINOSO</t>
         </is>
       </c>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>1.927,00</t>
+          <t>1.764,00</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D525" s="6" t="inlineStr">
         <is>
-          <t>EXTENSIBLE 50MT</t>
+          <t>HIERRO CIMENTACIÓN</t>
         </is>
       </c>
       <c r="E525" s="6" t="inlineStr">
         <is>
-          <t>ALVARO BERNAL ZARAZAGA</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F525" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G525" s="4" t="n">
-        <v>63.93</v>
+        <v>441.36</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="6" t="inlineStr">
         <is>
-          <t>26022 - OBRA COLEGIO MONOVAR</t>
+          <t>26020 - OBRA CARLA, PINOSO</t>
         </is>
       </c>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>1.928,00</t>
+          <t>1.812,00</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D526" s="6" t="inlineStr">
         <is>
-          <t>TUBERIA/TAPON/MORTERO/LADRILLO</t>
+          <t>PALA PAULINO</t>
         </is>
       </c>
       <c r="E526" s="6" t="inlineStr">
         <is>
-          <t>ALVARO BERNAL ZARAZAGA</t>
+          <t>PAULINO TOMAS JUAN</t>
         </is>
       </c>
       <c r="F526" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>INVÁLIDO</t>
         </is>
       </c>
       <c r="G526" s="4" t="n">
-        <v>19.13</v>
+        <v>180</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="6" t="inlineStr">
         <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B527" s="6" t="inlineStr">
+        <is>
+          <t>1.823,00</t>
+        </is>
+      </c>
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="D527" s="6" t="inlineStr">
+        <is>
+          <t>GRUA-CAMION</t>
+        </is>
+      </c>
+      <c r="E527" s="6" t="inlineStr">
+        <is>
+          <t>JOSE LUIS PEREZ JAREÑO</t>
+        </is>
+      </c>
+      <c r="F527" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G527" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="6" t="inlineStr">
+        <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B528" s="6" t="inlineStr">
+        <is>
+          <t>1.840,00</t>
+        </is>
+      </c>
+      <c r="C528" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="D528" s="6" t="inlineStr">
+        <is>
+          <t>MATERIAL OBRA</t>
+        </is>
+      </c>
+      <c r="E528" s="6" t="inlineStr">
+        <is>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+        </is>
+      </c>
+      <c r="F528" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G528" s="4" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="6" t="inlineStr">
+        <is>
+          <t>26020 - OBRA CARLA, PINOSO</t>
+        </is>
+      </c>
+      <c r="B529" s="6" t="inlineStr">
+        <is>
+          <t>1.759,00</t>
+        </is>
+      </c>
+      <c r="C529" s="6" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="D529" s="6" t="inlineStr">
+        <is>
+          <t>ARENA Y BARDO</t>
+        </is>
+      </c>
+      <c r="E529" s="6" t="inlineStr">
+        <is>
+          <t>BRICOLAJE BRICOMAN SLU</t>
+        </is>
+      </c>
+      <c r="F529" s="6" t="inlineStr">
+        <is>
+          <t>INVÁLIDO</t>
+        </is>
+      </c>
+      <c r="G529" s="4" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="6" t="inlineStr">
+        <is>
           <t>26022 - OBRA COLEGIO MONOVAR</t>
         </is>
       </c>
-      <c r="B527" s="6" t="inlineStr">
+      <c r="B530" s="6" t="inlineStr">
+        <is>
+          <t>1.973,00</t>
+        </is>
+      </c>
+      <c r="C530" s="6" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="D530" s="6" t="inlineStr">
+        <is>
+          <t>BIG BAG ARENA LAVADA DE RIO</t>
+        </is>
+      </c>
+      <c r="E530" s="6" t="inlineStr">
+        <is>
+          <t>ARENAS DEL VALLE SL</t>
+        </is>
+      </c>
+      <c r="F530" s="6" t="inlineStr">
+        <is>
+          <t>SIN IMPUTAR</t>
+        </is>
+      </c>
+      <c r="G530" s="4" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="6" t="inlineStr">
+        <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="B531" s="6" t="inlineStr">
+        <is>
+          <t>1.927,00</t>
+        </is>
+      </c>
+      <c r="C531" s="6" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="D531" s="6" t="inlineStr">
+        <is>
+          <t>EXTENSIBLE 50MT</t>
+        </is>
+      </c>
+      <c r="E531" s="6" t="inlineStr">
+        <is>
+          <t>ALVARO BERNAL ZARAZAGA</t>
+        </is>
+      </c>
+      <c r="F531" s="6" t="inlineStr">
+        <is>
+          <t>SIN IMPUTAR</t>
+        </is>
+      </c>
+      <c r="G531" s="4" t="n">
+        <v>63.93</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="6" t="inlineStr">
+        <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="B532" s="6" t="inlineStr">
+        <is>
+          <t>1.928,00</t>
+        </is>
+      </c>
+      <c r="C532" s="6" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="D532" s="6" t="inlineStr">
+        <is>
+          <t>TUBERIA/TAPON/MORTERO/LADRILLO</t>
+        </is>
+      </c>
+      <c r="E532" s="6" t="inlineStr">
+        <is>
+          <t>ALVARO BERNAL ZARAZAGA</t>
+        </is>
+      </c>
+      <c r="F532" s="6" t="inlineStr">
+        <is>
+          <t>SIN IMPUTAR</t>
+        </is>
+      </c>
+      <c r="G532" s="4" t="n">
+        <v>19.13</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="6" t="inlineStr">
+        <is>
+          <t>26022 - OBRA COLEGIO MONOVAR</t>
+        </is>
+      </c>
+      <c r="B533" s="6" t="inlineStr">
         <is>
           <t>1.926,00</t>
         </is>
       </c>
-      <c r="C527" s="6" t="inlineStr">
+      <c r="C533" s="6" t="inlineStr">
         <is>
           <t>23/09/2026</t>
         </is>
       </c>
-      <c r="D527" s="6" t="inlineStr">
+      <c r="D533" s="6" t="inlineStr">
         <is>
           <t>PISTOLA/MASILLA/CAPAZO</t>
         </is>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="E533" s="6" t="inlineStr">
         <is>
           <t>ALVARO BERNAL ZARAZAGA</t>
         </is>
       </c>
-      <c r="F527" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <t>SIN IMPUTAR</t>
         </is>
       </c>
-      <c r="G527" s="4" t="n">
+      <c r="G533" s="4" t="n">
         <v>19.04</v>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" s="7" t="inlineStr">
+    <row r="534">
+      <c r="A534" s="7" t="inlineStr">
         <is>
           <t>TOTAL FACTURAS POR OBRA</t>
         </is>
       </c>
-      <c r="B528" s="7" t="n"/>
-      <c r="C528" s="7" t="n"/>
-      <c r="D528" s="7" t="n"/>
-      <c r="E528" s="7" t="n"/>
-      <c r="F528" s="7" t="n"/>
-      <c r="G528" s="8">
-        <f>SUM(G4:G527)</f>
+      <c r="B534" s="7" t="n"/>
+      <c r="C534" s="7" t="n"/>
+      <c r="D534" s="7" t="n"/>
+      <c r="E534" s="7" t="n"/>
+      <c r="F534" s="7" t="n"/>
+      <c r="G534" s="8">
+        <f>SUM(G4:G533)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G527"/>
+  <autoFilter ref="A3:G533"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10160,7 +10160,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2097,7 +2097,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1.989,00</t>
+          <t>FE 022010015806AB0E30252026000000202</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1.988,00</t>
+          <t>193-1946</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.987,00</t>
+          <t>26FP001745</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1.982,00</t>
+          <t>833</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.980,00</t>
+          <t>035651026/00001592</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1.979,00</t>
+          <t>062-0009-254429</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1.964,00</t>
+          <t>B3301553</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1.963,00</t>
+          <t>2026000645</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1.960,00</t>
+          <t>73801/263340</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1.950,00</t>
+          <t>021-0009-268200</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1.944,00</t>
+          <t>005710/A/26/000899</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1.935,00</t>
+          <t>005710/A/26/000930</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1.933,00</t>
+          <t>PTL26-10476</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1.931,00</t>
+          <t>062-0009-253350</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1.930,00</t>
+          <t>261003480</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1.925,00</t>
+          <t>ES0000032279980-0726</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1.924,00</t>
+          <t>ES0000032528846-0826</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1.922,00</t>
+          <t>#F260423105</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1.918,00</t>
+          <t>V-26-08-43557</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1.911,00</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1.910,00</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1.908,00</t>
+          <t>FE26390033654360</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2683,7 +2683,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1.899,00</t>
+          <t>202646070</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1.898,00</t>
+          <t>202651930</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1.897,00</t>
+          <t>V-26-07-22190</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1.882,00</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>1.875,00</t>
+          <t>358898</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2801,7 +2801,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>1.874,00</t>
+          <t>738001/262878</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2827,7 +2827,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1.873,00</t>
+          <t>2026-0264</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1.860,00</t>
+          <t>G26.088</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>1.850,00</t>
+          <t>2602525</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1.846,00</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2927,7 +2927,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>1.845,00</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2953,7 +2953,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>1.842,00</t>
+          <t>1707183734</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>1.827,00</t>
+          <t>005710/A/26/000648</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>1.826,00</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -3031,7 +3031,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>1.825,00</t>
+          <t>18132026FN00000012</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>1.822,00</t>
+          <t>INV/2026/00157</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1.815,00</t>
+          <t>2026/D-1456</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -3109,7 +3109,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>1.814,00</t>
+          <t>73801/262633</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -3135,7 +3135,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>1.811,00</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>1.808,00</t>
+          <t>R/000110-26</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>1.807,00</t>
+          <t>R/000111-26</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1.806,00</t>
+          <t>001-375</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1.805,00</t>
+          <t>#F260308867</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1.799,00</t>
+          <t>V-26-06-27489</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3287,7 +3287,7 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>1.797,00</t>
+          <t>PTL26-07243</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>1.794,00</t>
+          <t>FE26390025724556</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>1.786,00</t>
+          <t>1707159563</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>1.785,00</t>
+          <t>054900026/00002940</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>1.776,00</t>
+          <t>F/002383-26</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -3413,7 +3413,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>1.775,00</t>
+          <t>F/002396-26</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>1.774,00</t>
+          <t>F/002505-26</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>1.768,00</t>
+          <t>F/002807-26</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>1.767,00</t>
+          <t>A - 077794</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>1.766,00</t>
+          <t>02605-00</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3539,7 +3539,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>1.756,00</t>
+          <t>10229032</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3565,7 +3565,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>1.755,00</t>
+          <t>20841706</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>1.754,00</t>
+          <t>105-0006-343393</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -3617,7 +3617,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>1.753,00</t>
+          <t>105-0006-343390</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>1.752,00</t>
+          <t>2602279</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>1.751,00</t>
+          <t>ES/143704</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>1.750,00</t>
+          <t>ES6TE5N4AEUD</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -3721,7 +3721,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>1.749,00</t>
+          <t>ES61HZ5BAEUI</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>1.748,00</t>
+          <t>ES6X86BMAEUD</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -3773,7 +3773,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>1.747,00</t>
+          <t>ES6XPKOKAEUD</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>1.746,00</t>
+          <t>ES6Z0P9ZAEUD</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>1.744,00</t>
+          <t>01/00008</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>1.730,00</t>
+          <t>ES6X14S6AEUD</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>1.728,00</t>
+          <t>062-0006-202651</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -3903,7 +3903,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>1.726,00</t>
+          <t>026-0005-491653</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -3929,7 +3929,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>1.722,00</t>
+          <t>F260253181</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -3955,7 +3955,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1.721,00</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -3977,7 +3977,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>1.720,00</t>
+          <t>062-0006-194616</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>1.716,00</t>
+          <t>FE26390022197863</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>1.706,00</t>
+          <t>2026-0188</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -4073,7 +4073,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>1.699,00</t>
+          <t>26MET01129</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>1.698,00</t>
+          <t>260256</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>1.693,00</t>
+          <t>26FP001018</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4151,7 +4151,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>1.692,00</t>
+          <t>014/26</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4177,7 +4177,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>1.685,00</t>
+          <t>005710/A/26/000556</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>1.681,00</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -4229,7 +4229,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>1.674,00</t>
+          <t>202634415</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>1.673,00</t>
+          <t>f/002361-26</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4277,7 +4277,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>1.667,00</t>
+          <t>FV26-015025</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
@@ -4303,7 +4303,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>1.654,00</t>
+          <t>2026/A-3098</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>1.648,00</t>
+          <t>V-26-05-21273</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>1.646,00</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>1.645,00</t>
+          <t>2601845</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>1.644,00</t>
+          <t>F/002284-26</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>1.643,00</t>
+          <t>623973</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>1.641,00</t>
+          <t>062-0005-181112</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -4481,7 +4481,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>1.640,00</t>
+          <t>2026/A-2796</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>1.639,00</t>
+          <t>FV26-02386</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -4533,7 +4533,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>1.636,00</t>
+          <t>PTL26-05515</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>1.634,00</t>
+          <t>2026/1663</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>1.631,00</t>
+          <t>621610290004972 BIS</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>1.630,00</t>
+          <t>622168</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>1.629,00</t>
+          <t>2026-0119</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>1.628,00</t>
+          <t>ES60002QHM0XHI</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>1.627,00</t>
+          <t>ES6PJKKQAEUD</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>1.626,00</t>
+          <t>ES6000ABL37FLI</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>1.625,00</t>
+          <t>ES6PVYHFAEUD</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
@@ -4763,7 +4763,7 @@
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>1.624,00</t>
+          <t>ES617EMVAEUI</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>1.623,00</t>
+          <t>NL600C2QAQQ1TU</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>1.622,00</t>
+          <t>LU624SXPDAEUI</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>1.621,00</t>
+          <t>ES6193J1AEUI</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -4863,7 +4863,7 @@
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>1.620,00</t>
+          <t>ES600897G8NPRI</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -4889,7 +4889,7 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>1.619,00</t>
+          <t>ES6SBYU8AEUD</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>1.618,00</t>
+          <t>2026-0151</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
@@ -4937,7 +4937,7 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>1.617,00</t>
+          <t>013/26</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
@@ -4963,7 +4963,7 @@
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>1.616,00</t>
+          <t>602104136</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>1.615,00</t>
+          <t>FV26-013108</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>1.614,00</t>
+          <t>PTL26-05264</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>1.613,00</t>
+          <t>F/002066-26</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>1.612,00</t>
+          <t>602104187</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>1.611,00</t>
+          <t>F/002102-26</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>1.610,00</t>
+          <t>FV26-013723</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -5145,7 +5145,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>1.602,00</t>
+          <t>034445/A/26/000346</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>1.601,00</t>
+          <t>18132026FN00000008</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>1.593,00</t>
+          <t>6,22E+14</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>1.592,00</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>1.591,00</t>
+          <t>01262026A100047290</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>1.587,00</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -5301,7 +5301,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>1.583,00</t>
+          <t>005710/A/26/000464</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>1.582,00</t>
+          <t>2601609</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>1.579,00</t>
+          <t>F/001959-26</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
@@ -5379,7 +5379,7 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>1.578,00</t>
+          <t>mar-38</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
@@ -5405,7 +5405,7 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>1.576,00</t>
+          <t>FV26-012726</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
@@ -5431,7 +5431,7 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>1.574,00</t>
+          <t>321348</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -5457,7 +5457,7 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>1.573,00</t>
+          <t>011/26</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>1.570,00</t>
+          <t>#F260142934</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -5509,7 +5509,7 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>1.569,00</t>
+          <t>#F260197959</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>1.568,00</t>
+          <t>M01/0087127250</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -5561,7 +5561,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>1.567,00</t>
+          <t>202628623</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
@@ -5583,7 +5583,7 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>1.566,00</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
@@ -5609,7 +5609,7 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>1.565,00</t>
+          <t>FE26390017782098</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>1.564,00</t>
+          <t>PTL26-05128</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -5657,7 +5657,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>1.544,00</t>
+          <t>L021-631</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>1.543,00</t>
+          <t>L021-632</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
@@ -5709,7 +5709,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>1.542,00</t>
+          <t>062-0004-172456</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
@@ -5735,7 +5735,7 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>1.540,00</t>
+          <t>4735764821</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -5761,7 +5761,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>1.535,00</t>
+          <t>L021-692</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>1.523,00</t>
+          <t>ORD_449_2026/0010348</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>1.517,00</t>
+          <t>V-26-04-21648</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>1.516,00</t>
+          <t>Nº4</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -5865,7 +5865,7 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>1.515,00</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>1.514,00</t>
+          <t>12600544-A</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
@@ -5917,7 +5917,7 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>1.513,00</t>
+          <t>11T/2026/5.617</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>1.512,00</t>
+          <t>BORME/2026/4172</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>1.511,00</t>
+          <t>LU6YVGE2AEUI</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
@@ -5991,7 +5991,7 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>1.507,00</t>
+          <t>L021-603</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>1.506,00</t>
+          <t>L021-604</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>1.503,00</t>
+          <t>FACTE530046956</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>1.502,00</t>
+          <t>26FP000747</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
@@ -6095,7 +6095,7 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>1.501,00</t>
+          <t>DGFCJ2600260649</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>1.498,00</t>
+          <t>060-26</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>1.497,00</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>1.496,00</t>
+          <t>FE26390013469837</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>1.495,00</t>
+          <t>A/856</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>1.493,00</t>
+          <t>ES20260426000008</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>1.280,00</t>
+          <t>4735701206</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
@@ -6273,7 +6273,7 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>1.274,00</t>
+          <t>M01/0087093395</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>1.271,00</t>
+          <t>26FP000621</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -6325,7 +6325,7 @@
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>1.270,00</t>
+          <t>202622887</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
@@ -6347,7 +6347,7 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>1.264,00</t>
+          <t>015795/A/26/000979</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>1.257,00</t>
+          <t>011375/A/26/000711</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>1.255,00</t>
+          <t>V-26-03-32995</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
@@ -6425,7 +6425,7 @@
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>1.254,00</t>
+          <t>G26.037</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>1.245,00</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
@@ -6473,7 +6473,7 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>1.237,00</t>
+          <t>315438</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -6499,7 +6499,7 @@
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>1.236,00</t>
+          <t>602102633</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -6525,7 +6525,7 @@
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>1.235,00</t>
+          <t>26FP000568</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
@@ -6551,7 +6551,7 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>1.233,00</t>
+          <t>01250026/00001912</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>1.232,00</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>1.230,00</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -6629,7 +6629,7 @@
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>1.228,00</t>
+          <t>L021-456</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>1.227,00</t>
+          <t>A20260211</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
@@ -6681,7 +6681,7 @@
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>1.226,00</t>
+          <t>46126/101F00194</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>1.225,00</t>
+          <t>6/201072143</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>1.222,00</t>
+          <t>011375/A/26000600</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>1.219,00</t>
+          <t>011375/V/26/000076</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>1.218,00</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
@@ -6811,7 +6811,7 @@
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>1.199,00</t>
+          <t>311843</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
@@ -6837,7 +6837,7 @@
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>1.198,00</t>
+          <t>26FP000428</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
@@ -6863,7 +6863,7 @@
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>1.197,00</t>
+          <t>005710/A/26/000273</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -6889,7 +6889,7 @@
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>1.196,00</t>
+          <t>26FP000499</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
@@ -6915,7 +6915,7 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>1.195,00</t>
+          <t>46126/101F00186</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -6941,7 +6941,7 @@
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>1.194,00</t>
+          <t>46126/101F00184</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -6967,7 +6967,7 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>1.193,00</t>
+          <t>46126/101F00192</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
@@ -6993,7 +6993,7 @@
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>1.192,00</t>
+          <t>46126/101F00185</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>1.191,00</t>
+          <t>46126/101F00187</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>1.190,00</t>
+          <t>46126/101F00188</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
@@ -7071,7 +7071,7 @@
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>1.189,00</t>
+          <t>011375/V/26/000074</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -7097,7 +7097,7 @@
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>1.187,00</t>
+          <t>26MST03210</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
@@ -7123,7 +7123,7 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>1.184,00</t>
+          <t>L021-421</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -7149,7 +7149,7 @@
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>1.181,00</t>
+          <t>L021-462</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
@@ -7175,7 +7175,7 @@
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>1.171,00</t>
+          <t>20269-0053</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
@@ -7197,7 +7197,7 @@
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>1.170,00</t>
+          <t>2026-0081</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>1.166,00</t>
+          <t>602102263</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -7245,7 +7245,7 @@
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>1.156,00</t>
+          <t>F0018-026-54-0/0000185</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
@@ -7271,7 +7271,7 @@
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>1.147,00</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -7293,7 +7293,7 @@
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>1.146,00</t>
+          <t>A/502</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
@@ -7319,7 +7319,7 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>1.145,00</t>
+          <t>2600088</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -7345,7 +7345,7 @@
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>1.144,00</t>
+          <t>2600106</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>1.143,00</t>
+          <t>FE26390009325438</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -7393,7 +7393,7 @@
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>1.142,00</t>
+          <t>035651026/00000530</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>1.139,00</t>
+          <t>6/201068505</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -7445,7 +7445,7 @@
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>1.138,00</t>
+          <t>2600111</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>1.133,00</t>
+          <t>F0018-026-51-07/0002824</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -7497,7 +7497,7 @@
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>1.128,00</t>
+          <t>ES0000030611120-1225</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
@@ -7519,7 +7519,7 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>1.127,00</t>
+          <t>ES0000030849450-0126</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
@@ -7541,7 +7541,7 @@
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>1.126,00</t>
+          <t>#F260088899</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
@@ -7567,7 +7567,7 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>1.125,00</t>
+          <t>ES0000031076700-0226</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>1.124,00</t>
+          <t>Nº3</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
@@ -7615,7 +7615,7 @@
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>1.123,00</t>
+          <t>V-26-02-18969</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -7641,7 +7641,7 @@
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>1.122,00</t>
+          <t>M01/0087059497</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
@@ -7667,7 +7667,7 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>1.120,00</t>
+          <t>2026-0025</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>1.107,00</t>
+          <t>005710/A/26/000213</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
@@ -7715,7 +7715,7 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>1.106,00</t>
+          <t>26MET01030</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -7741,7 +7741,7 @@
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>1.104,00</t>
+          <t>260084</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
@@ -7767,7 +7767,7 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>1.101,00</t>
+          <t>18132026FN00000003</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>1.094,00</t>
+          <t>INV/2026/00026</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>1.093,00</t>
+          <t>INV/2026/00025</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>1.092,00</t>
+          <t>6/201062718</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
@@ -7871,7 +7871,7 @@
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>1.091,00</t>
+          <t>FE2630005167586</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -7897,7 +7897,7 @@
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>1.090,00</t>
+          <t>M01/0087025989</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
@@ -7923,7 +7923,7 @@
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>1.089,00</t>
+          <t>INV/2026/00027</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -7949,7 +7949,7 @@
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>1.088,00</t>
+          <t>26FP000201</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
@@ -7975,7 +7975,7 @@
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>1.087,00</t>
+          <t>A26-0031</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -8001,7 +8001,7 @@
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>1.086,00</t>
+          <t>6/201062120</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
@@ -8027,7 +8027,7 @@
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>1.085,00</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>1.084,00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
@@ -8079,7 +8079,7 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>1.083,00</t>
+          <t>005710/A/26/000120</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -8105,7 +8105,7 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>1.082,00</t>
+          <t>26FP000199</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
@@ -8131,7 +8131,7 @@
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>1.081,00</t>
+          <t>INV/2026/00014</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -8157,7 +8157,7 @@
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>1.080,00</t>
+          <t>FV26-01517</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>1.078,00</t>
+          <t>18132026FN00000001</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -8209,7 +8209,7 @@
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>1.077,00</t>
+          <t>055513026/00000162</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>1.076,00</t>
+          <t>026-0001-415359</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -8261,7 +8261,7 @@
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>1.075,00</t>
+          <t>INV/2026/00015</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
@@ -8287,7 +8287,7 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>1.074,00</t>
+          <t>618104210</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
@@ -8313,7 +8313,7 @@
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>1.073,00</t>
+          <t>346593</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>1.072,00</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
@@ -8365,7 +8365,7 @@
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>1.071,00</t>
+          <t>DGFCJ2600056841</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
@@ -8391,7 +8391,7 @@
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>1.070,00</t>
+          <t>FE26390001083912</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
@@ -8417,7 +8417,7 @@
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>1.069,00</t>
+          <t>26.801</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>1.068,00</t>
+          <t>031-0001-025095</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>1.067,00</t>
+          <t>6/201058487</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>1.064,00</t>
+          <t>M01/0086992086</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -8521,7 +8521,7 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>FE25390028648675</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
@@ -8547,7 +8547,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>V-26-01-19308</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -8573,7 +8573,7 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>01262026A100017608</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
@@ -8599,7 +8599,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>S101-000147</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>INV/2026/00042</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>INV/2026/00041</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -8677,7 +8677,7 @@
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -8725,7 +8725,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>048304026/00000807</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
@@ -8751,7 +8751,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>L021-81</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -8777,7 +8777,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>FV-26-005110</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
@@ -8803,7 +8803,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>FV26-004716</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -8829,7 +8829,7 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>26FP000345</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
@@ -8855,7 +8855,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>005710/A/26/000210</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
@@ -8881,7 +8881,7 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>INV/2026/00048</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
@@ -8907,7 +8907,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>2026/A-789</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
@@ -8933,7 +8933,7 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>DGFCJ2600124525</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
@@ -8959,7 +8959,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>FV26-004861</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
@@ -8985,7 +8985,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>FV26-004890</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
@@ -9011,7 +9011,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>2600538</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
@@ -9037,7 +9037,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>2600636</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
@@ -9063,7 +9063,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>26FP000292</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>FSIM 1 2026/001807</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>#F260035256</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>1.792,00</t>
+          <t>1613/FA</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -9247,7 +9247,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1.700,00</t>
+          <t>COMPRA RENAULT SCENIC</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -9269,7 +9269,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.660,00</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -9295,7 +9295,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1.220,00</t>
+          <t>FA 821</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -9321,7 +9321,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.209,00</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -9347,7 +9347,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1.179,00</t>
+          <t>FR26-0038</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -9373,7 +9373,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.098,00</t>
+          <t>595/FA</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -9399,7 +9399,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>546/FA</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>552/FA</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9499,7 +9499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tarifa: 20 EUR/hora (configurable)</t>
+          <t>Tarifa: 17,00 EUR/hora (leida del xlsx de mano de obra)</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
         <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4">
         <f>B5*C5</f>
@@ -9569,7 +9569,7 @@
         <v>437</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4">
         <f>B6*C6</f>
@@ -9593,7 +9593,7 @@
         <v>440</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4">
         <f>B7*C7</f>
@@ -9617,7 +9617,7 @@
         <v>643</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4">
         <f>B8*C8</f>
@@ -9641,7 +9641,7 @@
         <v>4119</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="4">
         <f>B9*C9</f>
@@ -9665,7 +9665,7 @@
         <v>750</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" s="4">
         <f>B10*C10</f>
@@ -9689,7 +9689,7 @@
         <v>51</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D11" s="4">
         <f>B11*C11</f>
@@ -9713,7 +9713,7 @@
         <v>592</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="4">
         <f>B12*C12</f>
@@ -9737,7 +9737,7 @@
         <v>1576</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" s="4">
         <f>B13*C13</f>
@@ -9761,7 +9761,7 @@
         <v>537</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D14" s="4">
         <f>B14*C14</f>
@@ -9785,7 +9785,7 @@
         <v>2536</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" s="4">
         <f>B15*C15</f>
@@ -9809,7 +9809,7 @@
         <v>52</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D16" s="4">
         <f>B16*C16</f>
@@ -9833,7 +9833,7 @@
         <v>117</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" s="4">
         <f>B17*C17</f>
@@ -9857,7 +9857,7 @@
         <v>865</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4">
         <f>B18*C18</f>
@@ -9881,7 +9881,7 @@
         <v>718</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D19" s="4">
         <f>B19*C19</f>
@@ -9905,7 +9905,7 @@
         <v>1284</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D20" s="4">
         <f>B20*C20</f>
@@ -9929,7 +9929,7 @@
         <v>304</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="4">
         <f>B21*C21</f>
@@ -9953,7 +9953,7 @@
         <v>221</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D22" s="4">
         <f>B22*C22</f>
@@ -9977,7 +9977,7 @@
         <v>413</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D23" s="4">
         <f>B23*C23</f>
@@ -10001,7 +10001,7 @@
         <v>178</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D24" s="4">
         <f>B24*C24</f>
@@ -10025,7 +10025,7 @@
         <v>681</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D25" s="4">
         <f>B25*C25</f>
@@ -10049,7 +10049,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D26" s="4">
         <f>B26*C26</f>
@@ -10073,7 +10073,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D27" s="4">
         <f>B27*C27</f>
@@ -10143,7 +10143,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D30" s="4">
         <f>B30*C30</f>
@@ -10167,7 +10167,7 @@
         <v>36</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D31" s="4">
         <f>B31*C31</f>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>26/151</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>606659-2</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.167,00</t>
+          <t>FH2600236</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.175,00</t>
+          <t>3475/2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.130,00</t>
+          <t>FH 2600236</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>AS0260189</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1.132,00</t>
+          <t>S/24</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>606659-1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>609212</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>608952</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>607423-1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>1.172,00</t>
+          <t>FV26-007739</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>FV26-005483</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>TND/17</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>TND/18</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>1.659,00</t>
+          <t>F1/2026063</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>1.494,00</t>
+          <t>A-1423/2026</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>1.217,00</t>
+          <t>2026-31</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>2026-3</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>1.537,00</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>2026-18</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>1.486,00</t>
+          <t>F26 00000029</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>1.719,00</t>
+          <t>F260013</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>1.117,00</t>
+          <t>TND/33</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>1.536,00</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>1.216,00</t>
+          <t>VOR 000066</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>2026-19</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>1.165,00</t>
+          <t>A/61</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>1.538,00</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>A/43</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>1.262,00</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>1.114,00</t>
+          <t>TND/35</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>1.962,00</t>
+          <t>A-737/2026</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>1.758,00</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>2026-2</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>1.210,00</t>
+          <t>A-260/2026</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>1.163,00</t>
+          <t>26-004</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>1.118,00</t>
+          <t>2026 C1 45</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>1.119,00</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>1.781,00</t>
+          <t>A-546/2026</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>1.168,00</t>
+          <t>A-225/2026</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>1.109,00</t>
+          <t>A-26/50</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>1.211,00</t>
+          <t>A/157</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>26/131</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>A-26/0000279</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>1.215,00</t>
+          <t>F26/0235</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>FCO-0014226-00002</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>249</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>A/116</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>1.239,00</t>
+          <t>TPV26-02100</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>1.240,00</t>
+          <t>021-0003-170093</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>026-0001-416342</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>1.096,00</t>
+          <t>105197</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>1.830,00</t>
+          <t>2026-68</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>1.273,00</t>
+          <t>2026/36</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>1.655,00</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>1.200,00</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>1.763,00</t>
+          <t>42070</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>1.488,00</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>F2600000012</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>1.809,00</t>
+          <t>77/2026</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>1.789,00</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>1.598,00</t>
+          <t>2026-46</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>1.832,00</t>
+          <t>2026-69</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>1.762,00</t>
+          <t>A-26/0000576</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>1.888,00</t>
+          <t>98-3/2026</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>1.831,00</t>
+          <t>2026-70</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>1.734,00</t>
+          <t>26/2384</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>605458</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>1.780,00</t>
+          <t>F26 00000045</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>1.657,00</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>1.662,00</t>
+          <t>F26-053</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>1.803,00</t>
+          <t>G26.084</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>A-26/0000066</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>1.779,00</t>
+          <t>7200418723</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>1.885,00</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>1.586,00</t>
+          <t>A-26/0001515</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>A-26/0000182</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>1.732,00</t>
+          <t>A-26/0002196</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>1.777,00</t>
+          <t>7300304391</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>1.834,00</t>
+          <t>2026-72</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>1.489,00</t>
+          <t>A-26/0001348</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>1.838,00</t>
+          <t>26/2881</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>1.824,00</t>
+          <t>F1-1-02128</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>1.729,00</t>
+          <t>420</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>1.735,00</t>
+          <t>A-26/194</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>1.656,00</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>1.740,00</t>
+          <t>7300299570</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>1.275,00</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>1.206,00</t>
+          <t>2026-32</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>G26.013</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>1.881,00</t>
+          <t>G26.103</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>1.886,00</t>
+          <t>7300319538</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>1.604,00</t>
+          <t>A-26/0001739</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>1.234,00</t>
+          <t>A-26/0001103</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>1.605,00</t>
+          <t>A-26/156</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>1.861,00</t>
+          <t>A26/770</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>1.561,00</t>
+          <t>A26/368</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>1.259,00</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>1.889,00</t>
+          <t>A-26/0002947</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -14293,7 +14293,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>1.958,00</t>
+          <t>A/157</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>1.095,00</t>
+          <t>609212-2</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>1.738,00</t>
+          <t>058-0006-960004</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>1.745,00</t>
+          <t>457</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>1.818,00</t>
+          <t>A-26/212-</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>1.801,00</t>
+          <t>A-26/212</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>1.771,00</t>
+          <t>2026/A-3836</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>1.244,00</t>
+          <t>615228</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>1.862,00</t>
+          <t>7300307647</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>1.784,00</t>
+          <t>A-26/0002461</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>1.252,00</t>
+          <t>G26.039</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>1.859,00</t>
+          <t>G26.089</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>1.835,00</t>
+          <t>A-26/244</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>1.715,00</t>
+          <t>ASO260560</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>1.948,00</t>
+          <t>A 02026046</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>1.949,00</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>1.876,00</t>
+          <t>A-26/281</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>1.651,00</t>
+          <t>A-26/0001945</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>1.887,00</t>
+          <t>26/618</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>1.836,00</t>
+          <t>A-26/0002695</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>1.741,00</t>
+          <t>062-0006-204596</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>1.913,00</t>
+          <t>A-26/310</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>1.650,00</t>
+          <t>A-26/177</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>1.524,00</t>
+          <t>A-26/138</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>1.201,00</t>
+          <t>A-26/107</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>1.110,00</t>
+          <t>A-26/50</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>1.491,00</t>
+          <t>062-0004-165426</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>A-26/0000441</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>26/00059</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>1.765,00</t>
+          <t>A/4707</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>1.739,00</t>
+          <t>7300299569</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>1.940,00</t>
+          <t>A-26/0003407</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>1.851,00</t>
+          <t>7300307326</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>1.575,00</t>
+          <t>2026/D-970</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>1.580,00</t>
+          <t>01/000006</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>1.892,00</t>
+          <t>A-26/0002646</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>FPL26-017</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>1.783,00</t>
+          <t>A-26/0002460</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>1.848,00</t>
+          <t>7300308667</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>1.731,00</t>
+          <t>A-26/0002195</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>1.241,00</t>
+          <t>b-26/0000474</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>1.717,00</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>1.277,00</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>1.956,00</t>
+          <t>26 1498</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>1.837,00</t>
+          <t>A-26/0002694</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>1.791,00</t>
+          <t>7300305504</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>1.770,00</t>
+          <t>26/2526</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>A-26/0000442</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>1.788,00</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>1.853,00</t>
+          <t>26/576</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>1.723,00</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>1.724,00</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>1.603,00</t>
+          <t>A-26/0001738</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>1.737,00</t>
+          <t>026-005-503303</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>1.813,00</t>
+          <t>7300306828</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>1.773,00</t>
+          <t>FPRAL2606-03407</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>1.713,00</t>
+          <t>F268100664</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>1.849,00</t>
+          <t>FV26-018622</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>1.880,00</t>
+          <t>26/3126</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>1.778,00</t>
+          <t>7200444821</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>1.844,00</t>
+          <t>FV26-019257</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>1.675,00</t>
+          <t>2600706</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>1.742,00</t>
+          <t>062-0006-204604</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>1.890,00</t>
+          <t>A-26/0002948</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>1.608,00</t>
+          <t>2600542</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>1.490,00</t>
+          <t>2600425</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>1.718,00</t>
+          <t>105-0006-340550</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>1.847,00</t>
+          <t>3050210</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>1.702,00</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>1.658,00</t>
+          <t>00-000902/2026</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>1.174,00</t>
+          <t>A/6</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>A/1</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -16972,7 +16972,7 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>1.251,00</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>26/47</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>1.521,00</t>
+          <t>00-000646/2026</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>1.607,00</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>1.522,00</t>
+          <t>00-000643/2026</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>1.560,00</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>1.635,00</t>
+          <t>31/26</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>1.589,00</t>
+          <t>613558</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>1.632,00</t>
+          <t>623752</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>1.483,00</t>
+          <t>26/310</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>1.683,00</t>
+          <t>G26.073</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>1.597,00</t>
+          <t>G26.059</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>1.520,00</t>
+          <t>G26.048</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>A/4</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>1.563,00</t>
+          <t>621346</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>601688</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>1.594,00</t>
+          <t>00-000794/2026</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>1.482,00</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>1.590,00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>1.249,00</t>
+          <t>616208</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>1.704,00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>1.534,00</t>
+          <t>00-000725/2026</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>1.802,00</t>
+          <t>G26.083</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>1.481,00</t>
+          <t>G26.045</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>1.682,00</t>
+          <t>G26.072</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>1.600,00</t>
+          <t>A/11</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>1.599,00</t>
+          <t>G26.061</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>1.637,00</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>1.541,00</t>
+          <t>00-000725</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>1.707,00</t>
+          <t>026-0005-510135</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>1.665,00</t>
+          <t>33/26</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>1.571,00</t>
+          <t>621460</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>1.638,00</t>
+          <t>G26.062</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>1.546,00</t>
+          <t>4735749690</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>1.701,00</t>
+          <t>00-000993/2026</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>1.678,00</t>
+          <t>105-006-339957</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>1.676,00</t>
+          <t>026-0006-515778</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>1.733,00</t>
+          <t>FV26-02893</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>1.705,00</t>
+          <t>026-0006-516703</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>1.666,00</t>
+          <t>2026-0025</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>1.505,00</t>
+          <t>00-000591/2026</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>00-000216/2026</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>1.694,00</t>
+          <t>105-0005-338031</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>1.214,00</t>
+          <t>INV/2026/00067</t>
         </is>
       </c>
       <c r="C230" s="6" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>1.533,00</t>
+          <t>00-000727/2026</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>00-000218/2026</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>1.689,00</t>
+          <t>026-52-07/0008060</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>1.670,00</t>
+          <t>105-0006-340306</t>
         </is>
       </c>
       <c r="C234" s="6" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>1.588,00</t>
+          <t>1 00370</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
@@ -18718,7 +18718,7 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>1.530,00</t>
+          <t>1 000370</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>1.596,00</t>
+          <t>105-0005-337328</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>1.668,00</t>
+          <t>026-51-07/0008723</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>1.679,00</t>
+          <t>026-0006-513975</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>1.687,00</t>
+          <t>062-0005-191421</t>
         </is>
       </c>
       <c r="C240" s="6" t="inlineStr">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>026-0001-401807</t>
         </is>
       </c>
       <c r="C241" s="6" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>1.686,00</t>
+          <t>105-0005-339207</t>
         </is>
       </c>
       <c r="C242" s="6" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>1.677,00</t>
+          <t>105-0006-339914</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>026-0001-397477</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>1.669,00</t>
+          <t>105-0006-340377</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>1.231,00</t>
+          <t>062-0003-153085</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>1.609,00</t>
+          <t>26/00184</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>1.703,00</t>
+          <t>026-0006-522816</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>1.688,00</t>
+          <t>062-0005-191414</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>1.268,00</t>
+          <t>105-0004-331337</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>A/3</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>1.157,00</t>
+          <t>ASO260231</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>1.131,00</t>
+          <t>3486/2026</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>2026/01/ 000491</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>605142-2</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>605142-1</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>605357</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>1.642,00</t>
+          <t>2026/01/002920</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>1.633,00</t>
+          <t>2026/01/ 010088</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>2026/01/003000</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>2026/01/ 000971</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>2026/01/ 000989</t>
         </is>
       </c>
       <c r="C262" s="6" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>2026/01/ 000988</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>2026/01/ 001078</t>
         </is>
       </c>
       <c r="C264" s="6" t="inlineStr">
@@ -19733,7 +19733,7 @@
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>2026/01/ 001217</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>2026/01/ 001408</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>1.112,00</t>
+          <t>031-0003-079564</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
@@ -19838,7 +19838,7 @@
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>1.134,00</t>
+          <t>2026-24</t>
         </is>
       </c>
       <c r="C268" s="6" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>1.208,00</t>
+          <t>A-266/2026</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>1.238,00</t>
+          <t>026-0003-462004</t>
         </is>
       </c>
       <c r="C270" s="6" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>1.111,00</t>
+          <t>021-0002-154831</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>1.761,00</t>
+          <t>A/122</t>
         </is>
       </c>
       <c r="C272" s="6" t="inlineStr">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>1.279,00</t>
+          <t>2026-37</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>1.833,00</t>
+          <t>2026-71</t>
         </is>
       </c>
       <c r="C274" s="6" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>1.710,00</t>
+          <t>TND/109</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>1.709,00</t>
+          <t>TND/108</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>1.176,00</t>
+          <t>621310</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>1.499,00</t>
+          <t>A-26/0001435</t>
         </is>
       </c>
       <c r="C278" s="6" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>1.857,00</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>1.856,00</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C280" s="6" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>1.869,00</t>
+          <t>F00052</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>1.868,00</t>
+          <t>F00051</t>
         </is>
       </c>
       <c r="C282" s="6" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>1.577,00</t>
+          <t>2026-42</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>1.866,00</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>1.485,00</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>1.855,00</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>1.854,00</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
@@ -20584,7 +20584,7 @@
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>1.867,00</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>1.484,00</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>INV/2026/00152</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>INV/2026/00094</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>1.787,00</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>1.115,00</t>
+          <t>26/0922</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>26/0102</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>1.793,00</t>
+          <t>A-26/0002591</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>1.879,00</t>
+          <t>26/4173</t>
         </is>
       </c>
       <c r="C298" s="6" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>1.532,00</t>
+          <t>INV/2026/00335</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>1.258,00</t>
+          <t>INV/2026/00254</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>1.649,00</t>
+          <t>INV/2026/00434</t>
         </is>
       </c>
       <c r="C301" s="6" t="inlineStr">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>1.894,00</t>
+          <t>G26.105</t>
         </is>
       </c>
       <c r="C302" s="6" t="inlineStr">
@@ -21031,7 +21031,7 @@
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>1.711,00</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>1.983,00</t>
+          <t>062-0009-252127</t>
         </is>
       </c>
       <c r="C304" s="6" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>1.652,00</t>
+          <t>26/2694</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>1.572,00</t>
+          <t>7300283565</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>1.585,00</t>
+          <t>031-0005-144343</t>
         </is>
       </c>
       <c r="C307" s="6" t="inlineStr">
@@ -21206,7 +21206,7 @@
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>1.727,00</t>
+          <t>ST26002</t>
         </is>
       </c>
       <c r="C308" s="6" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>1.684,00</t>
+          <t>G26.074</t>
         </is>
       </c>
       <c r="C309" s="6" t="inlineStr">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>1.697,00</t>
+          <t>7300286614</t>
         </is>
       </c>
       <c r="C310" s="6" t="inlineStr">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>1.606,00</t>
+          <t>105-0005-336280</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
@@ -21346,7 +21346,7 @@
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>1.878,00</t>
+          <t>26/4174</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>1.562,00</t>
+          <t>26/2425</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>1.250,00</t>
+          <t>26/1393</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>1.937,00</t>
+          <t>062-0009-250239</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>1.653,00</t>
+          <t>FV26-08532</t>
         </is>
       </c>
       <c r="C316" s="6" t="inlineStr">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>1.941,00</t>
+          <t>A-26/0003409</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>1.690,00</t>
+          <t>026-0005-510149</t>
         </is>
       </c>
       <c r="C318" s="6" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>1.584,00</t>
+          <t>031-0005-144272</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>1.712,00</t>
+          <t>FV26-015871</t>
         </is>
       </c>
       <c r="C320" s="6" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>1.672,00</t>
+          <t>026-51-07/0008724</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>1.955,00</t>
+          <t>026-0009-581851</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>1.936,00</t>
+          <t>062-0009-250185</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>1.743,00</t>
+          <t>260633</t>
         </is>
       </c>
       <c r="C324" s="6" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>1.504,00</t>
+          <t>00-000590/2026</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
@@ -21836,7 +21836,7 @@
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>1.977,00</t>
+          <t>062-0009-254429</t>
         </is>
       </c>
       <c r="C326" s="6" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>1.760,00</t>
+          <t>026-0006-536939</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>1.663,00</t>
+          <t>26/2171</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>1.527,00</t>
+          <t>062-0004-175953</t>
         </is>
       </c>
       <c r="C330" s="6" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>1.695,00</t>
+          <t>105-0005-338032</t>
         </is>
       </c>
       <c r="C331" s="6" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>1.798,00</t>
+          <t>4736118735</t>
         </is>
       </c>
       <c r="C332" s="6" t="inlineStr">
@@ -22081,7 +22081,7 @@
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>1.757,00</t>
+          <t>260341</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>1.529,00</t>
+          <t>105-0004-333399</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>1.725,00</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>1.680,00</t>
+          <t>026-0006-513994</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>1.915,00</t>
+          <t>26/3340</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
@@ -22256,7 +22256,7 @@
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>1.581,00</t>
+          <t>105-0005-335619</t>
         </is>
       </c>
       <c r="C338" s="6" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>1.985,00</t>
+          <t>FV26-023818</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>1.531,00</t>
+          <t>026-0004-479639</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
@@ -22361,7 +22361,7 @@
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>1.959,00</t>
+          <t>FSIM 1 2026/018395</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
@@ -22396,7 +22396,7 @@
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>1.736,00</t>
+          <t>026-0005-503323</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>1.526,00</t>
+          <t>105-0004-334321</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>1.696,00</t>
+          <t>7300286634</t>
         </is>
       </c>
       <c r="C344" s="6" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>1.943,00</t>
+          <t>FSIM 1 2026/019338</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>1.957,00</t>
+          <t>FSIM 1 2026/018503</t>
         </is>
       </c>
       <c r="C346" s="6" t="inlineStr">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>1.595,00</t>
+          <t>2026-48</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>2026-17</t>
         </is>
       </c>
       <c r="C348" s="6" t="inlineStr">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>2026-1</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>G26.009</t>
         </is>
       </c>
       <c r="C350" s="6" t="inlineStr">
@@ -22711,7 +22711,7 @@
       </c>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>26/181</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>G26.008</t>
         </is>
       </c>
       <c r="C352" s="6" t="inlineStr">
@@ -22781,7 +22781,7 @@
       </c>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>G26.012</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
@@ -22816,7 +22816,7 @@
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>026-0002-423838</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>202600569</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
@@ -22886,7 +22886,7 @@
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>1.136,00</t>
+          <t>062-0003-151703</t>
         </is>
       </c>
       <c r="C356" s="6" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>026-0002-423880</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>1.795,00</t>
+          <t>062-0007-213115</t>
         </is>
       </c>
       <c r="C358" s="6" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>1.772,00</t>
+          <t>2026/D-1351</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>1.137,00</t>
+          <t>041-0003-958136</t>
         </is>
       </c>
       <c r="C360" s="6" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>1.796,00</t>
+          <t>041-0007-987322</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>6/201063526</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>1.100,00</t>
+          <t>26/186</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>V/71</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>1.242,00</t>
+          <t>614823</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>1.113,00</t>
+          <t>062-0003-149290</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>1.151,00</t>
+          <t>062-0003-155752</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>1.545,00</t>
+          <t>L00165</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>1.278,00</t>
+          <t>616670</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>1.202,00</t>
+          <t>FH2600346</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
@@ -23411,7 +23411,7 @@
       </c>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>1.129,00</t>
+          <t>FH 2600235</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>V/86</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>1.256,00</t>
+          <t>FH2600348</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>1.525,00</t>
+          <t>G26.049</t>
         </is>
       </c>
       <c r="C374" s="6" t="inlineStr">
@@ -23551,7 +23551,7 @@
       </c>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>1.164,00</t>
+          <t>G26.028</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>1.102,00</t>
+          <t>2/00641</t>
         </is>
       </c>
       <c r="C376" s="6" t="inlineStr">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>1.272,00</t>
+          <t>A/260799</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>1.664,00</t>
+          <t>3508/2026</t>
         </is>
       </c>
       <c r="C378" s="6" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>1.769,00</t>
+          <t>3549/2026</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>1.492,00</t>
+          <t>613788</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>MMC-001/26</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>1.539,00</t>
+          <t>A/996</t>
         </is>
       </c>
       <c r="C382" s="6" t="inlineStr">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>1.661,00</t>
+          <t>3496/2026</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>1.477,00</t>
+          <t>26/330</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>1.253,00</t>
+          <t>G26.038</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>1.478,00</t>
+          <t>G26.044</t>
         </is>
       </c>
       <c r="C386" s="6" t="inlineStr">
@@ -23971,7 +23971,7 @@
       </c>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>1.141,00</t>
+          <t>3485/2026</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>1.207,00</t>
+          <t>A/695</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>1.177,00</t>
+          <t>611490</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>1.097,00</t>
+          <t>610328</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>001100063/26</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
@@ -24177,7 +24177,7 @@
       </c>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>1.480,00</t>
+          <t>A/883</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>1.276,00</t>
+          <t>616437</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>01/000001</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="B396" s="6" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>A/235</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>1.103,00</t>
+          <t>T/00260</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="B398" s="6" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>INV/2026/00055</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>INV/2026/00054</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>1.479,00</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>1.528,00</t>
+          <t>A20260291</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>A20260117</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>A20260123</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="B404" s="6" t="inlineStr">
         <is>
-          <t>1.108,00</t>
+          <t>A20260134</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="B405" s="6" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>605142</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
@@ -24632,7 +24632,7 @@
       </c>
       <c r="B406" s="6" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>609376</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="B407" s="6" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>607423-2</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>1.121,00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
@@ -24737,7 +24737,7 @@
       </c>
       <c r="B409" s="6" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>SF 260021</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>1.267,00</t>
+          <t>F-030</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>1.178,00</t>
+          <t>ene-26</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>471</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="B413" s="6" t="inlineStr">
         <is>
-          <t>1.180,00</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="B414" s="6" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>26/0101</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="B415" s="6" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>606525</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="B416" s="6" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>026-0002-418032</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
@@ -25017,7 +25017,7 @@
       </c>
       <c r="B417" s="6" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>A/20</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
@@ -25052,7 +25052,7 @@
       </c>
       <c r="B418" s="6" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>105-002-322743</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="B419" s="6" t="inlineStr">
         <is>
-          <t>1.116,00</t>
+          <t>26/0923</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="B420" s="6" t="inlineStr">
         <is>
-          <t>1.135,00</t>
+          <t>026-0003-447956</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
@@ -25157,7 +25157,7 @@
       </c>
       <c r="B421" s="6" t="inlineStr">
         <is>
-          <t>1.223,00</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="B422" s="6" t="inlineStr">
         <is>
-          <t>1.155,00</t>
+          <t>026-0002-426922</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
@@ -25227,7 +25227,7 @@
       </c>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>472</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="B424" s="6" t="inlineStr">
         <is>
-          <t>1.212,00</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="B425" s="6" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>MF1-1918</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>026-0002-418056</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>026-0002-423664</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>1.248,00</t>
+          <t>261392</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>1.508,00</t>
+          <t>105-0004-332459</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>1.099,00</t>
+          <t>062-0003-150443</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>1.221,00</t>
+          <t>MF1-19888</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>1.229,00</t>
+          <t>105-0003-328916</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="B433" s="6" t="inlineStr">
         <is>
-          <t>1.213,00</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="B434" s="6" t="inlineStr">
         <is>
-          <t>1.263,00</t>
+          <t>026-0004-471905</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="B435" s="6" t="inlineStr">
         <is>
-          <t>1.269,00</t>
+          <t>105-0004-331415</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="B436" s="6" t="inlineStr">
         <is>
-          <t>1.224,00</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
@@ -25713,7 +25713,7 @@
       </c>
       <c r="B437" s="6" t="inlineStr">
         <is>
-          <t>1.204,00</t>
+          <t>105-003-329830</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="B438" s="6" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>026-0002-423691</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
@@ -25783,7 +25783,7 @@
       </c>
       <c r="B439" s="6" t="inlineStr">
         <is>
-          <t>1.247,00</t>
+          <t>MF1-1989</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
@@ -25818,7 +25818,7 @@
       </c>
       <c r="B440" s="6" t="inlineStr">
         <is>
-          <t>1.173,00</t>
+          <t>SF 260066</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="B441" s="6" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>SF 260020</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
@@ -25888,7 +25888,7 @@
       </c>
       <c r="B442" s="6" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>603119</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>602161</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="B444" s="6" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>601689</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="B445" s="6" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>607424-1</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
@@ -26028,7 +26028,7 @@
       </c>
       <c r="B446" s="6" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>CTD/26 000038</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="B447" s="6" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>607424-2</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
@@ -26098,7 +26098,7 @@
       </c>
       <c r="B448" s="6" t="inlineStr">
         <is>
-          <t>1.518,00</t>
+          <t>26/344</t>
         </is>
       </c>
       <c r="C448" s="6" t="inlineStr">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="B449" s="6" t="inlineStr">
         <is>
-          <t>1.281,00</t>
+          <t>617768</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="B450" s="6" t="inlineStr">
         <is>
-          <t>1.243,00</t>
+          <t>615230</t>
         </is>
       </c>
       <c r="C450" s="6" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="B451" s="6" t="inlineStr">
         <is>
-          <t>1.487,00</t>
+          <t>G26.043</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="B452" s="6" t="inlineStr">
         <is>
-          <t>1.261,00</t>
+          <t>2026/00/004198</t>
         </is>
       </c>
       <c r="C452" s="6" t="inlineStr">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="B453" s="6" t="inlineStr">
         <is>
-          <t>1.519,00</t>
+          <t>G26.050</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="B454" s="6" t="inlineStr">
         <is>
-          <t>1.182,00</t>
+          <t>062-0003-156460</t>
         </is>
       </c>
       <c r="C454" s="6" t="inlineStr">
@@ -26343,7 +26343,7 @@
       </c>
       <c r="B455" s="6" t="inlineStr">
         <is>
-          <t>1.203,00</t>
+          <t>041-0003-962017</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="B456" s="6" t="inlineStr">
         <is>
-          <t>1.266,00</t>
+          <t>CTD/26 000063</t>
         </is>
       </c>
       <c r="C456" s="6" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="B457" s="6" t="inlineStr">
         <is>
-          <t>1.188,00</t>
+          <t>B-26/0000340</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
@@ -26448,7 +26448,7 @@
       </c>
       <c r="B458" s="6" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>CTD/26 00039</t>
         </is>
       </c>
       <c r="C458" s="6" t="inlineStr">
@@ -26483,7 +26483,7 @@
       </c>
       <c r="B459" s="6" t="inlineStr">
         <is>
-          <t>1.246,00</t>
+          <t>062-0003-162313</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
@@ -26518,7 +26518,7 @@
       </c>
       <c r="B460" s="6" t="inlineStr">
         <is>
-          <t>1.260,00</t>
+          <t>CTD/26 000068</t>
         </is>
       </c>
       <c r="C460" s="6" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="B461" s="6" t="inlineStr">
         <is>
-          <t>1.205,00</t>
+          <t>105-0003-329641</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="B462" s="6" t="inlineStr">
         <is>
-          <t>1.183,00</t>
+          <t>062-0003-156440</t>
         </is>
       </c>
       <c r="C462" s="6" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="B463" s="6" t="inlineStr">
         <is>
-          <t>1.265,00</t>
+          <t>A20260268</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="B464" s="6" t="inlineStr">
         <is>
-          <t>1.153,00</t>
+          <t>602-003-153052</t>
         </is>
       </c>
       <c r="C464" s="6" t="inlineStr">
@@ -26693,7 +26693,7 @@
       </c>
       <c r="B465" s="6" t="inlineStr">
         <is>
-          <t>1.186,00</t>
+          <t>105-0003-327844</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="B466" s="6" t="inlineStr">
         <is>
-          <t>1.154,00</t>
+          <t>026-0003-448904</t>
         </is>
       </c>
       <c r="C466" s="6" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>1.185,00</t>
+          <t>00-000411/2026</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>1.152,00</t>
+          <t>062-0003-153069</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
@@ -26833,7 +26833,7 @@
       </c>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>1.932,00</t>
+          <t>A-26/345</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>1.971,00</t>
+          <t>26/723</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>1.901,00</t>
+          <t>A-26/315</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
@@ -26938,7 +26938,7 @@
       </c>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>1.969,00</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
@@ -26973,7 +26973,7 @@
       </c>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>1.929,00</t>
+          <t>026-0009-591697</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>1.967,00</t>
+          <t>2026I2000850</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>1.951,00</t>
+          <t>031-0009-288782</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>1.934,00</t>
+          <t>031-0009-301057</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
@@ -27113,7 +27113,7 @@
       </c>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>1.917,00</t>
+          <t>FV26-022573</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>1.966,00</t>
+          <t>F-04401540</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>1.984,00</t>
+          <t>FV26-023756</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>1.906,00</t>
+          <t>TND/154</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>1.821,00</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
@@ -27284,7 +27284,7 @@
       </c>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>1.872,00</t>
+          <t>641758</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>1.820,00</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>1.961,00</t>
+          <t>A-26/0003239</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>1.939,00</t>
+          <t>A-26/0003408</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>1.916,00</t>
+          <t>26/4745</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>1.938,00</t>
+          <t>26/3572</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
@@ -27494,7 +27494,7 @@
       </c>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>1.905,00</t>
+          <t>026-0008-574780</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>1.900,00</t>
+          <t>026-0009-579169</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>1.953,00</t>
+          <t>062-0009-246220</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>1.945,00</t>
+          <t>026-0009-584095</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>1.921,00</t>
+          <t>F0018-026-51-07/0014627</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
@@ -27669,7 +27669,7 @@
       </c>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>1.952,00</t>
+          <t>062-0009-246244</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>1.909,00</t>
+          <t>F0018-026-51-07/0015088</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>1.968,00</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>1.954,00</t>
+          <t>041-0009-000837</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>1.946,00</t>
+          <t>F0018-026-52-07/0014366</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>1.904,00</t>
+          <t>026-0008-574800</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>1.903,00</t>
+          <t>026-0008-576011</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>1.841,00</t>
+          <t>F2641339</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>1.829,00</t>
+          <t>26/566</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>1.895,00</t>
+          <t>H-26-003731</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>1.907,00</t>
+          <t>26/652</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>1.843,00</t>
+          <t>S/92</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>1.877,00</t>
+          <t>0/000853</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>1.893,00</t>
+          <t>G26.104</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>1.865,00</t>
+          <t>641631</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>1.972,00</t>
+          <t>26/721</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>1.947,00</t>
+          <t>H-26-004255</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>1.810,00</t>
+          <t>S/87</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
@@ -28299,7 +28299,7 @@
       </c>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>1.919,00</t>
+          <t>0/000934</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>1.852,00</t>
+          <t>A26/108</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>1.912,00</t>
+          <t>G26.107</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>1.858,00</t>
+          <t>G26.090</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
@@ -28439,7 +28439,7 @@
       </c>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>1.884,00</t>
+          <t>A-701/2026</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>1.790,00</t>
+          <t>026-0007-543619</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
@@ -28509,7 +28509,7 @@
       </c>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>1.981,00</t>
+          <t>FV26-024018</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>1.975,00</t>
+          <t>026-0009-593707</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>1.976,00</t>
+          <t>FV26-024513</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
@@ -28614,7 +28614,7 @@
       </c>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>1.970,00</t>
+          <t>026-0009-593885</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
@@ -28649,7 +28649,7 @@
       </c>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>1.978,00</t>
+          <t>FACT202610591</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>1.986,00</t>
+          <t>FV26-023639</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>1.974,00</t>
+          <t>L00360</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>1.891,00</t>
+          <t>A-26/0002949</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>1.828,00</t>
+          <t>0/004471</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
@@ -28824,7 +28824,7 @@
       </c>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>1.914,00</t>
+          <t>G26.108</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
@@ -28859,7 +28859,7 @@
       </c>
       <c r="B527" s="6" t="inlineStr">
         <is>
-          <t>1.920,00</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
@@ -28894,7 +28894,7 @@
       </c>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>1.923,00</t>
+          <t>FV26-020474</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
@@ -28929,7 +28929,7 @@
       </c>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>1.839,00</t>
+          <t>A/1697</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>1.942,00</t>
+          <t>A/1382</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>1.782,00</t>
+          <t>A/1583</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>1.800,00</t>
+          <t>L00292</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>1.804,00</t>
+          <t>G26.085</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>1.764,00</t>
+          <t>26/508</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>1.812,00</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
@@ -29174,7 +29174,7 @@
       </c>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>1.823,00</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
@@ -29209,7 +29209,7 @@
       </c>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>1.840,00</t>
+          <t>A/1722</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
@@ -29244,7 +29244,7 @@
       </c>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>1.759,00</t>
+          <t>026-0006-536923</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
@@ -29279,7 +29279,7 @@
       </c>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>1.973,00</t>
+          <t>001-3098</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>1.927,00</t>
+          <t>A-26/0005322.</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>1.928,00</t>
+          <t>A-26/0005321</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>1.926,00</t>
+          <t>A-26/0005323</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>52020.39999999999</v>
+        <v>67766.98</v>
       </c>
       <c r="D18" s="6">
         <f>C18/C27</f>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1284</v>
+        <v>1332</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>34338.63</v>
+        <v>33313.12</v>
       </c>
       <c r="D24" s="6">
         <f>C24/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>33313.12</v>
+        <v>32986.99</v>
       </c>
       <c r="D24" s="6">
         <f>C24/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>32986.99</v>
+        <v>34049.67</v>
       </c>
       <c r="D24" s="6">
         <f>C24/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2536</v>
+        <v>2564</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
     </font>
   </fonts>
   <fills count="4">
@@ -110,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +124,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -489,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1503,39 +1508,276 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>OBRAS SIN CERTIFICACION (6) - 26,471.80 EUR de perdida</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2100 - OBRA MURO VECINO CAMPO</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <f>C36*$B$7</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A36,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A36,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>D36+E36+F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>B36-G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="6">
+        <f>IF(B36=0,0,G36/B36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4">
+        <f>C37*$B$7</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A37,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A37,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>D37+E37+F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>B37-G37</f>
+        <v/>
+      </c>
+      <c r="I37" s="6">
+        <f>IF(B37=0,0,G37/B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>24001 - OBRA C/IBIZA, ASPE (CASA CABO)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4">
+        <f>C38*$B$7</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A38,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A38,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>D38+E38+F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="4">
+        <f>B38-G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>IF(B38=0,0,G38/B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2400 - ARREGLOS OBRAS ARAQUE Y MAQUEDA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4">
+        <f>C39*$B$7</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A39,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A39,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>D39+E39+F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>B39-G39</f>
+        <v/>
+      </c>
+      <c r="I39" s="6">
+        <f>IF(B39=0,0,G39/B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4">
+        <f>C40*$B$7</f>
+        <v/>
+      </c>
+      <c r="E40" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A40,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F40" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A40,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G40" s="4">
+        <f>D40+E40+F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="4">
+        <f>B40-G40</f>
+        <v/>
+      </c>
+      <c r="I40" s="6">
+        <f>IF(B40=0,0,G40/B40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4">
+        <f>C41*$B$7</f>
+        <v/>
+      </c>
+      <c r="E41" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A41,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F41" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A41,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G41" s="4">
+        <f>D41+E41+F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="4">
+        <f>B41-G41</f>
+        <v/>
+      </c>
+      <c r="I41" s="6">
+        <f>IF(B41=0,0,G41/B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B35" s="8">
-        <f>SUM(B12:B34)</f>
-        <v/>
-      </c>
-      <c r="C35" s="7">
-        <f>SUM(C12:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D12:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="8">
-        <f>SUM(E12:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="8">
-        <f>SUM(F12:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="8">
-        <f>SUM(G12:G34)</f>
-        <v/>
-      </c>
-      <c r="H35" s="8">
-        <f>SUM(H12:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="7">
-        <f>IF(B35=0,0,G35/B35)</f>
+      <c r="B42" s="9">
+        <f>SUM(B12:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="8">
+        <f>SUM(C12:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>SUM(D12:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="9">
+        <f>SUM(E12:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="9">
+        <f>SUM(F12:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="9">
+        <f>SUM(G12:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="9">
+        <f>SUM(H12:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="8">
+        <f>IF(B42=0,0,G42/B42)</f>
         <v/>
       </c>
     </row>
@@ -2013,21 +2255,21 @@
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>TOTAL CERTIFICACIONES</t>
         </is>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="9">
         <f>SUM(C4:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <f>SUM(D4:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9139,19 +9381,19 @@
       <c r="F279" s="6" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="7" t="n"/>
-      <c r="B280" s="7" t="n"/>
-      <c r="C280" s="7" t="inlineStr">
+      <c r="A280" s="8" t="n"/>
+      <c r="B280" s="8" t="n"/>
+      <c r="C280" s="8" t="inlineStr">
         <is>
           <t>TOTAL GASTOS GENERALES</t>
         </is>
       </c>
-      <c r="D280" s="7" t="n"/>
-      <c r="E280" s="8">
+      <c r="D280" s="8" t="n"/>
+      <c r="E280" s="9">
         <f>SUM(E4:E279)</f>
         <v/>
       </c>
-      <c r="F280" s="7" t="n"/>
+      <c r="F280" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9449,19 +9691,19 @@
       <c r="F12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>TOTAL VEHICULOS</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="8">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9">
         <f>SUM(E4:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="7" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10182,22 +10424,22 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <f>SUM(B5:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9">
         <f>SUM(D5:D31)</f>
         <v/>
       </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10513,7 +10755,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS - CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
@@ -10533,16 +10775,16 @@
       <c r="C29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>TOTAL GASTOS DIRECTOS</t>
         </is>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <f>SUM(B4:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="7" t="n"/>
+      <c r="C30" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10579,7 +10821,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Usa los filtros desplegables en la fila 3 para buscar por proyecto, proveedor, etc.</t>
         </is>
@@ -28644,7 +28886,7 @@
     <row r="521">
       <c r="A521" s="6" t="inlineStr">
         <is>
-          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS - CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
         </is>
       </c>
       <c r="B521" s="6" t="inlineStr">
@@ -28679,7 +28921,7 @@
     <row r="522">
       <c r="A522" s="6" t="inlineStr">
         <is>
-          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS - CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
+          <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
         </is>
       </c>
       <c r="B522" s="6" t="inlineStr">
@@ -29412,17 +29654,17 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="7" t="inlineStr">
+      <c r="A543" s="8" t="inlineStr">
         <is>
           <t>TOTAL FACTURAS POR OBRA</t>
         </is>
       </c>
-      <c r="B543" s="7" t="n"/>
-      <c r="C543" s="7" t="n"/>
-      <c r="D543" s="7" t="n"/>
-      <c r="E543" s="7" t="n"/>
-      <c r="F543" s="7" t="n"/>
-      <c r="G543" s="8">
+      <c r="B543" s="8" t="n"/>
+      <c r="C543" s="8" t="n"/>
+      <c r="D543" s="8" t="n"/>
+      <c r="E543" s="8" t="n"/>
+      <c r="F543" s="8" t="n"/>
+      <c r="G543" s="9">
         <f>SUM(G4:G542)</f>
         <v/>
       </c>
@@ -29903,20 +30145,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <f>SUM(B6:B28)</f>
         <v/>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>SUM(C6:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="9">
         <f>SUM(D6:D28)</f>
         <v/>
       </c>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1508,7 +1508,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>OBRAS SIN CERTIFICACION (6) - 26,471.80 EUR de perdida</t>
+          <t>OBRAS SIN CERTIFICACION (7) - 52,362.80 EUR de perdida</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1671,7 +1671,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
+          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
@@ -1708,7 +1708,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
+          <t>26010 - PROYECTO 4 BASCULAS EN SILOS - Paraje de los Rincones S,N - Poligono 3, parcelas 94 y 113 - Algueña (Alicante)</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
@@ -1743,41 +1743,78 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>26021 - OBRA CRISTINA RESTAURANTE, ALICANTE</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4">
+        <f>C42*$B$7</f>
+        <v/>
+      </c>
+      <c r="E42" s="4">
+        <f>SUMIF('Gastos por Proyecto'!A:A,A42,'Gastos por Proyecto'!B:B)</f>
+        <v/>
+      </c>
+      <c r="F42" s="4">
+        <f>SUMIF('Mano de Obra'!A:A,A42,'Mano de Obra'!D:D)</f>
+        <v/>
+      </c>
+      <c r="G42" s="4">
+        <f>D42+E42+F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="4">
+        <f>B42-G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="6">
+        <f>IF(B42=0,0,G42/B42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>TOTAL GENERAL</t>
         </is>
       </c>
-      <c r="B42" s="9">
-        <f>SUM(B12:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="8">
-        <f>SUM(C12:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="9">
-        <f>SUM(D12:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="9">
-        <f>SUM(E12:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="9">
-        <f>SUM(F12:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="9">
-        <f>SUM(G12:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="9">
-        <f>SUM(H12:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="8">
-        <f>IF(B42=0,0,G42/B42)</f>
+      <c r="B43" s="9">
+        <f>SUM(B12:B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="8">
+        <f>SUM(C12:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="9">
+        <f>SUM(D12:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="9">
+        <f>SUM(E12:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="9">
+        <f>SUM(F12:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="9">
+        <f>SUM(G12:G42)</f>
+        <v/>
+      </c>
+      <c r="H43" s="9">
+        <f>SUM(H12:H42)</f>
+        <v/>
+      </c>
+      <c r="I43" s="8">
+        <f>IF(B43=0,0,G43/B43)</f>
         <v/>
       </c>
     </row>
@@ -10284,7 +10321,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
+          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA (COLEGIO MAYOR)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -10332,7 +10369,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2100 - MURO VECINO</t>
+          <t>2100 - OBRA MURO VECINO CAMPO</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -10355,7 +10392,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2600 - OBRA CAMPO</t>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2564</v>
+        <v>2588</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>718</v>
+        <v>746</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10181,7 +10181,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>67766.98</v>
+        <v>63374.44</v>
       </c>
       <c r="D18" s="6">
         <f>C18/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -28006,7 +28006,7 @@
       </c>
       <c r="F489" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G489" s="4" t="n">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="F490" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G490" s="4" t="n">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="F496" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G496" s="4" t="n">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="F497" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G497" s="4" t="n">
@@ -28321,7 +28321,7 @@
       </c>
       <c r="F498" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G498" s="4" t="n">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="F499" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G499" s="4" t="n">
@@ -28391,7 +28391,7 @@
       </c>
       <c r="F500" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G500" s="4" t="n">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="F502" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G502" s="4" t="n">
@@ -28496,7 +28496,7 @@
       </c>
       <c r="F503" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G503" s="4" t="n">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="F504" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G504" s="4" t="n">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="F506" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G506" s="4" t="n">
@@ -28986,7 +28986,7 @@
       </c>
       <c r="F517" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G517" s="4" t="n">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="F528" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G528" s="4" t="n">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F529" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G529" s="4" t="n">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="F530" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G530" s="4" t="n">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="F531" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G531" s="4" t="n">
@@ -30176,7 +30176,7 @@
       </c>
       <c r="F551" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G551" s="4" t="n">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="F552" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G552" s="4" t="n">
@@ -30246,7 +30246,7 @@
       </c>
       <c r="F553" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G553" s="4" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2588</v>
+        <v>2612</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1376</v>
+        <v>1400</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>15047.28</v>
+        <v>15019.02</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10837,7 +10837,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2640</v>
+        <v>2664</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10815,7 +10815,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2664</v>
+        <v>2688</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1452</v>
+        <v>1428</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2688</v>
+        <v>2736</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2736</v>
+        <v>2788</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>746</v>
+        <v>782</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2786</v>
+        <v>2818</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1434</v>
+        <v>1450</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2818</v>
+        <v>2854</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1450</v>
+        <v>1466</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2854</v>
+        <v>2890</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1466</v>
+        <v>1482</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2890</v>
+        <v>2938</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'Gastos Generales'!E304</f>
+        <f>'Gastos Generales'!E305</f>
         <v/>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:F305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2337,7 +2337,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GASTOS GENERALES (300 facturas)</t>
+          <t>GASTOS GENERALES (301 facturas)</t>
         </is>
       </c>
     </row>
@@ -2376,138 +2376,134 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>202657783</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>DESBROCE SOLAR</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>MARCOS GALIANO POVEDA</t>
-        </is>
-      </c>
+          <t>CONECTA 3 - OCTUBRE</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="4" t="n">
-        <v>260</v>
+        <v>54.36</v>
       </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>602109077</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>DESBROCE SOLAR</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>COMERFONSA SL</t>
+          <t>MARCOS GALIANO POVEDA</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>292.29</v>
+        <v>260</v>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>26FP001789</t>
+          <t>602109077</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>84.34</v>
+        <v>292.29</v>
       </c>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>26FP001789</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>E.S. PINOSO S.L.</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="n">
-        <v>260</v>
+        <v>84.34</v>
       </c>
       <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000970</t>
+          <t>691</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="4" t="n">
-        <v>94.04000000000001</v>
+        <v>260</v>
       </c>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>26FP001878</t>
+          <t>005710/A/26/000970</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2517,18 +2513,18 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>21.12</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>26FP001879</t>
+          <t>26FP001878</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -2547,188 +2543,188 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>73.13</v>
+        <v>21.12</v>
       </c>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>F0018-026-51-07/0014627</t>
+          <t>26FP001879</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>DISCO CORTE/GUANTES</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>45.03</v>
+        <v>73.13</v>
       </c>
       <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>A26-0218</t>
+          <t>F0018-026-51-07/0014627</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>BILLD IN 2026</t>
+          <t>DISCO CORTE/GUANTES</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SIDE QUEST APES, S.L.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1138.8</v>
+        <v>45.03</v>
       </c>
       <c r="F12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>FE26390029900065</t>
+          <t>A26-0218</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>NATURGY JULIO</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
+          <t>BILLD IN 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SIDE QUEST APES, S.L.</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="n">
-        <v>31.71</v>
+        <v>1138.8</v>
       </c>
       <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>01262026A100076291</t>
+          <t>FE26390029900065</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>HIDRAQUA AGOSTO</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
-        </is>
-      </c>
+          <t>NATURGY JULIO</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="4" t="n">
-        <v>30.65</v>
+        <v>31.71</v>
       </c>
       <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>01262026A100076291</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL AGOSTO</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
+          <t>HIDRAQUA AGOSTO</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="n">
-        <v>260</v>
+        <v>30.65</v>
       </c>
       <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F260480780</t>
+          <t>614</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>HOLDED SEPTIEMBRE</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL AGOSTO</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="4" t="n">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00210</t>
+          <t>F260480780</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>PISTOLA ATAR SUP TJEP</t>
+          <t>HOLDED SEPTIEMBRE</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1395</v>
+        <v>59</v>
       </c>
       <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1-02943</t>
+          <t>INV/2026/00210</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -2738,101 +2734,101 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>OBSEQUIO CLIENTES</t>
+          <t>PISTOLA ATAR SUP TJEP</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>DISJOVER BEBIDAS SL.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>533.58</v>
+        <v>1395</v>
       </c>
       <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>062-0010-259415</t>
+          <t>1-02943</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>CLAVADORA</t>
+          <t>OBSEQUIO CLIENTES</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>DISJOVER BEBIDAS SL.</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>531.27</v>
+        <v>533.58</v>
       </c>
       <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>V-26-09-24286</t>
+          <t>062-0010-259415</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SEPTIEMBRE</t>
+          <t>CLAVADORA</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2045.71</v>
+        <v>531.27</v>
       </c>
       <c r="F20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2.007,00</t>
+          <t>V-26-09-24286</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>PLENOIL SEPTIEMBRE</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>JYSK DBL IBERIA SLU</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-23.69</v>
+        <v>2045.71</v>
       </c>
       <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2.005,00</t>
+          <t>2.007,00</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -2842,180 +2838,180 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>HERRAMIENTA</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>JYSK DBL IBERIA SLU</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1086</v>
+        <v>-23.69</v>
       </c>
       <c r="F22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-0299</t>
+          <t>2.005,00</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
+          <t>HERRAMIENTA</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LEROY MERLIN ESPAÑA SL</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="n">
-        <v>360.15</v>
+        <v>-1086</v>
       </c>
       <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>2026-0299</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>DUCHA PINOSO</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>SALTOKI ELCHE SL.</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="4" t="n">
-        <v>265.05</v>
+        <v>360.15</v>
       </c>
       <c r="F24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>062-0009- 253350</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>HERRAMIENTA</t>
+          <t>DUCHA PINOSO</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>SALTOKI ELCHE SL.</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1086.1</v>
+        <v>265.05</v>
       </c>
       <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>635927488</t>
+          <t>062-0009- 253350</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>HERRAMIENTA</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>JYSK DBL IBERIA SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>44.28</v>
+        <v>1086.1</v>
       </c>
       <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>062-0009-255228</t>
+          <t>635927488</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL VARIO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>JYSK DBL IBERIA SLU</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>195.07</v>
+        <v>44.28</v>
       </c>
       <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>FE 022010015806AB0E30252026000000202</t>
+          <t>062-0009-255228</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL VARIO</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>GALP ENERGIA ESPAÑA SAU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>51.8</v>
+        <v>195.07</v>
       </c>
       <c r="F28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>193-1946</t>
+          <t>FE 022010015806AB0E30252026000000202</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -3025,23 +3021,23 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TECNONOIL SOLUTIONS SOCIEDAD ANONIMA.</t>
+          <t>GALP ENERGIA ESPAÑA SAU</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>74.37</v>
+        <v>51.8</v>
       </c>
       <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>26FP001745</t>
+          <t>193-1946</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -3051,23 +3047,23 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>TECNONOIL SOLUTIONS SOCIEDAD ANONIMA.</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>71.5</v>
+        <v>74.37</v>
       </c>
       <c r="F30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>26FP001745</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -3077,23 +3073,23 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE NAVARRO ROBLES SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>16.53</v>
+        <v>71.5</v>
       </c>
       <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>035651026/00001592</t>
+          <t>833</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -3103,18 +3099,18 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>VECTALIA OIL SL.</t>
+          <t>HIJOS DE NAVARRO ROBLES SL</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>16.14</v>
+        <v>16.53</v>
       </c>
       <c r="F32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>062-0009-254429</t>
+          <t>035651026/00001592</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -3124,184 +3120,184 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>BOMBILLAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>VECTALIA OIL SL.</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>32.21</v>
+        <v>16.14</v>
       </c>
       <c r="F33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1.965,00</t>
+          <t>062-0009-254429</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTO ANULADO</t>
+          <t>BOMBILLAS</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-60</v>
+        <v>32.21</v>
       </c>
       <c r="F34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>B3301553</t>
+          <t>1.965,00</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>DOMINIO EMAILS</t>
+          <t>RECONOCIMIENTO ANULADO</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>DINAHOSTING SL</t>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>-60</v>
       </c>
       <c r="F35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026000645</t>
+          <t>B3301553</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>DOMINIO EMAILS</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>EURO MARKWT FANG XIANG MAO S.L.</t>
+          <t>DINAHOSTING SL</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.83</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>73801/263340</t>
+          <t>2026000645</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTO ANULADO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+          <t>EURO MARKWT FANG XIANG MAO S.L.</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>60</v>
+        <v>10.83</v>
       </c>
       <c r="F37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>021-0009-268200</t>
+          <t>73801/263340</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>BRIDAS</t>
+          <t>RECONOCIMIENTO ANULADO</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.43</v>
+        <v>60</v>
       </c>
       <c r="F38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000899</t>
+          <t>021-0009-268200</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>BRIDAS</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>82.83</v>
+        <v>6.43</v>
       </c>
       <c r="F39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000930</t>
+          <t>005710/A/26/000899</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -3315,66 +3311,66 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>78.89</v>
+        <v>82.83</v>
       </c>
       <c r="F40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>PTL26-10476</t>
+          <t>005710/A/26/000930</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BEBIDA PARA OBRA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>56.4</v>
+        <v>78.89</v>
       </c>
       <c r="F41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>062-0009-253350</t>
+          <t>PTL26-10476</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>HERRAMIENTA</t>
+          <t>BEBIDA PARA OBRA</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1086</v>
+        <v>56.4</v>
       </c>
       <c r="F42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>261003480</t>
+          <t>062-0009-253350</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -3384,55 +3380,59 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>HERRAMIENTA</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>MORAMON SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>91.23999999999999</v>
+        <v>1086</v>
       </c>
       <c r="F43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>ES0000032279980-0726</t>
+          <t>261003480</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>VIA T - JULIO</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>MORAMON SL</t>
+        </is>
+      </c>
       <c r="E44" s="4" t="n">
-        <v>15</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="F44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>ES0000032528846-0826</t>
+          <t>ES0000032279980-0726</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>VIA T - AGOSTO</t>
+          <t>VIA T - JULIO</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -3444,85 +3444,81 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>#F260423105</t>
+          <t>ES0000032528846-0826</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>HOLDED AGOSTO</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
-        </is>
-      </c>
+          <t>VIA T - AGOSTO</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="4" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>V-26-08-43557</t>
+          <t>#F260423105</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL AGOSTO</t>
+          <t>HOLDED AGOSTO</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>846.6900000000001</v>
+        <v>59</v>
       </c>
       <c r="F47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>V-26-08-43557</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE SEPTIEMBRE</t>
+          <t>PLENOIL AGOSTO</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>350</v>
+        <v>846.6900000000001</v>
       </c>
       <c r="F48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3532,7 +3528,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE AGOSTO</t>
+          <t>ALQUILER NAVE SEPTIEMBRE</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3548,99 +3544,99 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>FE26390033654360</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>NATURGY AGOSTO</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr"/>
+          <t>ALQUILER NAVE AGOSTO</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
+        </is>
+      </c>
       <c r="E50" s="4" t="n">
-        <v>53.13</v>
+        <v>350</v>
       </c>
       <c r="F50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>202646070</t>
+          <t>FE26390033654360</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - AGOSTO</t>
+          <t>NATURGY AGOSTO</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="4" t="n">
-        <v>54.51</v>
+        <v>53.13</v>
       </c>
       <c r="F51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>202651930</t>
+          <t>202646070</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3  - SEPTIEMBRE</t>
+          <t>CONECTA 3 - AGOSTO</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
       <c r="E52" s="4" t="n">
-        <v>54.36</v>
+        <v>54.51</v>
       </c>
       <c r="F52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>V-26-07-22190</t>
+          <t>202651930</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL JULIO</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>PLENOIL SL.</t>
-        </is>
-      </c>
+          <t>CONECTA 3  - SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
       <c r="E53" s="4" t="n">
-        <v>1699.09</v>
+        <v>54.36</v>
       </c>
       <c r="F53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>V-26-07-22190</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3650,45 +3646,45 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL JULIO</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr"/>
+          <t>PLENOIL JULIO</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>PLENOIL SL.</t>
+        </is>
+      </c>
       <c r="E54" s="4" t="n">
-        <v>260</v>
+        <v>1699.09</v>
       </c>
       <c r="F54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>358898</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>CONCORDY SA</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL JULIO</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
       <c r="E55" s="4" t="n">
-        <v>74.39</v>
+        <v>260</v>
       </c>
       <c r="F55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>738001/262878</t>
+          <t>358898</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3698,23 +3694,23 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTOS MEDICOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+          <t>CONCORDY SA</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>175.8</v>
+        <v>74.39</v>
       </c>
       <c r="F56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-0264</t>
+          <t>738001/262878</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3724,97 +3720,97 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr"/>
+          <t>RECONOCIMIENTOS MEDICOS</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="n">
-        <v>360.15</v>
+        <v>175.8</v>
       </c>
       <c r="F57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>G26.088</t>
+          <t>2026-0264</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr"/>
       <c r="E58" s="4" t="n">
-        <v>260</v>
+        <v>360.15</v>
       </c>
       <c r="F58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2602525</t>
+          <t>G26.088</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>CUERDA</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>64.7</v>
+        <v>260</v>
       </c>
       <c r="F59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2602525</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>LAVADO COHES</t>
+          <t>CUERDA</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>FARES JAVIER HERNANDEZ OSORIO</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>59</v>
+        <v>64.7</v>
       </c>
       <c r="F60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3824,7 +3820,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>LAVADO OPEL COMBO</t>
+          <t>LAVADO COHES</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -3833,66 +3829,66 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>1707183734</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>SACO ASPIRADORA</t>
+          <t>LAVADO OPEL COMBO</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>HILTI ESPAÑOLA SA</t>
+          <t>FARES JAVIER HERNANDEZ OSORIO</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>74.76000000000001</v>
+        <v>35</v>
       </c>
       <c r="F62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000648</t>
+          <t>1707183734</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>SACO ASPIRADORA</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>HILTI ESPAÑOLA SA</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16.53</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="F63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>005710/A/26/000648</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -3902,175 +3898,175 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE JULIO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>350</v>
+        <v>16.53</v>
       </c>
       <c r="F64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>18132026FN00000012</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ALQUILER NAVE JULIO</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>22.97</v>
+        <v>350</v>
       </c>
       <c r="F65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00157</t>
+          <t>18132026FN00000012</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>DISCO DE CORTE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>187.5</v>
+        <v>22.97</v>
       </c>
       <c r="F66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026/D-1456</t>
+          <t>INV/2026/00157</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>SPRAY PINTURA</t>
+          <t>DISCO DE CORTE</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>19.31</v>
+        <v>187.5</v>
       </c>
       <c r="F67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>73801/262633</t>
+          <t>2026/D-1456</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>RECONOCIMIENTO MÉDICO</t>
+          <t>SPRAY PINTURA</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>175.8</v>
+        <v>19.31</v>
       </c>
       <c r="F68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>73801/262633</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>ASESORÍA LABORAL JUNIO</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr"/>
+          <t>RECONOCIMIENTO MÉDICO</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>EUROPREVEN SERVICIOS DE PREVENCION DE RIESGOS LABORALES SL</t>
+        </is>
+      </c>
       <c r="E69" s="4" t="n">
-        <v>260</v>
+        <v>175.8</v>
       </c>
       <c r="F69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>R/000110-26</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>TAPA POROS HIERRO GALVANIZADO</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
-        </is>
-      </c>
+          <t>ASESORÍA LABORAL JUNIO</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr"/>
       <c r="E70" s="4" t="n">
-        <v>-17</v>
+        <v>260</v>
       </c>
       <c r="F70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>R/000111-26</t>
+          <t>R/000110-26</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4080,7 +4076,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>FONTANERIA</t>
+          <t>TAPA POROS HIERRO GALVANIZADO</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -4089,218 +4085,218 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>-29.68</v>
+        <v>-17</v>
       </c>
       <c r="F71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>001-375</t>
+          <t>R/000111-26</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>MAQUINARIA HONDA</t>
+          <t>FONTANERIA</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>POLI PRIMI SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1983.47</v>
+        <v>-29.68</v>
       </c>
       <c r="F72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>#F260308867</t>
+          <t>001-375</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>HOLDED JUNIO</t>
+          <t>MAQUINARIA HONDA</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>POLI PRIMI SL</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>59</v>
+        <v>1983.47</v>
       </c>
       <c r="F73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>V-26-06-27489</t>
+          <t>#F260308867</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL JUNIO</t>
+          <t>HOLDED JUNIO</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1745.38</v>
+        <v>59</v>
       </c>
       <c r="F74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>PTL26-07243</t>
+          <t>V-26-06-27489</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>VARIOS COMPRA</t>
+          <t>PLENOIL JUNIO</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>134.86</v>
+        <v>1745.38</v>
       </c>
       <c r="F75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>FE26390025724556</t>
+          <t>PTL26-07243</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>NATURGY JUNIO</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr"/>
+          <t>VARIOS COMPRA</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>CASH LEVANTE SL</t>
+        </is>
+      </c>
       <c r="E76" s="4" t="n">
-        <v>30.35</v>
+        <v>134.86</v>
       </c>
       <c r="F76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>1707159563</t>
+          <t>FE26390025724556</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>SACO PARA POLVO</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>HILTI ESPAÑOLA SA</t>
-        </is>
-      </c>
+          <t>NATURGY JUNIO</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr"/>
       <c r="E77" s="4" t="n">
-        <v>100.28</v>
+        <v>30.35</v>
       </c>
       <c r="F77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>054900026/00002940</t>
+          <t>1707159563</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>SACO PARA POLVO</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>JR VIDAL RICO SL</t>
+          <t>HILTI ESPAÑOLA SA</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>65.69</v>
+        <v>100.28</v>
       </c>
       <c r="F78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>F/002383-26</t>
+          <t>054900026/00002940</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>JR VIDAL RICO SL</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>11.83</v>
+        <v>65.69</v>
       </c>
       <c r="F79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>F/002396-26</t>
+          <t>F/002383-26</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -4310,7 +4306,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>ARANDELAS</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -4319,24 +4315,24 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>43.75</v>
+        <v>11.83</v>
       </c>
       <c r="F80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>F/002505-26</t>
+          <t>F/002396-26</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>FONTANERIA</t>
+          <t>ARANDELAS</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -4345,24 +4341,24 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>29.68</v>
+        <v>43.75</v>
       </c>
       <c r="F81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>F/002807-26</t>
+          <t>F/002505-26</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>CONTROLADOR PH</t>
+          <t>FONTANERIA</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -4371,140 +4367,140 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>34.83</v>
+        <v>29.68</v>
       </c>
       <c r="F82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>A - 077794</t>
+          <t>F/002807-26</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OFICINA</t>
+          <t>CONTROLADOR PH</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>LOPA PAPER SL.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>34.83</v>
       </c>
       <c r="F83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>02605-00</t>
+          <t>A - 077794</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>VIA T</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr"/>
+          <t>MATERIAL OFICINA</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>LOPA PAPER SL.</t>
+        </is>
+      </c>
       <c r="E84" s="4" t="n">
-        <v>2.69</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>10229032</t>
+          <t>02605-00</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>EXPLOTACION ESTACION DE SERVICIO SA</t>
-        </is>
-      </c>
+          <t>VIA T</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr"/>
       <c r="E85" s="4" t="n">
-        <v>72.16</v>
+        <v>2.69</v>
       </c>
       <c r="F85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>20841706</t>
+          <t>10229032</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>DM BRICO SL</t>
+          <t>EXPLOTACION ESTACION DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>218.18</v>
+        <v>72.16</v>
       </c>
       <c r="F86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>105-0006-343393</t>
+          <t>20841706</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>FOCOS LUZ</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>DM BRICO SL</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>66.06999999999999</v>
+        <v>218.18</v>
       </c>
       <c r="F87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>105-0006-343390</t>
+          <t>105-0006-343393</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4514,7 +4510,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>PH REDUCTOR</t>
+          <t>FOCOS LUZ</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -4523,14 +4519,14 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>19.48</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="F88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2602279</t>
+          <t>105-0006-343390</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
@@ -4540,137 +4536,137 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>RUEDAS</t>
+          <t>PH REDUCTOR</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>20.38</v>
+        <v>19.48</v>
       </c>
       <c r="F89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>ES/143704</t>
+          <t>2602279</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL / BERMUDAS</t>
+          <t>RUEDAS</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>FORMATO DIGITAL ACTIVIDADES PUBLICITARIAS SOCIEDAD LIMITADA.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>142.6</v>
+        <v>20.38</v>
       </c>
       <c r="F90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>ES6TE5N4AEUD</t>
+          <t>ES/143704</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>COLCHA</t>
+          <t>ROPA LABORAL / BERMUDAS</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>FORMATO DIGITAL ACTIVIDADES PUBLICITARIAS SOCIEDAD LIMITADA.</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>50.4</v>
+        <v>142.6</v>
       </c>
       <c r="F91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>ES61HZ5BAEUI</t>
+          <t>ES6TE5N4AEUD</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>COMPRA AMAZON</t>
+          <t>COLCHA</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>28.92</v>
+        <v>50.4</v>
       </c>
       <c r="F92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>ES6X86BMAEUD</t>
+          <t>ES61HZ5BAEUI</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>FUNDA JARDIN</t>
+          <t>COMPRA AMAZON</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>53.71</v>
+        <v>28.92</v>
       </c>
       <c r="F93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>ES6XPKOKAEUD</t>
+          <t>ES6X86BMAEUD</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>PAGO TJ AMAZON</t>
+          <t>FUNDA JARDIN</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -4679,19 +4675,19 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>40.25</v>
+        <v>53.71</v>
       </c>
       <c r="F94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>ES6Z0P9ZAEUD</t>
+          <t>ES6XPKOKAEUD</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -4705,440 +4701,444 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>24.29</v>
+        <v>40.25</v>
       </c>
       <c r="F95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>01/00008</t>
+          <t>ES6Z0P9ZAEUD</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>HORAS JARDINERIA</t>
+          <t>PAGO TJ AMAZON</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>MARCOS GALIANO POVEDA</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>178</v>
+        <v>24.29</v>
       </c>
       <c r="F96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>ES6X14S6AEUD</t>
+          <t>01/00008</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>ARRANCADOR COCHE</t>
+          <t>HORAS JARDINERIA</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>MARCOS GALIANO POVEDA</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>57.84</v>
+        <v>178</v>
       </c>
       <c r="F97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>062-0006-202651</t>
+          <t>ES6X14S6AEUD</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>ARRANCADOR COCHE</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>27.26</v>
+        <v>57.84</v>
       </c>
       <c r="F98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>026-0005-491653</t>
+          <t>062-0006-202651</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>CALZADO LABORAL</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>79.67</v>
+        <v>27.26</v>
       </c>
       <c r="F99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>F260253181</t>
+          <t>026-0005-491653</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>HOLDED MAYO</t>
+          <t>CALZADO LABORAL</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>59</v>
+        <v>79.67</v>
       </c>
       <c r="F100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>F260253181</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>ASESORÍA MAYO</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr"/>
+          <t>HOLDED MAYO</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>HOLDED TECHNOLOGIES SL.</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="n">
-        <v>260</v>
+        <v>59</v>
       </c>
       <c r="F101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>062-0006-194616</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
-        </is>
-      </c>
+          <t>ASESORÍA MAYO</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr"/>
       <c r="E102" s="4" t="n">
-        <v>15.19</v>
+        <v>260</v>
       </c>
       <c r="F102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>FE26390022197863</t>
+          <t>062-0006-194616</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>NATURGY MAYO</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr"/>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>LEROY MERLIN ESPAÑA SL</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="n">
-        <v>25.3</v>
+        <v>15.19</v>
       </c>
       <c r="F103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>1.708,00</t>
+          <t>FE26390022197863</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>MAQUINA MULTIHERRAMIENTA</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>DETECTALIA EUROPE SL</t>
-        </is>
-      </c>
+          <t>NATURGY MAYO</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr"/>
       <c r="E104" s="4" t="n">
-        <v>3304.96</v>
+        <v>25.3</v>
       </c>
       <c r="F104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-0188</t>
+          <t>1.708,00</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL JUNIO</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr"/>
+          <t>MAQUINA MULTIHERRAMIENTA</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>DETECTALIA EUROPE SL</t>
+        </is>
+      </c>
       <c r="E105" s="4" t="n">
-        <v>360.15</v>
+        <v>3304.96</v>
       </c>
       <c r="F105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>26MET01129</t>
+          <t>2026-0188</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL JUNIO</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="4" t="n">
-        <v>8.26</v>
+        <v>360.15</v>
       </c>
       <c r="F106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>260256</t>
+          <t>26MET01129</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>TAPON LATON</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>ROSALIA MARTINEZ RUIZ</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1.69</v>
+        <v>8.26</v>
       </c>
       <c r="F107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>26FP001018</t>
+          <t>260256</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>TAPON LATON</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>ROSALIA MARTINEZ RUIZ</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>82.22</v>
+        <v>1.69</v>
       </c>
       <c r="F108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>014/26</t>
+          <t>26FP001018</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>CHINAWIN IBERICA SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>46.28</v>
+        <v>82.22</v>
       </c>
       <c r="F109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000556</t>
+          <t>014/26</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ROPA LABORAL</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>55.23</v>
+        <v>46.28</v>
       </c>
       <c r="F110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>005710/A/26/000556</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE JUNIO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>350</v>
+        <v>55.23</v>
       </c>
       <c r="F111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>202634415</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - MAYO</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr"/>
+          <t>ALQUILER NAVE JUNIO</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
+        </is>
+      </c>
       <c r="E112" s="4" t="n">
-        <v>34.53</v>
+        <v>350</v>
       </c>
       <c r="F112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>f/002361-26</t>
+          <t>202634415</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -5148,75 +5148,71 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>TAPA POROS HIERRO GALVANIZADO</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
-        </is>
-      </c>
+          <t>CONECTA 3 - MAYO</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr"/>
       <c r="E113" s="4" t="n">
-        <v>17</v>
+        <v>34.53</v>
       </c>
       <c r="F113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>FV26-015025</t>
+          <t>f/002361-26</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>ARANDELAS</t>
+          <t>TAPA POROS HIERRO GALVANIZADO</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>10.8</v>
+        <v>17</v>
       </c>
       <c r="F114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026/A-3098</t>
+          <t>FV26-015025</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>ARANDELAS</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>140.21</v>
+        <v>10.8</v>
       </c>
       <c r="F115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>V-26-05-21273</t>
+          <t>2026/A-3098</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
@@ -5226,133 +5222,133 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL MAYO</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1764.79</v>
+        <v>140.21</v>
       </c>
       <c r="F116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>V-26-05-21273</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO LABORAL ABRIL</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr"/>
+          <t>PLENOIL MAYO</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>PLENOIL SL.</t>
+        </is>
+      </c>
       <c r="E117" s="4" t="n">
-        <v>260</v>
+        <v>1764.79</v>
       </c>
       <c r="F117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2601845</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>MALLA GALLINERO</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>FERRELDA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO LABORAL ABRIL</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr"/>
       <c r="E118" s="4" t="n">
-        <v>92.98999999999999</v>
+        <v>260</v>
       </c>
       <c r="F118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>F/002284-26</t>
+          <t>2601845</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>CLORO PISCINA</t>
+          <t>MALLA GALLINERO</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>18.79</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>623973</t>
+          <t>F/002284-26</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 623973</t>
+          <t>CLORO PISCINA</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>313.22</v>
+        <v>18.79</v>
       </c>
       <c r="F120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>062-0005-181112</t>
+          <t>623973</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>PRESUPUESTO 623973</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -5361,40 +5357,40 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>43.87</v>
+        <v>313.22</v>
       </c>
       <c r="F121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026/A-2796</t>
+          <t>062-0005-181112</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>161.32</v>
+        <v>43.87</v>
       </c>
       <c r="F122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>FV26-02386</t>
+          <t>2026/A-2796</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -5404,175 +5400,175 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>LA AVENIDA CERAMICAS SL.</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>1096.03</v>
+        <v>161.32</v>
       </c>
       <c r="F123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>PTL26-05515</t>
+          <t>FV26-02386</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>LA AVENIDA CERAMICAS SL.</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>86.34999999999999</v>
+        <v>1096.03</v>
       </c>
       <c r="F124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026/1663</t>
+          <t>PTL26-05515</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>SERVICIO REPARACION</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>EVOTEK FUTURE SL.</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>78.51000000000001</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="F125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>621610290004972 BIS</t>
+          <t>2026/1663</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>IVA NO DEDUCIBLE</t>
+          <t>SERVICIO REPARACION</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>ACTION RETAIL SPAIN SL.</t>
+          <t>EVOTEK FUTURE SL.</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>0.86</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="F126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>622168</t>
+          <t>621610290004972 BIS</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 622168</t>
+          <t>IVA NO DEDUCIBLE</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>ACTION RETAIL SPAIN SL.</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>3981.68</v>
+        <v>0.86</v>
       </c>
       <c r="F127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-0119</t>
+          <t>622168</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr"/>
+          <t>PRESUPUESTO 622168</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>LEROY MERLIN ESPAÑA SL</t>
+        </is>
+      </c>
       <c r="E128" s="4" t="n">
-        <v>360.15</v>
+        <v>3981.68</v>
       </c>
       <c r="F128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>ES60002QHM0XHI</t>
+          <t>2026-0119</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>VENTOSA VIBRADORA</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>DIAMOND-SERVICE PRO TOOLS SL.</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr"/>
       <c r="E129" s="4" t="n">
-        <v>163.64</v>
+        <v>360.15</v>
       </c>
       <c r="F129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>ES6PJKKQAEUD</t>
+          <t>ES60002QHM0XHI</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -5582,23 +5578,23 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>INFLADORA</t>
+          <t>VENTOSA VIBRADORA</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>DIAMOND-SERVICE PRO TOOLS SL.</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>19.99</v>
+        <v>163.64</v>
       </c>
       <c r="F130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>ES6000ABL37FLI</t>
+          <t>ES6PJKKQAEUD</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -5608,97 +5604,101 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>ALMODILLA PULIDO DIAMANTE</t>
+          <t>INFLADORA</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>EASTAR SUPER HARD TOOLS SOCIEDAD LIMITADA.</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>40.04</v>
+        <v>19.99</v>
       </c>
       <c r="F131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>ES6PVYHFAEUD</t>
+          <t>ES6000ABL37FLI</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>GRIFO</t>
+          <t>ALMODILLA PULIDO DIAMANTE</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>EASTAR SUPER HARD TOOLS SOCIEDAD LIMITADA.</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>117.35</v>
+        <v>40.04</v>
       </c>
       <c r="F132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>ES617EMVAEUI</t>
+          <t>ES6PVYHFAEUD</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>citronela</t>
+          <t>GRIFO</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>6.12</v>
+        <v>117.35</v>
       </c>
       <c r="F133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>NL600C2QAQQ1TU</t>
+          <t>ES617EMVAEUI</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>ETIQUETS</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr"/>
+          <t>citronela</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
+        </is>
+      </c>
       <c r="E134" s="4" t="n">
-        <v>8.26</v>
+        <v>6.12</v>
       </c>
       <c r="F134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>LU624SXPDAEUI</t>
+          <t>NL600C2QAQQ1TU</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -5708,33 +5708,29 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>CANTU acondicionador</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
-        </is>
-      </c>
+          <t>ETIQUETS</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr"/>
       <c r="E135" s="4" t="n">
-        <v>4.84</v>
+        <v>8.26</v>
       </c>
       <c r="F135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>ES6193J1AEUI</t>
+          <t>LU624SXPDAEUI</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>DISPENSADOR AGUA</t>
+          <t>CANTU acondicionador</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -5743,14 +5739,14 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>8.23</v>
+        <v>4.84</v>
       </c>
       <c r="F136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>ES600897G8NPRI</t>
+          <t>ES6193J1AEUI</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -5760,123 +5756,123 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>BOMBILLAS</t>
+          <t>DISPENSADOR AGUA</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>AIGOTECH ONSYNK SL</t>
+          <t>AMAZON EU SARL SUCURSAL EN ESPAÑA.</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>33.75</v>
+        <v>8.23</v>
       </c>
       <c r="F137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>ES6SBYU8AEUD</t>
+          <t>ES600897G8NPRI</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>SOPORTE MADERA</t>
+          <t>BOMBILLAS</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
+          <t>AIGOTECH ONSYNK SL</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>17.97</v>
+        <v>33.75</v>
       </c>
       <c r="F138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-0151</t>
+          <t>ES6SBYU8AEUD</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE-FISCAL</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr"/>
+          <t>SOPORTE MADERA</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
+        </is>
+      </c>
       <c r="E139" s="4" t="n">
-        <v>360.15</v>
+        <v>17.97</v>
       </c>
       <c r="F139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>013/26</t>
+          <t>2026-0151</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>CHALECO</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>CHINAWIN IBERICA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE-FISCAL</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
       <c r="E140" s="4" t="n">
-        <v>70.25</v>
+        <v>360.15</v>
       </c>
       <c r="F140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>602104136</t>
+          <t>013/26</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>TUBO GOTEO</t>
+          <t>CHALECO</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>COMERFONSA SL</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>70.27</v>
+        <v>70.25</v>
       </c>
       <c r="F141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>FV26-013108</t>
+          <t>602104136</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
@@ -5886,49 +5882,49 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>CEMENTO/RESINA</t>
+          <t>TUBO GOTEO</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>18.53</v>
+        <v>70.27</v>
       </c>
       <c r="F142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>PTL26-05264</t>
+          <t>FV26-013108</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>CEMENTO/RESINA</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>CASH LEVANTE SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>47.5</v>
+        <v>18.53</v>
       </c>
       <c r="F143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>F/002066-26</t>
+          <t>PTL26-05264</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
@@ -5943,44 +5939,44 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>17.96</v>
+        <v>47.5</v>
       </c>
       <c r="F144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>602104187</t>
+          <t>F/002066-26</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>MANGUERA</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>COMERFONSA SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>18.99</v>
+        <v>17.96</v>
       </c>
       <c r="F145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>F/002102-26</t>
+          <t>602104187</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
@@ -5990,80 +5986,80 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>MANGUERA</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>69.44</v>
+        <v>18.99</v>
       </c>
       <c r="F146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>FV26-013723</t>
+          <t>F/002102-26</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>QUITACEMENTO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>37.96</v>
+        <v>69.44</v>
       </c>
       <c r="F147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>034445/A/26/000346</t>
+          <t>FV26-013723</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>QUITACEMENTO</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>58.13</v>
+        <v>37.96</v>
       </c>
       <c r="F148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>18132026FN00000008</t>
+          <t>034445/A/26/000346</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -6073,179 +6069,179 @@
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>22.27</v>
+        <v>58.13</v>
       </c>
       <c r="F149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>6,2161E+14</t>
+          <t>18132026FN00000008</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>ACTION RETAIL SPAIN SL.</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>4.09</v>
+        <v>22.27</v>
       </c>
       <c r="F150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6,2161E+14</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE MAYO</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>ACTION RETAIL SPAIN SL.</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>350</v>
+        <v>4.09</v>
       </c>
       <c r="F151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>01262026A100047290</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>AGUA 2026/02</t>
+          <t>ALQUILER NAVE MAYO</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>30.65</v>
+        <v>350</v>
       </c>
       <c r="F152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>260980</t>
+          <t>01262026A100047290</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>CAMBIO NOMBRE RENAULT MEGANE SCENIC</t>
+          <t>AGUA 2026/02</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>ACCIONGEST ASEGEST SLP.</t>
+          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>190.16</v>
+        <v>30.65</v>
       </c>
       <c r="F153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000464</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>CAMBIO NOMBRE RENAULT MEGANE SCENIC</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>ACCIONGEST ASEGEST SLP.</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>68.20999999999999</v>
+        <v>190.16</v>
       </c>
       <c r="F154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>2601609</t>
+          <t>005710/A/26/000464</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>49.92</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>F/001959-26</t>
+          <t>2601609</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -6255,18 +6251,18 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>16.36</v>
+        <v>49.92</v>
       </c>
       <c r="F156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>mar-38</t>
+          <t>F/001959-26</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -6276,49 +6272,49 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>GLEM S.L.</t>
+          <t>SUMINISTROS DOMINGUEZ AGUILERA ELDA SL.</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>17.2</v>
+        <v>16.36</v>
       </c>
       <c r="F157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>FV26-012726</t>
+          <t>mar-38</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>FIANZA AHOYADORA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>GLEM S.L.</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>247.93</v>
+        <v>17.2</v>
       </c>
       <c r="F158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>321348</t>
+          <t>FV26-012726</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
@@ -6328,85 +6324,85 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>FIANZA AHOYADORA</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>DISTRIBUCION QING YONG SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>247.93</v>
       </c>
       <c r="F159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>011/26</t>
+          <t>321348</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL PRUEBA</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>CHINAWIN IBERICA SL</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>59.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>#F260142934</t>
+          <t>011/26</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>HOLDED MARZO</t>
+          <t>ROPA LABORAL PRUEBA</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
+          <t>CHINAWIN IBERICA SL</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="F161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>#F260197959</t>
+          <t>#F260142934</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>HOLDED ABRIL</t>
+          <t>HOLDED MARZO</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -6422,81 +6418,81 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>M01/0087127250</t>
+          <t>#F260197959</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL ABRIL</t>
+          <t>HOLDED ABRIL</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>23.93</v>
+        <v>59</v>
       </c>
       <c r="F163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>202628623</t>
+          <t>M01/0087127250</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 - MAYO</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr"/>
+          <t>JAZZTEL ABRIL</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>ORANGE ESPAGNE SAU.</t>
+        </is>
+      </c>
       <c r="E164" s="4" t="n">
-        <v>34.68</v>
+        <v>23.93</v>
       </c>
       <c r="F164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>202628623</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t>Mª CARMEN PRIETO AVELLAN</t>
-        </is>
-      </c>
+          <t>CONECTA 3 - MAYO</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr"/>
       <c r="E165" s="4" t="n">
-        <v>65</v>
+        <v>34.68</v>
       </c>
       <c r="F165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>FE26390017782098</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
@@ -6506,71 +6502,71 @@
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>NATURGY ABRIL</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr"/>
+          <t>ROPA LABORAL</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>Mª CARMEN PRIETO AVELLAN</t>
+        </is>
+      </c>
       <c r="E166" s="4" t="n">
-        <v>23.6</v>
+        <v>65</v>
       </c>
       <c r="F166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>PTL26-05128</t>
+          <t>FE26390017782098</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>BEBIDA OBRA</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>CASH LEVANTE SL</t>
-        </is>
-      </c>
+          <t>NATURGY ABRIL</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr"/>
       <c r="E167" s="4" t="n">
-        <v>61.8</v>
+        <v>23.6</v>
       </c>
       <c r="F167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>L021-631</t>
+          <t>PTL26-05128</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>BEBIDA OBRA</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>CASH LEVANTE SL</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="F168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>L021-632</t>
+          <t>L021-631</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
@@ -6589,14 +6585,14 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>33.73</v>
+        <v>57.85</v>
       </c>
       <c r="F169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>062-0004-172456</t>
+          <t>L021-632</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
@@ -6606,153 +6602,153 @@
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>89.83</v>
+        <v>33.73</v>
       </c>
       <c r="F170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>4735764821</t>
+          <t>062-0004-172456</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>RADIAL ANGULAR</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>WURTH ESPAÑA SA</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>511.2</v>
+        <v>89.83</v>
       </c>
       <c r="F171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>L021-692</t>
+          <t>4735764821</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>RADIAL ANGULAR</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>WURTH ESPAÑA SA</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>76.16</v>
+        <v>511.2</v>
       </c>
       <c r="F172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>ORD_449_2026/0010348</t>
+          <t>L021-692</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>COMPRA IKEA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>IKEA IBERICA SAU</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>52.03</v>
+        <v>76.16</v>
       </c>
       <c r="F173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>V-26-04-21648</t>
+          <t>ORD_449_2026/0010348</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL ABRIL</t>
+          <t>COMPRA IKEA</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>IKEA IBERICA SAU</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1729.15</v>
+        <v>52.03</v>
       </c>
       <c r="F174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>Nº4</t>
+          <t>V-26-04-21648</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE ABRIL</t>
+          <t>PLENOIL ABRIL</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>350</v>
+        <v>1729.15</v>
       </c>
       <c r="F175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>Nº4</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
@@ -6762,75 +6758,75 @@
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>ROPA LABORAL</t>
+          <t>ALQUILER NAVE ABRIL</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Mª CARMEN PRIETO AVELLAN</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>833.5</v>
+        <v>350</v>
       </c>
       <c r="F176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>12600544-A</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>COMPRAVENTA PARTICIPACIONES SOCIALES</t>
+          <t>ROPA LABORAL</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>ALEJANDRO PEREZ MARTINEZ</t>
+          <t>Mª CARMEN PRIETO AVELLAN</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>381.09</v>
+        <v>833.5</v>
       </c>
       <c r="F177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>11T/2026/5.617</t>
+          <t>12600544-A</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>REGISTRO MERCANTIL COMPRA EMPRESA</t>
+          <t>COMPRAVENTA PARTICIPACIONES SOCIALES</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>REGISTRO MERCANTIL DE ALICANTE, S.C.</t>
+          <t>ALEJANDRO PEREZ MARTINEZ</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>97.81</v>
+        <v>381.09</v>
       </c>
       <c r="F178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>BORME/2026/4172</t>
+          <t>11T/2026/5.617</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -6840,71 +6836,71 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>PUBLICACION BORME</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr"/>
+          <t>REGISTRO MERCANTIL COMPRA EMPRESA</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>REGISTRO MERCANTIL DE ALICANTE, S.C.</t>
+        </is>
+      </c>
       <c r="E179" s="4" t="n">
-        <v>28.72</v>
+        <v>97.81</v>
       </c>
       <c r="F179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>LU6YVGE2AEUI</t>
+          <t>BORME/2026/4172</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>COMPRA AMAZON</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>AMAZON EU SARL LUXEMBURGO</t>
-        </is>
-      </c>
+          <t>PUBLICACION BORME</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr"/>
       <c r="E180" s="4" t="n">
-        <v>80.08</v>
+        <v>28.72</v>
       </c>
       <c r="F180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>L021-603</t>
+          <t>LU6YVGE2AEUI</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>COMPRA AMAZON</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>AMAZON EU SARL LUXEMBURGO</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>60.33</v>
+        <v>80.08</v>
       </c>
       <c r="F181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>L021-604</t>
+          <t>L021-603</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
@@ -6923,19 +6919,19 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>45.83</v>
+        <v>60.33</v>
       </c>
       <c r="F182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>FACTE530046956</t>
+          <t>L021-604</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -6945,23 +6941,23 @@
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>NOVELDIESEL SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>87.26000000000001</v>
+        <v>45.83</v>
       </c>
       <c r="F183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>26FP000747</t>
+          <t>FACTE530046956</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -6971,248 +6967,248 @@
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>NOVELDIESEL SL</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="F184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>DGFCJ2600260649</t>
+          <t>26FP000747</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>DIGI MARZO-ABRIL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>6.45</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>060-26</t>
+          <t>DGFCJ2600260649</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>FONTANERO</t>
+          <t>DIGI MARZO-ABRIL</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO REYES PACHECO</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>195</v>
+        <v>6.45</v>
       </c>
       <c r="F186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>060-26</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>HONORARIOS</t>
+          <t>FONTANERO</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>INMOCEYLAN SL.</t>
+          <t>JOSE ANTONIO REYES PACHECO</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>4000</v>
+        <v>195</v>
       </c>
       <c r="F187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>FE26390013469837</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>NATURGY MARZO</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr"/>
+          <t>HONORARIOS</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>INMOCEYLAN SL.</t>
+        </is>
+      </c>
       <c r="E188" s="4" t="n">
-        <v>51.16</v>
+        <v>4000</v>
       </c>
       <c r="F188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>A/856</t>
+          <t>FE26390013469837</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
-        <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
-        </is>
-      </c>
+          <t>NATURGY MARZO</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr"/>
       <c r="E189" s="4" t="n">
-        <v>26.36</v>
+        <v>51.16</v>
       </c>
       <c r="F189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>ES20260426000008</t>
+          <t>A/856</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>COMPRA VENTILADORES</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>INDEPSALE TECHNOLOGY LIMITED</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>564.22</v>
+        <v>26.36</v>
       </c>
       <c r="F190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>4735701206</t>
+          <t>ES20260426000008</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>DISCO DIAMANTE MINI</t>
+          <t>COMPRA VENTILADORES</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>WURTH ESPAÑA SA</t>
+          <t>INDEPSALE TECHNOLOGY LIMITED</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>170.4</v>
+        <v>564.22</v>
       </c>
       <c r="F191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>M01/0087093395</t>
+          <t>4735701206</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL MARZ</t>
+          <t>DISCO DIAMANTE MINI</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>WURTH ESPAÑA SA</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>31.66</v>
+        <v>170.4</v>
       </c>
       <c r="F192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>26FP000621</t>
+          <t>M01/0087093395</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>JAZZTEL MARZ</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>69.08</v>
+        <v>31.66</v>
       </c>
       <c r="F193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>202622887</t>
+          <t>26FP000621</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
@@ -7222,50 +7218,50 @@
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>CONECTA 3 MARZO</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>E.S. PINOSO S.L.</t>
+        </is>
+      </c>
       <c r="E194" s="4" t="n">
-        <v>44.66</v>
+        <v>69.08</v>
       </c>
       <c r="F194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>015795/A/26/000979</t>
+          <t>202622887</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
-        <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
-        </is>
-      </c>
+          <t>CONECTA 3 MARZO</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr"/>
       <c r="E195" s="4" t="n">
-        <v>72.34</v>
+        <v>44.66</v>
       </c>
       <c r="F195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>011375/A/26/000711</t>
+          <t>015795/A/26/000979</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -7279,40 +7275,40 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>75.8</v>
+        <v>72.34</v>
       </c>
       <c r="F196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>V-26-03-32995</t>
+          <t>011375/A/26/000711</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL MARZO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1557.38</v>
+        <v>75.8</v>
       </c>
       <c r="F197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>G26.037</t>
+          <t>V-26-03-32995</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
@@ -7322,23 +7318,23 @@
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>PLENOIL MARZO</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>480</v>
+        <v>1557.38</v>
       </c>
       <c r="F198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>G26.037</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -7348,71 +7344,71 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO LABORAL MARZO</t>
-        </is>
-      </c>
-      <c r="D199" s="6" t="inlineStr"/>
+          <t>GRUA</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+        </is>
+      </c>
       <c r="E199" s="4" t="n">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="F199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>315438</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>DISTRIBUCION QING YONG SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO LABORAL MARZO</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr"/>
       <c r="E200" s="4" t="n">
-        <v>16.86</v>
+        <v>260</v>
       </c>
       <c r="F200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>602102633</t>
+          <t>315438</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>MAGUERA Y ADAPTADORES</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>COMERFONSA SL</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>74.18000000000001</v>
+        <v>16.86</v>
       </c>
       <c r="F201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>26FP000568</t>
+          <t>602102633</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
@@ -7422,28 +7418,28 @@
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MAGUERA Y ADAPTADORES</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>56.86</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="F202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>01250026/00001912</t>
+          <t>26FP000568</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -7453,44 +7449,44 @@
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>MOEVE RETAIL OPERATIONS S.A.U.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>17.65</v>
+        <v>56.86</v>
       </c>
       <c r="F203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>01250026/00001912</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>MARCO  + TAPADERA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>SALTOKI ELCHE SL.</t>
+          <t>MOEVE RETAIL OPERATIONS S.A.U.</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>-70.06999999999999</v>
+        <v>17.65</v>
       </c>
       <c r="F204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -7509,40 +7505,40 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="F205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>L021-456</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MARCO  + TAPADERA</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>SALTOKI ELCHE SL.</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>76.92</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>A20260211</t>
+          <t>L021-456</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
@@ -7552,80 +7548,80 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>PALA PLUS MARTILLO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>EUROBAMAS SL</t>
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>14.04</v>
+        <v>76.92</v>
       </c>
       <c r="F207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00194</t>
+          <t>A20260211</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>PARKING CANALEJAS</t>
+          <t>PALA PLUS MARTILLO</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>PARKING 3000 SL</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>6.28</v>
+        <v>14.04</v>
       </c>
       <c r="F208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>6/201072143</t>
+          <t>46126/101F00194</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PARKING CANALEJAS</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>PARKING 3000 SL</t>
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>17.5</v>
+        <v>6.28</v>
       </c>
       <c r="F209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>011375/A/26000600</t>
+          <t>6/201072143</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -7635,23 +7631,23 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="F210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>011375/V/26/000076</t>
+          <t>011375/A/26000600</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -7672,7 +7668,7 @@
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>011375/V/26/000076</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
@@ -7682,28 +7678,28 @@
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>FINA LIFANTE FLORES</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>11.24</v>
+        <v>60</v>
       </c>
       <c r="F212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>311843</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -7713,49 +7709,49 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>DISTRIBUCION QING YONG SL</t>
+          <t>FINA LIFANTE FLORES</t>
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>11.49</v>
+        <v>11.24</v>
       </c>
       <c r="F213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>26FP000428</t>
+          <t>311843</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>DISTRIBUCION QING YONG SL</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>61.98</v>
+        <v>11.49</v>
       </c>
       <c r="F214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000273</t>
+          <t>26FP000428</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -7765,23 +7761,23 @@
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>24.79</v>
+        <v>61.98</v>
       </c>
       <c r="F215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>26FP000499</t>
+          <t>005710/A/26/000273</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -7791,44 +7787,44 @@
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>118.53</v>
+        <v>24.79</v>
       </c>
       <c r="F216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00186</t>
+          <t>26FP000499</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>PARKING CANALEJAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>PARKING 3000 SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>12.6</v>
+        <v>118.53</v>
       </c>
       <c r="F217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00184</t>
+          <t>46126/101F00186</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
@@ -7847,14 +7843,14 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>12.69</v>
+        <v>12.6</v>
       </c>
       <c r="F218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00192</t>
+          <t>46126/101F00184</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -7873,14 +7869,14 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>11.94</v>
+        <v>12.69</v>
       </c>
       <c r="F219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00185</t>
+          <t>46126/101F00192</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
@@ -7899,14 +7895,14 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>12.4</v>
+        <v>11.94</v>
       </c>
       <c r="F220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00187</t>
+          <t>46126/101F00185</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -7925,14 +7921,14 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>8.6</v>
+        <v>12.4</v>
       </c>
       <c r="F221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>46126/101F00188</t>
+          <t>46126/101F00187</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
@@ -7951,102 +7947,102 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>12.19</v>
+        <v>8.6</v>
       </c>
       <c r="F222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>011375/V/26/000074</t>
+          <t>46126/101F00188</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>PARKING CANALEJAS</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>PARKING 3000 SL</t>
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>55</v>
+        <v>12.19</v>
       </c>
       <c r="F223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>26MST03210</t>
+          <t>011375/V/26/000074</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>RESPOSTAJE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>12.4</v>
+        <v>55</v>
       </c>
       <c r="F224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>L021-421</t>
+          <t>26MST03210</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>REPOSATAJE</t>
+          <t>RESPOSTAJE</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>EUROBAMAS SL</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>74.38</v>
+        <v>12.4</v>
       </c>
       <c r="F225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>L021-462</t>
+          <t>L021-421</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>REPOSATAJE</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
@@ -8055,41 +8051,45 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>60.17</v>
+        <v>74.38</v>
       </c>
       <c r="F226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>20269-0053</t>
+          <t>L021-462</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>ASESORAMIENTO CONTABLE FISCAL</t>
-        </is>
-      </c>
-      <c r="D227" s="6" t="inlineStr"/>
+          <t>REPOSTAJE</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>EUROBAMAS SL</t>
+        </is>
+      </c>
       <c r="E227" s="4" t="n">
-        <v>360.15</v>
+        <v>60.17</v>
       </c>
       <c r="F227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>2026-0081</t>
+          <t>20269-0053</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
@@ -8106,133 +8106,129 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>602102263</t>
+          <t>2026-0081</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>MANGUERA RIEGO</t>
-        </is>
-      </c>
-      <c r="D229" s="6" t="inlineStr">
-        <is>
-          <t>COMERFONSA SL</t>
-        </is>
-      </c>
+          <t>ASESORAMIENTO CONTABLE FISCAL</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr"/>
       <c r="E229" s="4" t="n">
-        <v>142.11</v>
+        <v>360.15</v>
       </c>
       <c r="F229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>F0018-026-54-0/0000185</t>
+          <t>602102263</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>MANGUERA RIEGO</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>COMERFONSA SL</t>
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>2.02</v>
+        <v>142.11</v>
       </c>
       <c r="F230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>F0018-026-54-0/0000185</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL FEBRERO</t>
-        </is>
-      </c>
-      <c r="D231" s="6" t="inlineStr"/>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>BRICOLAJE BRICOMAN SLU</t>
+        </is>
+      </c>
       <c r="E231" s="4" t="n">
-        <v>260</v>
+        <v>2.02</v>
       </c>
       <c r="F231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>A/502</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="D232" s="6" t="inlineStr">
-        <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL FEBRERO</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr"/>
       <c r="E232" s="4" t="n">
-        <v>21.82</v>
+        <v>260</v>
       </c>
       <c r="F232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>2600088</t>
+          <t>A/502</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>PUERTA RELLENABLE GALVANIZADA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>TOSANTO SL</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>105.08</v>
+        <v>21.82</v>
       </c>
       <c r="F233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>2600106</t>
+          <t>2600088</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
@@ -8242,7 +8238,7 @@
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>PUERTA RELLENABLE</t>
+          <t>PUERTA RELLENABLE GALVANIZADA</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
@@ -8251,358 +8247,358 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>179.87</v>
+        <v>105.08</v>
       </c>
       <c r="F234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>FE26390009325438</t>
+          <t>2600106</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>NATURGY FEBRERO</t>
-        </is>
-      </c>
-      <c r="D235" s="6" t="inlineStr"/>
+          <t>PUERTA RELLENABLE</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>TOSANTO SL</t>
+        </is>
+      </c>
       <c r="E235" s="4" t="n">
-        <v>40.54</v>
+        <v>179.87</v>
       </c>
       <c r="F235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>035651026/00000530</t>
+          <t>FE26390009325438</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D236" s="6" t="inlineStr">
-        <is>
-          <t>VECTALIA OIL SL.</t>
-        </is>
-      </c>
+          <t>NATURGY FEBRERO</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr"/>
       <c r="E236" s="4" t="n">
-        <v>26.37</v>
+        <v>40.54</v>
       </c>
       <c r="F236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>6/201068505</t>
+          <t>035651026/00000530</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>08/03/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>VECTALIA OIL SL.</t>
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>26.37</v>
       </c>
       <c r="F237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>2600111</t>
+          <t>6/201068505</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>08/03/2026</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>CABALLETES TRABAJAO TELESCOPICOS</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>TOSANTO SL</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>328.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>F0018-026-51-07/0002824</t>
+          <t>2600111</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>CAPAZOS</t>
+          <t>CABALLETES TRABAJAO TELESCOPICOS</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>TOSANTO SL</t>
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>28.51</v>
+        <v>328.1</v>
       </c>
       <c r="F239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>ES0000030611120-1225</t>
+          <t>F0018-026-51-07/0002824</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>VIA T ENERO</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr"/>
+          <t>CAPAZOS</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>BRICOLAJE BRICOMAN SLU</t>
+        </is>
+      </c>
       <c r="E240" s="4" t="n">
-        <v>10.81</v>
+        <v>28.51</v>
       </c>
       <c r="F240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>ES0000030849450-0126</t>
+          <t>ES0000030611120-1225</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>VIA T FEBRERO</t>
+          <t>VIA T ENERO</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr"/>
       <c r="E241" s="4" t="n">
-        <v>32.52</v>
+        <v>10.81</v>
       </c>
       <c r="F241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>#F260088899</t>
+          <t>ES0000030849450-0126</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>21/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>HOLDED FEBRERO</t>
-        </is>
-      </c>
-      <c r="D242" s="6" t="inlineStr">
-        <is>
-          <t>HOLDED TECHNOLOGIES SL.</t>
-        </is>
-      </c>
+          <t>VIA T FEBRERO</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr"/>
       <c r="E242" s="4" t="n">
-        <v>59</v>
+        <v>32.52</v>
       </c>
       <c r="F242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>ES0000031076700-0226</t>
+          <t>#F260088899</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>21/02/2026</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>VIA T MARZO</t>
-        </is>
-      </c>
-      <c r="D243" s="6" t="inlineStr"/>
+          <t>HOLDED FEBRERO</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>HOLDED TECHNOLOGIES SL.</t>
+        </is>
+      </c>
       <c r="E243" s="4" t="n">
-        <v>9.42</v>
+        <v>59</v>
       </c>
       <c r="F243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>Nº3</t>
+          <t>ES0000031076700-0226</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE MARZO</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
-        <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
-        </is>
-      </c>
+          <t>VIA T MARZO</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr"/>
       <c r="E244" s="4" t="n">
-        <v>350</v>
+        <v>9.42</v>
       </c>
       <c r="F244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>V-26-02-18969</t>
+          <t>Nº3</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>GASOLINA FEBRERO</t>
+          <t>ALQUILER NAVE MARZO</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>1017.62</v>
+        <v>350</v>
       </c>
       <c r="F245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>M01/0087059497</t>
+          <t>V-26-02-18969</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL FEBRERO</t>
+          <t>GASOLINA FEBRERO</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>41.28</v>
+        <v>1017.62</v>
       </c>
       <c r="F246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>2026-0025</t>
+          <t>M01/0087059497</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>IGUALA ENERO</t>
-        </is>
-      </c>
-      <c r="D247" s="6" t="inlineStr"/>
+          <t>JAZZTEL FEBRERO</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>ORANGE ESPAGNE SAU.</t>
+        </is>
+      </c>
       <c r="E247" s="4" t="n">
-        <v>360.15</v>
+        <v>41.28</v>
       </c>
       <c r="F247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000213</t>
+          <t>2026-0025</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
-        </is>
-      </c>
-      <c r="D248" s="6" t="inlineStr">
-        <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
-        </is>
-      </c>
+          <t>IGUALA ENERO</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr"/>
       <c r="E248" s="4" t="n">
-        <v>33.06</v>
+        <v>360.15</v>
       </c>
       <c r="F248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>26MET01030</t>
+          <t>005710/A/26/000213</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
@@ -8617,96 +8613,96 @@
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>16.53</v>
+        <v>33.06</v>
       </c>
       <c r="F249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>260084</t>
+          <t>26MET01030</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>ROSALIA MARTINEZ RUIZ</t>
+          <t>FLASH-CAR LEVANTE SERVICIOS SL</t>
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>13.84</v>
+        <v>16.53</v>
       </c>
       <c r="F250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>18132026FN00000003</t>
+          <t>260084</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>ROSALIA MARTINEZ RUIZ</t>
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>19.79</v>
+        <v>13.84</v>
       </c>
       <c r="F251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00026</t>
+          <t>18132026FN00000003</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>PROLONGADOR 50M IP55</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>1203.5</v>
+        <v>19.79</v>
       </c>
       <c r="F252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00025</t>
+          <t>INV/2026/00026</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -8716,7 +8712,7 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>GENERADOR MOTOR HONDA</t>
+          <t>PROLONGADOR 50M IP55</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
@@ -8725,66 +8721,66 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>1430</v>
+        <v>1203.5</v>
       </c>
       <c r="F253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>6/201062718</t>
+          <t>INV/2026/00025</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>GENERADOR MOTOR HONDA</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>15.48</v>
+        <v>1430</v>
       </c>
       <c r="F254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>FE2630005167586</t>
+          <t>6/201062718</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>NATURGY ENERO</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>48.52</v>
+        <v>15.48</v>
       </c>
       <c r="F255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>M01/0087025989</t>
+          <t>FE2630005167586</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
@@ -8794,75 +8790,75 @@
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL ENERO</t>
+          <t>NATURGY ENERO</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>41.28</v>
+        <v>48.52</v>
       </c>
       <c r="F256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00027</t>
+          <t>M01/0087025989</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>GUANTES TRABAJO</t>
+          <t>JAZZTEL ENERO</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>120</v>
+        <v>41.28</v>
       </c>
       <c r="F257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>26FP000201</t>
+          <t>INV/2026/00027</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>GUANTES TRABAJO</t>
         </is>
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>61.99</v>
+        <v>120</v>
       </c>
       <c r="F258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>A26-0031</t>
+          <t>26FP000201</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -8872,127 +8868,127 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>ON BOARGING BILLD IN</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>SIDE QUEST APES, S.L.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>1200</v>
+        <v>61.99</v>
       </c>
       <c r="F259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>6/201062120</t>
+          <t>A26-0031</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ON BOARGING BILLD IN</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>SIDE QUEST APES, S.L.</t>
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>19.26</v>
+        <v>1200</v>
       </c>
       <c r="F260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>6/201062120</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>CHAQUETAS LABORAL</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>INDICATIVO SL</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>430</v>
+        <v>19.26</v>
       </c>
       <c r="F261" s="6" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C262" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE FEBRERO</t>
+          <t>CHAQUETAS LABORAL</t>
         </is>
       </c>
       <c r="D262" s="6" t="inlineStr">
         <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
+          <t>INDICATIVO SL</t>
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>350</v>
+        <v>430</v>
       </c>
       <c r="F262" s="6" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000120</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ALQUILER NAVE FEBRERO</t>
         </is>
       </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>74.38</v>
+        <v>350</v>
       </c>
       <c r="F263" s="6" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>26FP000199</t>
+          <t>005710/A/26/000120</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
@@ -9007,96 +9003,96 @@
       </c>
       <c r="D264" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>37.19</v>
+        <v>74.38</v>
       </c>
       <c r="F264" s="6" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00014</t>
+          <t>26FP000199</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>ROLLO HILO DE ALAMBRE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D265" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>300</v>
+        <v>37.19</v>
       </c>
       <c r="F265" s="6" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>FV26-01517</t>
+          <t>INV/2026/00014</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>GUANTE SOLDADOR / MASCARILLA / SOPLETE</t>
+          <t>ROLLO HILO DE ALAMBRE</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
         <is>
-          <t>SUMINISTROS INDUSTRIALES FARELL SA</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>160.74</v>
+        <v>300</v>
       </c>
       <c r="F266" s="6" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>18132026FN00000001</t>
+          <t>FV26-01517</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>GUANTE SOLDADOR / MASCARILLA / SOPLETE</t>
         </is>
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
+          <t>SUMINISTROS INDUSTRIALES FARELL SA</t>
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>13.18</v>
+        <v>160.74</v>
       </c>
       <c r="F267" s="6" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>055513026/00000162</t>
+          <t>18132026FN00000001</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
@@ -9111,44 +9107,44 @@
       </c>
       <c r="D268" s="6" t="inlineStr">
         <is>
-          <t>REATA ESTACIONES SL.</t>
+          <t>CAMPSA ESTACIONES DE SERVICIO SA</t>
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>29.38</v>
+        <v>13.18</v>
       </c>
       <c r="F268" s="6" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>026-0001-415359</t>
+          <t>055513026/00000162</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>ALARGADERA</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>REATA ESTACIONES SL.</t>
         </is>
       </c>
       <c r="E269" s="4" t="n">
-        <v>51.24</v>
+        <v>29.38</v>
       </c>
       <c r="F269" s="6" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00015</t>
+          <t>026-0001-415359</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
@@ -9158,75 +9154,75 @@
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>PROLONGADOR 50M IP55</t>
+          <t>ALARGADERA</t>
         </is>
       </c>
       <c r="D270" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>234</v>
+        <v>51.24</v>
       </c>
       <c r="F270" s="6" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>618104210</t>
+          <t>INV/2026/00015</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>VARIOS</t>
+          <t>PROLONGADOR 50M IP55</t>
         </is>
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>JYSK DBL IBERIA SLU</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E271" s="4" t="n">
-        <v>44.86</v>
+        <v>234</v>
       </c>
       <c r="F271" s="6" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>346593</t>
+          <t>618104210</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>VARIOS</t>
         </is>
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>CONCORDY SA</t>
+          <t>JYSK DBL IBERIA SLU</t>
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>56.07</v>
+        <v>44.86</v>
       </c>
       <c r="F272" s="6" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>346593</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
@@ -9236,283 +9232,283 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>PEGATINAS VALLAS</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>INDICATIVO SL</t>
+          <t>CONCORDY SA</t>
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>200</v>
+        <v>56.07</v>
       </c>
       <c r="F273" s="6" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>DGFCJ2600056841</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>DIGI ENERO</t>
+          <t>PEGATINAS VALLAS</t>
         </is>
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>INDICATIVO SL</t>
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>9.09</v>
+        <v>200</v>
       </c>
       <c r="F274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>FE26390001083912</t>
+          <t>DGFCJ2600056841</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>NATURGY DICIEMBRE</t>
+          <t>DIGI ENERO</t>
         </is>
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>32.89</v>
+        <v>9.09</v>
       </c>
       <c r="F275" s="6" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>26.801</t>
+          <t>FE26390001083912</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>MAQUINA STHILL</t>
+          <t>NATURGY DICIEMBRE</t>
         </is>
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>MARHUENDA IMPORTACIONES SL</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E276" s="4" t="n">
-        <v>1716.53</v>
+        <v>32.89</v>
       </c>
       <c r="F276" s="6" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>031-0001-025095</t>
+          <t>26.801</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>CALZADO LABORAL</t>
+          <t>MAQUINA STHILL</t>
         </is>
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>MARHUENDA IMPORTACIONES SL</t>
         </is>
       </c>
       <c r="E277" s="4" t="n">
-        <v>119.09</v>
+        <v>1716.53</v>
       </c>
       <c r="F277" s="6" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>6/201058487</t>
+          <t>031-0001-025095</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>CALZADO LABORAL</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>ESTACION OMEGA ESPINARDO SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>16.94</v>
+        <v>119.09</v>
       </c>
       <c r="F278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>M01/0086992086</t>
+          <t>6/201058487</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>JAZZTEL DICIEMBRE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>ORANGE ESPAGNE SAU.</t>
+          <t>ESTACION OMEGA ESPINARDO SL</t>
         </is>
       </c>
       <c r="E279" s="4" t="n">
-        <v>73.02</v>
+        <v>16.94</v>
       </c>
       <c r="F279" s="6" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>FE25390028648675</t>
+          <t>M01/0086992086</t>
         </is>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C280" s="6" t="inlineStr">
         <is>
-          <t>NATURGY AGOSTO</t>
+          <t>JAZZTEL DICIEMBRE</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>NATURGY IBERIA SA.</t>
+          <t>ORANGE ESPAGNE SAU.</t>
         </is>
       </c>
       <c r="E280" s="4" t="n">
-        <v>19.68</v>
+        <v>73.02</v>
       </c>
       <c r="F280" s="6" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>V-26-01-19308</t>
+          <t>FE25390028648675</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL ENERO</t>
+          <t>NATURGY AGOSTO</t>
         </is>
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>PLENOIL SL.</t>
+          <t>NATURGY IBERIA SA.</t>
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>1109.93</v>
+        <v>19.68</v>
       </c>
       <c r="F281" s="6" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>01262026A100017608</t>
+          <t>V-26-01-19308</t>
         </is>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>AGUA ENERO</t>
+          <t>PLENOIL ENERO</t>
         </is>
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
+          <t>PLENOIL SL.</t>
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>31.33</v>
+        <v>1109.93</v>
       </c>
       <c r="F282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>S101-000147</t>
+          <t>01262026A100017608</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>SELLO FACTURAS</t>
+          <t>AGUA ENERO</t>
         </is>
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>ENDLESS SYSTEMS SLU</t>
+          <t>HIDRAQUA GESTIÓN INTEGRAL DE AGUAS DE LEVANTE SL</t>
         </is>
       </c>
       <c r="E283" s="4" t="n">
-        <v>26.45</v>
+        <v>31.33</v>
       </c>
       <c r="F283" s="6" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00042</t>
+          <t>S101-000147</t>
         </is>
       </c>
       <c r="B284" s="6" t="inlineStr">
@@ -9522,23 +9518,23 @@
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>ROLLO ALAMBRE</t>
+          <t>SELLO FACTURAS</t>
         </is>
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ENDLESS SYSTEMS SLU</t>
         </is>
       </c>
       <c r="E284" s="4" t="n">
-        <v>1000</v>
+        <v>26.45</v>
       </c>
       <c r="F284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00041</t>
+          <t>INV/2026/00042</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
@@ -9548,7 +9544,7 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>ROLLO ALAMBRE</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
@@ -9557,93 +9553,93 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>389.7</v>
+        <v>1000</v>
       </c>
       <c r="F285" s="6" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>INV/2026/00041</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>31/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>ASESORIA LABORAL ENERO</t>
-        </is>
-      </c>
-      <c r="D286" s="6" t="inlineStr"/>
+          <t>MATERIAL OBRA</t>
+        </is>
+      </c>
+      <c r="D286" s="6" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+        </is>
+      </c>
       <c r="E286" s="4" t="n">
-        <v>260</v>
+        <v>389.7</v>
       </c>
       <c r="F286" s="6" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER NAVE ENERO</t>
-        </is>
-      </c>
-      <c r="D287" s="6" t="inlineStr">
-        <is>
-          <t>PINKY VELVET INTERNATIONAL SL</t>
-        </is>
-      </c>
+          <t>ASESORIA LABORAL ENERO</t>
+        </is>
+      </c>
+      <c r="D287" s="6" t="inlineStr"/>
       <c r="E287" s="4" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="F287" s="6" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>048304026/00000807</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>ALQUILER NAVE ENERO</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>JR VIDAL RICO SL</t>
+          <t>PINKY VELVET INTERNATIONAL SL</t>
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>59.66</v>
+        <v>350</v>
       </c>
       <c r="F288" s="6" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>L021-81</t>
+          <t>048304026/00000807</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
@@ -9653,44 +9649,44 @@
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>E.E. CAÑIZARES, CB</t>
+          <t>JR VIDAL RICO SL</t>
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>74.38</v>
+        <v>59.66</v>
       </c>
       <c r="F289" s="6" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>FV-26-005110</t>
+          <t>L021-81</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>GUANTES</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>E.E. CAÑIZARES, CB</t>
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>7.25</v>
+        <v>74.38</v>
       </c>
       <c r="F290" s="6" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>FV26-004716</t>
+          <t>FV-26-005110</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
@@ -9700,7 +9696,7 @@
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>GUANTES</t>
         </is>
       </c>
       <c r="D291" s="6" t="inlineStr">
@@ -9709,45 +9705,45 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>321.37</v>
+        <v>7.25</v>
       </c>
       <c r="F291" s="6" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>26FP000345</t>
+          <t>FV26-004716</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>24.9</v>
+        <v>321.37</v>
       </c>
       <c r="F292" s="6" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>005710/A/26/000210</t>
+          <t>26FP000345</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
@@ -9757,96 +9753,96 @@
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>63.79</v>
+        <v>24.9</v>
       </c>
       <c r="F293" s="6" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>INV/2026/00048</t>
+          <t>005710/A/26/000210</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>MASCARILLAS / CALDERETA / NIVEL ASER</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>REPSOL SOLUCIONES ENERGETICAS SA.</t>
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>976.7</v>
+        <v>63.79</v>
       </c>
       <c r="F294" s="6" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>2026/A-789</t>
+          <t>INV/2026/00048</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>15/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>BARNIZ</t>
+          <t>MASCARILLAS / CALDERETA / NIVEL ASER</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>PINTURAS IDELLA SL.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="E295" s="4" t="n">
-        <v>7.34</v>
+        <v>976.7</v>
       </c>
       <c r="F295" s="6" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>DGFCJ2600124525</t>
+          <t>2026/A-789</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>15/02/2026</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>DIGI FEBRERO</t>
+          <t>BARNIZ</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>DIGI SPAIN TELECOM SL</t>
+          <t>PINTURAS IDELLA SL.</t>
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>9.09</v>
+        <v>7.34</v>
       </c>
       <c r="F296" s="6" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>FV26-004861</t>
+          <t>DGFCJ2600124525</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
@@ -9856,23 +9852,23 @@
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>CAPAZO / BORRIQUETA / TAPA CONTADOR</t>
+          <t>DIGI FEBRERO</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>HIJOS DE JOSE BUSQUIER SL</t>
+          <t>DIGI SPAIN TELECOM SL</t>
         </is>
       </c>
       <c r="E297" s="4" t="n">
-        <v>143.47</v>
+        <v>9.09</v>
       </c>
       <c r="F297" s="6" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>FV26-004890</t>
+          <t>FV26-004861</t>
         </is>
       </c>
       <c r="B298" s="6" t="inlineStr">
@@ -9882,7 +9878,7 @@
       </c>
       <c r="C298" s="6" t="inlineStr">
         <is>
-          <t>ESPATULA</t>
+          <t>CAPAZO / BORRIQUETA / TAPA CONTADOR</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
@@ -9891,50 +9887,50 @@
         </is>
       </c>
       <c r="E298" s="4" t="n">
-        <v>54.51</v>
+        <v>143.47</v>
       </c>
       <c r="F298" s="6" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>2600538</t>
+          <t>FV26-004890</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL VARIO</t>
+          <t>ESPATULA</t>
         </is>
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>FERRELDA SL</t>
+          <t>HIJOS DE JOSE BUSQUIER SL</t>
         </is>
       </c>
       <c r="E299" s="4" t="n">
-        <v>44.67</v>
+        <v>54.51</v>
       </c>
       <c r="F299" s="6" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>2600636</t>
+          <t>2600538</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
         <is>
-          <t>TALADRO ATORNILLADOR</t>
+          <t>MATERIAL VARIO</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
@@ -9943,102 +9939,128 @@
         </is>
       </c>
       <c r="E300" s="4" t="n">
-        <v>57.85</v>
+        <v>44.67</v>
       </c>
       <c r="F300" s="6" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>26FP000292</t>
+          <t>2600636</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>REPOSTAJE</t>
+          <t>TALADRO ATORNILLADOR</t>
         </is>
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>E.S. PINOSO S.L.</t>
+          <t>FERRELDA SL</t>
         </is>
       </c>
       <c r="E301" s="4" t="n">
-        <v>107.46</v>
+        <v>57.85</v>
       </c>
       <c r="F301" s="6" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>FSIM 1 2026/001807</t>
+          <t>26FP000292</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="C302" s="6" t="inlineStr">
         <is>
-          <t>DISCO DE CORTE</t>
+          <t>REPOSTAJE</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA-VISTA ALEGRE SL</t>
+          <t>E.S. PINOSO S.L.</t>
         </is>
       </c>
       <c r="E302" s="4" t="n">
-        <v>8.26</v>
+        <v>107.46</v>
       </c>
       <c r="F302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
+          <t>FSIM 1 2026/001807</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="C303" s="6" t="inlineStr">
+        <is>
+          <t>DISCO DE CORTE</t>
+        </is>
+      </c>
+      <c r="D303" s="6" t="inlineStr">
+        <is>
+          <t>FERRETERIA-VISTA ALEGRE SL</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="F303" s="6" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="inlineStr">
+        <is>
           <t>#F260035256</t>
         </is>
       </c>
-      <c r="B303" s="6" t="inlineStr">
+      <c r="B304" s="6" t="inlineStr">
         <is>
           <t>21/01/2026</t>
         </is>
       </c>
-      <c r="C303" s="6" t="inlineStr">
+      <c r="C304" s="6" t="inlineStr">
         <is>
           <t>HOLDED ENERO</t>
         </is>
       </c>
-      <c r="D303" s="6" t="inlineStr">
+      <c r="D304" s="6" t="inlineStr">
         <is>
           <t>HOLDED TECHNOLOGIES SL.</t>
         </is>
       </c>
-      <c r="E303" s="4" t="n">
+      <c r="E304" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="F303" s="6" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="8" t="n"/>
-      <c r="B304" s="8" t="n"/>
-      <c r="C304" s="8" t="inlineStr">
+      <c r="F304" s="6" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="8" t="n"/>
+      <c r="B305" s="8" t="n"/>
+      <c r="C305" s="8" t="inlineStr">
         <is>
           <t>TOTAL GASTOS GENERALES</t>
         </is>
       </c>
-      <c r="D304" s="8" t="n"/>
-      <c r="E304" s="9">
-        <f>SUM(E4:E303)</f>
-        <v/>
-      </c>
-      <c r="F304" s="8" t="n"/>
+      <c r="D305" s="8" t="n"/>
+      <c r="E305" s="9">
+        <f>SUM(E4:E304)</f>
+        <v/>
+      </c>
+      <c r="F305" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15952,7 +15974,7 @@
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G129" s="4" t="n">
@@ -16372,7 +16394,7 @@
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G141" s="4" t="n">
@@ -16547,7 +16569,7 @@
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
@@ -17422,7 +17444,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G171" s="4" t="n">
@@ -28247,7 +28269,7 @@
       </c>
       <c r="F482" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G482" s="4" t="n">
@@ -28527,7 +28549,7 @@
       </c>
       <c r="F490" s="6" t="inlineStr">
         <is>
-          <t>SIN IMPUTAR</t>
+          <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G490" s="4" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>171613.88</v>
+        <v>171885.2</v>
       </c>
       <c r="D8" s="6">
         <f>C8/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2938</v>
+        <v>2994</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2994</v>
+        <v>3074</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3074</v>
+        <v>3080</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3080</v>
+        <v>3155</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>305555.25</v>
+        <v>364931.58</v>
       </c>
       <c r="D14" s="6">
         <f>C14/C27</f>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>63374.44</v>
+        <v>82667.51999999999</v>
       </c>
       <c r="D18" s="6">
         <f>C18/C27</f>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>15019.02</v>
+        <v>24613.04</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C27</f>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>16100.81</v>
+        <v>16856.76</v>
       </c>
       <c r="D22" s="6">
         <f>C22/C27</f>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>61269.98</v>
+        <v>92506.82000000001</v>
       </c>
       <c r="D23" s="6">
         <f>C23/C27</f>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>34049.67</v>
+        <v>49293.55</v>
       </c>
       <c r="D24" s="6">
         <f>C24/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3155</v>
+        <v>3233</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>871</v>
+        <v>894</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4119</v>
+        <v>4135</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>17</v>
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3238</v>
+        <v>3305</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>24613.04</v>
+        <v>24371.04</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>24371.04</v>
+        <v>25135.12</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4135</v>
+        <v>4143</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>17</v>
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3305</v>
+        <v>3375</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10959,7 +10959,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>627</v>
+        <v>669</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>51343.23</v>
+        <v>52301.25</v>
       </c>
       <c r="D19" s="6">
         <f>C19/C27</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3374</v>
+        <v>3429</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1482</v>
+        <v>1506</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>669</v>
+        <v>693</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4143</v>
+        <v>4149</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>17</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>3429</v>
+        <v>3504</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>17</v>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>17</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17</v>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>
